--- a/results/tsp_final_results.xlsx
+++ b/results/tsp_final_results.xlsx
@@ -486,17 +486,17 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>518</v>
+        <v>544</v>
       </c>
       <c r="E2" t="n">
-        <v>21.5962441314554</v>
+        <v>27.69953051643192</v>
       </c>
       <c r="F2" t="n">
         <v>0.0003740787506103516</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>[21, 0, 31, 10, 37, 4, 48, 8, 49, 15, 1, 28, 20, 33, 29, 9, 38, 32, 44, 14, 43, 36, 16, 3, 17, 46, 11, 45, 50, 26, 5, 47, 7, 25, 30, 27, 2, 19, 34, 35, 6, 22, 23, 13, 24, 12, 40, 18, 41, 39, 42]</t>
+          <t>[4, 37, 8, 48, 9, 29, 33, 49, 15, 1, 28, 20, 19, 34, 35, 2, 27, 30, 7, 25, 6, 22, 23, 13, 24, 17, 3, 16, 36, 14, 43, 41, 18, 40, 12, 39, 46, 11, 45, 50, 26, 0, 31, 10, 21, 47, 5, 42, 44, 32, 38]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -520,17 +520,17 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>450</v>
+        <v>431</v>
       </c>
       <c r="E3" t="n">
-        <v>5.633802816901409</v>
+        <v>1.173708920187793</v>
       </c>
       <c r="F3" t="n">
-        <v>1.785118341445923</v>
+        <v>1.730304956436157</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>[21, 2, 19, 34, 35, 27, 30, 25, 6, 22, 42, 23, 5, 26, 50, 45, 11, 46, 17, 13, 24, 12, 40, 39, 18, 41, 3, 16, 36, 43, 14, 44, 32, 38, 9, 29, 33, 20, 28, 1, 15, 49, 8, 48, 4, 37, 10, 31, 0, 47, 7]</t>
+          <t>[20, 33, 29, 9, 38, 32, 44, 14, 43, 41, 18, 39, 40, 12, 24, 13, 23, 42, 6, 22, 47, 5, 26, 50, 45, 11, 46, 17, 3, 16, 36, 4, 48, 37, 10, 31, 0, 21, 7, 25, 30, 27, 2, 35, 34, 19, 28, 1, 15, 8, 49]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -554,17 +554,17 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E4" t="n">
-        <v>6.338028169014084</v>
+        <v>6.807511737089202</v>
       </c>
       <c r="F4" t="n">
-        <v>60.0000159740448</v>
+        <v>60.00000095367432</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>[15, 49, 8, 37, 10, 31, 0, 21, 27, 30, 7, 25, 6, 22, 42, 23, 17, 46, 3, 16, 36, 14, 43, 41, 39, 18, 40, 12, 24, 13, 5, 47, 26, 50, 45, 11, 4, 48, 9, 44, 32, 38, 29, 33, 20, 28, 19, 34, 35, 2, 1]</t>
+          <t>[46, 3, 16, 14, 36, 11, 45, 50, 26, 0, 31, 10, 37, 4, 48, 8, 49, 15, 1, 28, 20, 33, 29, 9, 38, 32, 44, 43, 41, 18, 39, 40, 12, 24, 23, 42, 22, 6, 25, 30, 27, 2, 35, 34, 19, 21, 7, 47, 5, 13, 17]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -588,17 +588,17 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>0.2347417840375587</v>
       </c>
       <c r="F5" t="n">
-        <v>0.111616849899292</v>
+        <v>0.08046102523803711</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>[25, 7, 21, 0, 31, 10, 37, 4, 36, 16, 3, 17, 46, 11, 45, 50, 26, 5, 47, 22, 6, 42, 23, 13, 24, 12, 40, 39, 18, 41, 43, 14, 44, 32, 38, 9, 48, 8, 29, 33, 49, 15, 20, 28, 1, 19, 34, 35, 2, 27, 30]</t>
+          <t>[2, 27, 30, 25, 7, 21, 0, 31, 10, 37, 8, 48, 4, 36, 16, 3, 17, 46, 11, 45, 50, 26, 5, 47, 22, 6, 42, 23, 13, 24, 12, 40, 39, 18, 41, 43, 14, 44, 32, 38, 9, 29, 33, 49, 15, 20, 28, 1, 19, 34, 35]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -628,7 +628,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1371331214904785</v>
+        <v>0.1212430000305176</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
@@ -652,17 +652,17 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>9323</v>
+        <v>9098</v>
       </c>
       <c r="E7" t="n">
-        <v>23.61442588172898</v>
+        <v>20.63113232564307</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0003859996795654297</v>
+        <v>0.0003869533538818359</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>[14, 4, 23, 47, 37, 39, 36, 38, 35, 34, 33, 43, 45, 15, 49, 19, 22, 30, 17, 21, 0, 48, 31, 44, 18, 40, 7, 9, 8, 42, 3, 5, 24, 11, 27, 26, 25, 46, 12, 13, 51, 10, 50, 32, 2, 16, 20, 29, 28, 41, 6, 1]</t>
+          <t>[23, 47, 4, 14, 5, 3, 24, 45, 43, 33, 34, 35, 38, 39, 37, 36, 48, 31, 0, 21, 30, 17, 2, 18, 44, 40, 7, 9, 8, 42, 32, 50, 11, 27, 26, 25, 46, 12, 13, 51, 10, 15, 49, 19, 22, 29, 20, 16, 41, 6, 1, 28]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -686,17 +686,17 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8054</v>
+        <v>8144</v>
       </c>
       <c r="E8" t="n">
-        <v>6.788650225404402</v>
+        <v>7.981967647838769</v>
       </c>
       <c r="F8" t="n">
-        <v>1.78541111946106</v>
+        <v>1.704467296600342</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>[26, 27, 25, 46, 28, 29, 1, 6, 41, 20, 16, 2, 40, 7, 8, 9, 32, 42, 18, 44, 31, 48, 0, 21, 17, 30, 22, 19, 49, 15, 45, 43, 33, 34, 35, 38, 39, 36, 37, 47, 23, 4, 14, 5, 3, 24, 11, 50, 10, 51, 13, 12]</t>
+          <t>[45, 24, 3, 5, 14, 4, 23, 47, 37, 36, 39, 38, 35, 34, 33, 43, 19, 22, 20, 41, 1, 6, 16, 2, 17, 30, 21, 0, 48, 31, 44, 18, 40, 7, 8, 9, 42, 32, 50, 10, 51, 13, 12, 26, 11, 27, 25, 46, 28, 29, 49, 15]</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -720,17 +720,17 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8206</v>
+        <v>8488</v>
       </c>
       <c r="E9" t="n">
-        <v>8.804030761071333</v>
+        <v>12.54309201803235</v>
       </c>
       <c r="F9" t="n">
-        <v>60.00007510185242</v>
+        <v>60.00001788139343</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>[2, 17, 30, 21, 33, 34, 35, 38, 39, 36, 37, 47, 23, 4, 14, 5, 3, 24, 45, 43, 15, 49, 19, 22, 0, 48, 31, 44, 18, 40, 7, 8, 9, 42, 32, 50, 11, 27, 25, 26, 10, 51, 13, 12, 46, 28, 29, 1, 6, 41, 20, 16]</t>
+          <t>[20, 30, 21, 0, 35, 38, 39, 36, 37, 47, 23, 4, 14, 5, 3, 24, 45, 15, 49, 19, 22, 43, 33, 34, 48, 31, 44, 18, 40, 7, 8, 9, 42, 32, 50, 10, 11, 27, 25, 26, 12, 51, 13, 46, 28, 29, 17, 2, 16, 6, 1, 41]</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -760,11 +760,11 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1172378063201904</v>
+        <v>0.1047639846801758</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>[5, 14, 4, 23, 47, 37, 36, 39, 38, 35, 34, 33, 43, 45, 15, 28, 49, 19, 22, 29, 1, 6, 41, 20, 16, 2, 17, 30, 21, 0, 48, 31, 44, 18, 40, 7, 8, 9, 42, 32, 50, 10, 51, 13, 12, 46, 25, 26, 27, 11, 24, 3]</t>
+          <t>[51, 10, 50, 32, 42, 9, 8, 7, 40, 18, 44, 31, 48, 0, 21, 30, 17, 2, 16, 20, 41, 6, 1, 29, 22, 19, 49, 28, 15, 45, 43, 33, 34, 35, 38, 39, 36, 37, 47, 23, 4, 14, 5, 3, 24, 11, 27, 26, 25, 46, 12, 13]</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.03368663787841797</v>
+        <v>0.03308010101318359</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
@@ -818,17 +818,17 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>60532</v>
+        <v>62693</v>
       </c>
       <c r="E12" t="n">
-        <v>25.60851611296715</v>
+        <v>30.09275590877965</v>
       </c>
       <c r="F12" t="n">
-        <v>0.007876873016357422</v>
+        <v>0.008841991424560547</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>[132, 131, 128, 103, 129, 130, 164, 165, 200, 198, 199, 227, 202, 228, 230, 229, 232, 231, 276, 275, 274, 278, 277, 280, 281, 282, 279, 283, 284, 285, 218, 220, 221, 208, 209, 207, 206, 203, 204, 205, 298, 226, 225, 224, 222, 223, 219, 210, 159, 160, 139, 138, 96, 95, 94, 97, 82, 83, 98, 99, 100, 101, 81, 78, 80, 19, 17, 18, 16, 14, 15, 84, 85, 93, 86, 90, 88, 89, 87, 13, 12, 11, 10, 9, 8, 7, 6, 91, 92, 143, 145, 144, 147, 146, 148, 149, 150, 151, 152, 153, 154, 155, 213, 214, 292, 291, 289, 290, 288, 287, 286, 216, 215, 217, 211, 212, 158, 157, 156, 142, 141, 140, 137, 136, 134, 135, 133, 162, 161, 163, 201, 102, 77, 75, 79, 74, 76, 71, 72, 73, 70, 28, 27, 26, 25, 24, 23, 22, 20, 21, 68, 69, 66, 67, 65, 62, 63, 104, 64, 61, 106, 105, 107, 108, 109, 60, 58, 59, 57, 56, 38, 42, 40, 39, 41, 36, 37, 35, 34, 31, 30, 29, 33, 32, 44, 45, 43, 46, 47, 48, 49, 50, 51, 52, 53, 55, 54, 115, 113, 114, 116, 118, 119, 121, 120, 124, 123, 125, 126, 122, 112, 110, 111, 127, 173, 171, 170, 172, 178, 188, 186, 177, 175, 174, 176, 189, 187, 249, 250, 248, 243, 244, 245, 246, 192, 195, 193, 194, 169, 168, 190, 191, 247, 267, 266, 264, 265, 262, 260, 254, 251, 252, 185, 184, 255, 183, 182, 181, 180, 179, 117, 253, 259, 261, 263, 258, 257, 256, 269, 268, 270, 238, 242, 241, 239, 240, 236, 237, 235, 272, 271, 273, 234, 233, 197, 196, 166, 167, 294, 293, 296, 295, 297, 0, 3, 2, 1, 5, 4]</t>
+          <t>[117, 119, 118, 116, 114, 115, 113, 54, 55, 53, 52, 51, 50, 49, 48, 47, 46, 43, 44, 45, 40, 42, 39, 41, 36, 37, 35, 34, 31, 30, 29, 33, 32, 65, 62, 63, 104, 64, 61, 106, 105, 107, 108, 109, 60, 58, 59, 57, 56, 38, 111, 110, 112, 122, 126, 125, 124, 123, 120, 121, 179, 180, 181, 182, 183, 184, 185, 255, 253, 259, 260, 254, 251, 252, 187, 249, 250, 248, 243, 244, 245, 246, 192, 195, 193, 194, 169, 168, 173, 171, 170, 172, 178, 188, 186, 177, 175, 174, 176, 127, 190, 191, 189, 247, 267, 266, 264, 265, 262, 263, 261, 258, 257, 256, 269, 268, 270, 238, 242, 241, 239, 240, 236, 237, 235, 272, 271, 273, 234, 233, 197, 196, 166, 167, 164, 165, 200, 198, 199, 227, 202, 228, 230, 229, 232, 231, 276, 275, 274, 278, 277, 280, 281, 282, 279, 283, 284, 285, 218, 220, 221, 208, 209, 207, 206, 203, 204, 205, 298, 226, 225, 224, 222, 223, 219, 210, 159, 160, 139, 138, 96, 95, 94, 97, 82, 83, 98, 99, 100, 101, 81, 78, 80, 19, 17, 18, 16, 14, 15, 84, 85, 93, 86, 90, 88, 89, 87, 13, 12, 11, 10, 9, 8, 7, 6, 91, 92, 143, 145, 144, 147, 146, 148, 149, 150, 151, 152, 153, 154, 155, 213, 214, 292, 291, 289, 290, 288, 287, 286, 216, 215, 217, 211, 212, 158, 157, 156, 142, 141, 140, 137, 136, 134, 135, 132, 131, 128, 103, 129, 130, 133, 162, 161, 163, 201, 102, 77, 75, 79, 74, 76, 71, 72, 73, 70, 28, 27, 26, 25, 24, 23, 22, 20, 21, 68, 69, 66, 67, 4, 5, 1, 2, 3, 0, 297, 295, 296, 293, 294]</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -852,17 +852,17 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>53631</v>
+        <v>51861</v>
       </c>
       <c r="E13" t="n">
-        <v>11.28841484924571</v>
+        <v>7.615529870722749</v>
       </c>
       <c r="F13" t="n">
-        <v>1.781154155731201</v>
+        <v>1.647085189819336</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>[63, 104, 67, 66, 68, 69, 167, 200, 165, 164, 130, 129, 103, 128, 131, 102, 77, 75, 79, 74, 76, 71, 72, 73, 70, 28, 27, 26, 25, 24, 23, 21, 22, 20, 17, 19, 80, 78, 81, 101, 100, 99, 98, 83, 82, 97, 94, 95, 96, 138, 140, 141, 142, 156, 214, 213, 155, 154, 153, 152, 146, 147, 144, 145, 143, 92, 91, 7, 8, 9, 10, 11, 12, 14, 16, 18, 15, 84, 86, 93, 85, 90, 88, 89, 87, 13, 6, 4, 5, 1, 2, 3, 0, 148, 149, 150, 151, 297, 295, 296, 293, 294, 292, 291, 289, 290, 288, 287, 286, 216, 215, 217, 211, 212, 157, 158, 139, 160, 159, 210, 209, 207, 219, 208, 221, 220, 218, 285, 284, 283, 279, 282, 281, 280, 277, 278, 274, 275, 276, 231, 232, 229, 230, 228, 298, 226, 224, 225, 222, 223, 206, 203, 204, 205, 137, 136, 135, 134, 132, 133, 162, 161, 163, 201, 202, 227, 199, 198, 234, 273, 272, 271, 238, 270, 268, 269, 242, 246, 245, 244, 250, 243, 248, 247, 267, 266, 264, 263, 261, 259, 258, 257, 256, 253, 255, 184, 183, 182, 181, 180, 179, 185, 252, 251, 254, 260, 262, 265, 249, 187, 189, 191, 190, 172, 171, 170, 178, 188, 186, 177, 175, 174, 176, 126, 122, 125, 123, 124, 120, 121, 119, 118, 116, 114, 117, 115, 113, 54, 55, 53, 52, 51, 50, 49, 48, 47, 46, 43, 45, 44, 42, 40, 39, 41, 36, 37, 35, 34, 31, 30, 29, 33, 32, 65, 62, 61, 64, 106, 105, 107, 108, 109, 60, 58, 59, 38, 56, 57, 111, 112, 110, 127, 173, 168, 169, 194, 193, 192, 195, 241, 239, 240, 236, 237, 235, 233, 197, 196, 166]</t>
+          <t>[93, 85, 89, 87, 13, 12, 11, 10, 9, 8, 7, 6, 91, 4, 5, 1, 2, 3, 0, 148, 146, 147, 144, 145, 143, 92, 142, 156, 214, 213, 155, 154, 153, 152, 151, 150, 149, 297, 295, 296, 293, 294, 292, 291, 289, 290, 288, 287, 286, 216, 215, 212, 211, 217, 220, 221, 208, 210, 209, 207, 219, 218, 285, 284, 283, 222, 223, 206, 203, 204, 205, 298, 226, 225, 224, 279, 282, 281, 280, 277, 278, 274, 275, 276, 231, 232, 229, 230, 228, 202, 227, 199, 198, 201, 163, 161, 162, 133, 136, 137, 135, 134, 132, 131, 128, 103, 129, 130, 164, 165, 200, 167, 166, 196, 197, 233, 234, 273, 272, 271, 237, 235, 236, 240, 239, 238, 270, 268, 269, 242, 241, 195, 192, 193, 194, 169, 127, 173, 168, 190, 191, 189, 187, 249, 250, 244, 246, 245, 243, 248, 247, 267, 266, 264, 265, 251, 254, 260, 262, 263, 261, 259, 253, 258, 257, 256, 255, 184, 183, 182, 181, 180, 179, 185, 252, 177, 186, 188, 178, 175, 174, 176, 170, 172, 171, 126, 122, 125, 123, 124, 120, 121, 119, 118, 117, 114, 116, 113, 115, 54, 55, 53, 52, 51, 50, 49, 48, 47, 46, 43, 45, 44, 40, 42, 39, 41, 36, 37, 35, 38, 56, 59, 58, 109, 60, 57, 111, 112, 110, 108, 107, 105, 106, 61, 64, 104, 63, 62, 34, 31, 30, 29, 33, 32, 65, 67, 66, 69, 68, 70, 73, 72, 71, 76, 74, 79, 75, 77, 102, 101, 81, 78, 21, 28, 27, 26, 25, 24, 23, 22, 20, 17, 16, 14, 15, 18, 19, 80, 83, 98, 99, 100, 97, 82, 84, 86, 94, 95, 96, 138, 139, 160, 159, 158, 157, 141, 140, 88, 90]</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -886,17 +886,17 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>58247</v>
+        <v>59709</v>
       </c>
       <c r="E14" t="n">
-        <v>20.86696686103214</v>
+        <v>23.90072835176693</v>
       </c>
       <c r="F14" t="n">
-        <v>60.00001621246338</v>
+        <v>60.00000715255737</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>[156, 138, 95, 94, 97, 100, 99, 98, 83, 82, 101, 81, 78, 19, 17, 18, 16, 14, 15, 84, 86, 93, 85, 90, 88, 89, 87, 13, 12, 11, 10, 9, 8, 7, 6, 91, 92, 143, 145, 144, 147, 146, 148, 149, 150, 151, 152, 153, 154, 155, 213, 214, 292, 291, 289, 290, 288, 287, 286, 216, 217, 215, 212, 211, 221, 219, 207, 223, 206, 203, 204, 205, 298, 226, 224, 279, 283, 281, 280, 282, 277, 278, 274, 276, 275, 232, 231, 198, 199, 227, 228, 230, 229, 202, 201, 163, 162, 161, 137, 136, 133, 134, 135, 132, 131, 128, 103, 129, 130, 164, 165, 200, 167, 166, 196, 197, 233, 234, 273, 235, 236, 239, 240, 237, 272, 271, 270, 269, 268, 238, 242, 241, 192, 195, 191, 193, 194, 169, 168, 190, 189, 188, 178, 170, 173, 171, 176, 126, 125, 122, 112, 110, 57, 111, 59, 38, 44, 45, 40, 42, 41, 39, 37, 36, 35, 34, 31, 30, 29, 33, 32, 65, 104, 63, 62, 61, 64, 106, 105, 107, 109, 60, 58, 56, 43, 46, 47, 48, 49, 50, 51, 52, 53, 55, 54, 115, 113, 116, 114, 118, 117, 119, 121, 120, 123, 124, 174, 175, 177, 186, 187, 249, 250, 244, 246, 245, 243, 247, 248, 267, 266, 264, 265, 263, 261, 262, 260, 253, 185, 179, 180, 181, 182, 183, 184, 255, 256, 257, 258, 259, 254, 251, 252, 172, 127, 108, 67, 66, 69, 68, 70, 73, 72, 71, 74, 76, 77, 75, 79, 80, 21, 20, 22, 23, 24, 25, 26, 27, 28, 102, 96, 139, 160, 159, 210, 209, 222, 225, 284, 285, 218, 220, 208, 158, 157, 140, 141, 142, 4, 5, 1, 2, 3, 0, 297, 295, 296, 293, 294]</t>
+          <t>[74, 26, 25, 24, 23, 22, 20, 17, 19, 18, 16, 14, 15, 84, 86, 94, 95, 96, 97, 82, 83, 98, 99, 100, 101, 81, 80, 78, 21, 79, 75, 77, 76, 71, 72, 27, 28, 73, 70, 68, 69, 66, 67, 65, 62, 63, 104, 106, 64, 61, 105, 108, 107, 109, 60, 58, 59, 57, 56, 38, 42, 40, 39, 41, 36, 37, 35, 34, 31, 30, 29, 33, 32, 44, 45, 43, 46, 47, 48, 49, 50, 51, 52, 53, 55, 54, 115, 113, 114, 116, 118, 117, 121, 120, 124, 123, 125, 112, 111, 110, 122, 126, 127, 173, 172, 171, 170, 178, 188, 186, 177, 174, 176, 175, 189, 187, 249, 247, 267, 243, 244, 245, 246, 192, 195, 193, 194, 169, 168, 190, 191, 250, 248, 266, 264, 265, 262, 260, 254, 251, 252, 185, 255, 184, 183, 182, 181, 180, 179, 119, 253, 259, 258, 256, 257, 261, 263, 242, 269, 268, 270, 238, 241, 239, 240, 236, 235, 237, 271, 272, 273, 234, 233, 197, 196, 166, 167, 164, 165, 200, 199, 198, 227, 202, 228, 230, 229, 232, 231, 276, 274, 278, 275, 277, 280, 281, 282, 279, 283, 284, 285, 218, 220, 221, 208, 219, 207, 206, 203, 204, 205, 298, 226, 224, 225, 222, 223, 209, 210, 159, 160, 139, 138, 93, 85, 90, 88, 87, 89, 13, 12, 11, 10, 9, 8, 7, 6, 91, 92, 143, 145, 144, 147, 146, 148, 149, 150, 151, 152, 153, 154, 155, 213, 214, 292, 291, 289, 290, 288, 287, 286, 216, 215, 217, 211, 212, 158, 157, 156, 142, 141, 140, 136, 133, 134, 132, 102, 131, 128, 103, 129, 130, 162, 163, 201, 161, 137, 135, 4, 5, 1, 2, 3, 0, 297, 295, 296, 293, 294]</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -920,17 +920,17 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>48985</v>
+        <v>49181</v>
       </c>
       <c r="E15" t="n">
-        <v>1.647610549687701</v>
+        <v>2.054325496461995</v>
       </c>
       <c r="F15" t="n">
-        <v>1.033608913421631</v>
+        <v>1.124595880508423</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>[187, 186, 177, 175, 174, 176, 171, 126, 125, 124, 120, 121, 123, 122, 112, 110, 111, 57, 59, 58, 60, 109, 105, 107, 108, 127, 173, 172, 170, 178, 188, 189, 190, 168, 169, 194, 193, 191, 192, 195, 241, 242, 269, 268, 270, 238, 239, 240, 236, 235, 237, 271, 272, 273, 234, 233, 197, 196, 166, 167, 164, 165, 200, 198, 199, 227, 229, 232, 231, 276, 275, 274, 278, 277, 280, 281, 230, 228, 202, 201, 163, 162, 161, 137, 135, 134, 136, 133, 130, 129, 103, 128, 131, 132, 102, 77, 75, 79, 76, 74, 21, 78, 80, 81, 101, 100, 99, 98, 83, 82, 97, 94, 95, 96, 138, 140, 141, 142, 156, 157, 158, 139, 160, 159, 210, 209, 207, 223, 222, 206, 203, 204, 205, 298, 226, 225, 224, 282, 279, 283, 284, 285, 218, 220, 219, 208, 221, 211, 212, 217, 215, 216, 286, 287, 288, 290, 289, 291, 292, 294, 293, 296, 295, 297, 214, 213, 155, 154, 153, 152, 151, 150, 149, 148, 146, 147, 144, 145, 143, 92, 91, 0, 3, 2, 1, 5, 4, 6, 7, 8, 9, 10, 11, 12, 13, 87, 89, 88, 90, 85, 93, 86, 84, 15, 14, 16, 18, 19, 17, 20, 22, 23, 24, 25, 26, 27, 28, 71, 72, 73, 70, 68, 69, 66, 67, 104, 63, 64, 106, 61, 62, 65, 32, 33, 29, 30, 31, 34, 35, 37, 36, 41, 39, 40, 42, 38, 56, 43, 44, 45, 46, 47, 48, 49, 50, 51, 52, 53, 55, 54, 115, 113, 116, 114, 117, 118, 119, 179, 180, 181, 182, 183, 184, 185, 255, 253, 259, 258, 256, 257, 261, 263, 262, 260, 254, 252, 251, 265, 264, 266, 267, 247, 248, 243, 245, 246, 244, 250, 249]</t>
+          <t>[280, 277, 278, 274, 275, 276, 231, 232, 229, 227, 202, 228, 230, 281, 224, 225, 226, 298, 205, 204, 203, 206, 222, 223, 219, 207, 209, 210, 159, 158, 157, 156, 142, 141, 140, 160, 139, 138, 96, 95, 94, 97, 82, 83, 98, 99, 100, 101, 81, 80, 78, 79, 75, 77, 102, 131, 132, 134, 135, 137, 136, 133, 162, 161, 163, 201, 199, 198, 200, 165, 164, 130, 128, 103, 129, 167, 166, 196, 197, 233, 234, 273, 272, 271, 237, 235, 236, 240, 239, 238, 270, 268, 269, 242, 241, 195, 192, 191, 190, 193, 194, 169, 168, 173, 127, 108, 107, 105, 106, 64, 61, 109, 60, 58, 38, 56, 59, 57, 111, 110, 112, 122, 123, 117, 121, 120, 124, 125, 126, 176, 174, 175, 177, 186, 188, 178, 170, 171, 172, 189, 187, 249, 250, 244, 246, 245, 243, 248, 247, 267, 266, 264, 265, 262, 263, 261, 258, 257, 256, 253, 259, 260, 254, 251, 252, 185, 255, 184, 183, 182, 181, 180, 179, 119, 118, 116, 114, 113, 115, 54, 55, 53, 52, 51, 50, 49, 48, 47, 46, 43, 45, 44, 42, 40, 39, 41, 36, 37, 35, 34, 31, 30, 29, 33, 32, 65, 62, 63, 104, 67, 66, 69, 68, 70, 73, 72, 28, 27, 26, 71, 76, 74, 25, 24, 23, 21, 22, 20, 17, 19, 18, 16, 14, 15, 84, 86, 93, 85, 89, 90, 88, 87, 13, 12, 11, 10, 9, 8, 7, 6, 4, 5, 1, 2, 3, 0, 91, 92, 143, 145, 144, 147, 146, 148, 149, 150, 151, 152, 153, 154, 155, 213, 214, 297, 295, 296, 293, 294, 292, 291, 289, 290, 288, 287, 286, 216, 215, 217, 212, 211, 208, 221, 220, 218, 285, 284, 283, 279, 282]</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -960,7 +960,7 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1.045958757400513</v>
+        <v>1.009711265563965</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
@@ -984,17 +984,17 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>53175</v>
+        <v>52887</v>
       </c>
       <c r="E17" t="n">
-        <v>26.51978395869519</v>
+        <v>25.83454281567489</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0112910270690918</v>
+        <v>0.009432077407836914</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>[39, 44, 47, 49, 54, 55, 58, 104, 56, 53, 50, 46, 43, 40, 42, 45, 51, 52, 57, 61, 62, 69, 73, 74, 80, 68, 72, 75, 79, 78, 76, 71, 67, 66, 70, 77, 81, 82, 83, 84, 85, 88, 89, 98, 97, 92, 91, 90, 95, 96, 100, 101, 63, 48, 315, 316, 103, 32, 27, 22, 19, 102, 20, 21, 28, 29, 30, 31, 14, 10, 9, 6, 5, 1, 0, 2, 7, 8, 16, 17, 24, 25, 15, 18, 23, 26, 11, 35, 36, 41, 38, 37, 144, 149, 152, 154, 159, 160, 163, 209, 161, 158, 155, 151, 148, 145, 147, 150, 156, 157, 162, 166, 167, 174, 178, 179, 185, 173, 177, 180, 184, 183, 181, 176, 172, 171, 175, 182, 186, 187, 188, 189, 86, 87, 195, 196, 200, 201, 205, 206, 99, 94, 93, 197, 202, 203, 194, 193, 190, 168, 64, 65, 60, 59, 153, 208, 137, 132, 127, 124, 207, 125, 126, 133, 134, 135, 136, 33, 34, 13, 12, 115, 114, 111, 110, 106, 105, 3, 4, 119, 116, 123, 128, 131, 130, 129, 122, 120, 121, 113, 112, 107, 109, 108, 215, 216, 219, 220, 117, 118, 224, 312, 230, 231, 238, 239, 240, 241, 237, 232, 229, 228, 233, 236, 235, 234, 227, 225, 226, 218, 217, 212, 211, 210, 221, 242, 245, 246, 251, 252, 255, 261, 262, 267, 266, 263, 260, 256, 253, 250, 313, 249, 254, 257, 259, 264, 265, 268, 314, 271, 272, 279, 283, 284, 290, 278, 282, 285, 289, 288, 286, 281, 277, 276, 280, 287, 291, 292, 293, 294, 191, 192, 300, 301, 305, 306, 310, 311, 204, 199, 198, 302, 307, 308, 299, 298, 295, 273, 169, 170, 165, 164, 258, 142, 143, 139, 138, 141, 140, 146, 248, 247, 244, 243, 223, 222, 214, 213, 317, 269, 270, 274, 275, 296, 297, 303, 304, 309]</t>
+          <t>[291, 287, 292, 293, 288, 286, 281, 277, 276, 280, 169, 170, 165, 164, 268, 265, 264, 259, 257, 254, 249, 258, 142, 143, 139, 138, 241, 240, 239, 238, 231, 230, 312, 229, 232, 237, 242, 236, 233, 228, 225, 227, 234, 235, 226, 218, 217, 212, 211, 210, 215, 216, 219, 220, 117, 118, 224, 221, 108, 109, 113, 112, 107, 106, 105, 110, 111, 114, 115, 12, 13, 119, 207, 125, 126, 133, 134, 135, 136, 132, 127, 124, 123, 128, 131, 130, 129, 122, 120, 121, 116, 137, 140, 141, 146, 147, 150, 156, 157, 162, 161, 158, 155, 151, 148, 145, 208, 144, 149, 152, 154, 159, 160, 163, 209, 166, 167, 174, 178, 179, 185, 173, 177, 180, 184, 183, 181, 176, 172, 171, 175, 182, 186, 187, 188, 189, 86, 87, 195, 196, 200, 201, 205, 206, 99, 94, 93, 197, 202, 203, 194, 193, 190, 168, 64, 65, 60, 59, 153, 37, 38, 34, 33, 36, 35, 25, 24, 17, 15, 16, 18, 23, 26, 27, 22, 19, 102, 20, 21, 28, 29, 30, 31, 32, 103, 39, 44, 47, 49, 54, 55, 58, 104, 56, 53, 50, 46, 43, 40, 42, 45, 51, 52, 57, 61, 62, 69, 73, 74, 80, 68, 72, 75, 79, 78, 76, 71, 67, 66, 70, 77, 81, 82, 83, 84, 85, 88, 89, 98, 97, 92, 91, 90, 95, 96, 100, 101, 63, 48, 315, 316, 41, 11, 14, 10, 9, 6, 5, 1, 0, 2, 7, 8, 4, 3, 313, 253, 256, 260, 263, 266, 267, 262, 261, 255, 252, 250, 251, 246, 245, 244, 243, 247, 248, 317, 269, 270, 274, 275, 296, 297, 303, 304, 309, 308, 307, 302, 301, 300, 198, 199, 204, 310, 311, 306, 305, 192, 191, 294, 295, 289, 285, 282, 278, 283, 284, 290, 279, 272, 271, 314, 273, 298, 299, 223, 222, 214, 213]</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1018,17 +1018,17 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>46227</v>
+        <v>44111</v>
       </c>
       <c r="E18" t="n">
-        <v>9.988341383330559</v>
+        <v>4.953722429750886</v>
       </c>
       <c r="F18" t="n">
-        <v>1.874983072280884</v>
+        <v>1.66391396522522</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>[187, 186, 182, 175, 172, 171, 188, 189, 86, 87, 93, 94, 99, 206, 205, 201, 200, 196, 195, 197, 202, 203, 194, 193, 185, 179, 178, 174, 173, 177, 180, 184, 190, 183, 181, 176, 168, 209, 166, 167, 165, 164, 268, 265, 264, 259, 257, 254, 256, 253, 250, 251, 252, 255, 261, 262, 267, 260, 263, 266, 314, 271, 272, 279, 278, 283, 284, 290, 289, 285, 282, 273, 169, 170, 191, 192, 300, 301, 198, 199, 204, 311, 310, 306, 305, 302, 294, 292, 291, 287, 280, 277, 276, 281, 286, 288, 293, 295, 298, 299, 307, 308, 309, 304, 303, 297, 296, 275, 274, 270, 269, 317, 247, 248, 245, 246, 244, 243, 223, 222, 213, 214, 218, 217, 212, 210, 211, 215, 216, 219, 220, 117, 118, 108, 109, 113, 112, 107, 116, 207, 133, 126, 125, 119, 115, 114, 111, 110, 106, 105, 3, 4, 12, 13, 16, 15, 17, 24, 25, 26, 23, 18, 11, 8, 7, 2, 0, 1, 5, 6, 9, 10, 14, 20, 21, 28, 102, 19, 22, 27, 29, 30, 31, 32, 103, 35, 36, 41, 40, 42, 45, 51, 52, 57, 62, 61, 56, 53, 50, 46, 43, 55, 54, 49, 47, 44, 39, 48, 315, 316, 58, 104, 63, 66, 67, 70, 71, 76, 78, 83, 77, 81, 82, 84, 90, 91, 95, 96, 100, 101, 92, 97, 98, 89, 88, 85, 79, 75, 72, 80, 74, 73, 68, 69, 65, 64, 60, 59, 163, 160, 159, 154, 152, 149, 153, 144, 37, 38, 34, 33, 136, 135, 134, 132, 127, 124, 131, 128, 123, 120, 121, 122, 129, 130, 141, 140, 137, 208, 145, 148, 151, 155, 158, 161, 162, 157, 156, 150, 147, 146, 143, 142, 139, 138, 241, 240, 239, 238, 231, 230, 312, 224, 221, 229, 232, 237, 236, 233, 228, 225, 226, 227, 234, 235, 242, 313, 249, 258]</t>
+          <t>[168, 177, 180, 184, 185, 179, 178, 173, 174, 167, 166, 209, 163, 59, 60, 62, 61, 69, 68, 73, 74, 80, 79, 75, 72, 71, 76, 78, 83, 85, 88, 89, 98, 97, 92, 101, 100, 96, 95, 91, 90, 84, 82, 81, 77, 70, 67, 66, 63, 104, 58, 316, 315, 48, 39, 44, 47, 49, 54, 55, 43, 46, 50, 53, 56, 57, 52, 51, 45, 42, 40, 41, 36, 35, 25, 24, 17, 15, 26, 23, 18, 11, 19, 22, 27, 32, 103, 31, 30, 29, 28, 21, 20, 102, 14, 10, 9, 6, 5, 1, 0, 2, 7, 8, 16, 13, 12, 4, 3, 105, 106, 110, 111, 114, 115, 119, 207, 125, 126, 133, 33, 34, 38, 37, 144, 153, 160, 159, 154, 152, 149, 208, 145, 148, 151, 155, 158, 161, 162, 157, 156, 150, 147, 146, 141, 140, 137, 136, 135, 134, 132, 127, 124, 128, 131, 130, 129, 122, 121, 120, 123, 116, 107, 112, 113, 109, 108, 216, 215, 211, 210, 212, 219, 220, 117, 118, 224, 312, 230, 231, 238, 239, 240, 241, 138, 139, 143, 142, 258, 265, 264, 259, 257, 254, 249, 313, 250, 253, 256, 260, 263, 266, 267, 262, 261, 255, 252, 251, 246, 245, 235, 234, 227, 226, 225, 228, 233, 236, 242, 237, 232, 229, 221, 217, 218, 214, 213, 222, 223, 243, 244, 247, 248, 317, 269, 270, 274, 275, 296, 297, 303, 304, 309, 308, 307, 302, 299, 298, 295, 293, 294, 292, 291, 287, 280, 277, 276, 273, 281, 286, 288, 282, 285, 289, 290, 284, 283, 278, 279, 272, 271, 314, 268, 164, 165, 169, 170, 191, 192, 300, 301, 305, 306, 310, 311, 204, 198, 199, 203, 202, 194, 193, 197, 190, 188, 183, 181, 176, 171, 172, 175, 182, 186, 187, 189, 195, 196, 200, 201, 205, 206, 99, 94, 93, 87, 86, 65, 64]</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1052,17 +1052,17 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>53025</v>
+        <v>51025</v>
       </c>
       <c r="E19" t="n">
-        <v>26.16288753003878</v>
+        <v>21.40426848128673</v>
       </c>
       <c r="F19" t="n">
-        <v>60.00000691413879</v>
+        <v>60.00000882148743</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>[54, 49, 47, 44, 39, 48, 55, 58, 104, 56, 53, 50, 46, 43, 40, 42, 45, 51, 52, 57, 61, 62, 69, 68, 74, 80, 73, 79, 75, 72, 78, 76, 71, 67, 66, 70, 77, 81, 82, 84, 83, 85, 88, 89, 98, 97, 92, 91, 90, 95, 96, 100, 101, 63, 316, 315, 103, 32, 27, 22, 19, 102, 20, 21, 28, 29, 30, 31, 14, 10, 9, 6, 5, 1, 0, 2, 7, 8, 16, 17, 24, 25, 15, 18, 11, 26, 23, 35, 36, 41, 38, 37, 144, 149, 152, 154, 159, 160, 163, 209, 161, 158, 155, 151, 148, 145, 147, 150, 156, 157, 162, 166, 167, 174, 178, 179, 185, 173, 177, 180, 184, 183, 181, 176, 172, 171, 175, 182, 186, 187, 188, 189, 86, 87, 195, 196, 200, 201, 205, 206, 99, 94, 93, 197, 202, 203, 194, 193, 190, 168, 64, 65, 60, 59, 153, 208, 137, 132, 127, 124, 207, 125, 126, 133, 134, 135, 136, 33, 34, 13, 12, 115, 114, 111, 110, 106, 105, 3, 4, 119, 116, 123, 128, 131, 130, 129, 122, 120, 121, 113, 112, 107, 109, 108, 215, 216, 219, 220, 117, 118, 224, 312, 230, 231, 238, 239, 240, 241, 237, 232, 229, 228, 233, 236, 235, 234, 227, 225, 226, 218, 217, 212, 211, 210, 221, 242, 245, 246, 251, 252, 255, 261, 262, 267, 266, 263, 260, 256, 253, 250, 313, 249, 254, 257, 259, 264, 265, 268, 314, 271, 272, 279, 283, 284, 290, 278, 282, 285, 289, 286, 288, 281, 277, 276, 280, 287, 291, 292, 293, 294, 191, 192, 300, 301, 305, 306, 310, 311, 204, 199, 198, 302, 307, 308, 299, 298, 295, 273, 169, 170, 165, 164, 258, 142, 143, 139, 138, 141, 140, 146, 248, 247, 244, 243, 223, 222, 214, 213, 317, 269, 270, 274, 275, 296, 297, 303, 304, 309]</t>
+          <t>[78, 76, 71, 81, 82, 84, 83, 77, 70, 67, 66, 63, 72, 75, 79, 80, 74, 73, 68, 69, 62, 61, 57, 52, 51, 42, 46, 43, 54, 55, 58, 104, 316, 315, 48, 39, 44, 47, 49, 56, 53, 50, 45, 41, 40, 103, 35, 36, 25, 24, 17, 15, 26, 32, 23, 18, 11, 102, 20, 21, 28, 31, 30, 29, 27, 22, 19, 14, 10, 9, 6, 5, 1, 0, 2, 7, 8, 16, 13, 12, 115, 110, 106, 105, 3, 4, 111, 114, 119, 126, 133, 132, 127, 124, 207, 125, 136, 135, 134, 137, 131, 128, 129, 122, 120, 123, 116, 107, 112, 113, 121, 130, 140, 141, 146, 145, 147, 150, 156, 157, 162, 161, 158, 155, 151, 148, 149, 144, 153, 154, 152, 159, 160, 163, 209, 166, 167, 174, 178, 179, 185, 184, 177, 173, 180, 181, 176, 168, 171, 172, 175, 182, 189, 187, 188, 186, 86, 87, 93, 94, 205, 206, 99, 201, 200, 196, 195, 197, 202, 203, 194, 193, 190, 183, 64, 65, 60, 59, 38, 37, 34, 33, 208, 143, 142, 139, 138, 238, 230, 224, 312, 221, 229, 237, 232, 242, 236, 233, 228, 225, 227, 234, 235, 226, 218, 217, 212, 210, 211, 216, 215, 108, 109, 219, 220, 117, 118, 231, 239, 240, 241, 249, 258, 259, 264, 265, 314, 266, 263, 256, 257, 260, 253, 250, 251, 252, 255, 261, 262, 267, 271, 272, 279, 290, 284, 283, 278, 282, 285, 289, 288, 286, 281, 273, 276, 277, 280, 287, 291, 292, 294, 191, 192, 300, 301, 198, 199, 204, 305, 306, 311, 310, 302, 307, 308, 299, 298, 295, 293, 169, 170, 165, 164, 268, 254, 313, 245, 246, 214, 213, 222, 223, 243, 244, 247, 248, 317, 269, 270, 274, 275, 296, 297, 303, 304, 309, 89, 88, 92, 90, 91, 95, 96, 100, 101, 97, 98, 85]</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1086,17 +1086,17 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>42969</v>
+        <v>42882</v>
       </c>
       <c r="E20" t="n">
-        <v>2.236550952913464</v>
+        <v>2.029551024292751</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9672880172729492</v>
+        <v>1.054385900497437</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>[188, 190, 184, 180, 177, 185, 179, 178, 173, 174, 167, 166, 168, 209, 163, 160, 159, 154, 152, 149, 153, 144, 208, 148, 151, 155, 158, 161, 162, 157, 156, 150, 147, 145, 146, 141, 140, 137, 132, 127, 124, 123, 128, 131, 130, 129, 122, 121, 120, 116, 119, 207, 125, 126, 133, 134, 135, 136, 33, 34, 37, 38, 59, 60, 64, 65, 69, 68, 73, 74, 80, 88, 89, 98, 97, 92, 101, 100, 96, 95, 91, 90, 84, 82, 81, 77, 70, 67, 66, 71, 76, 78, 83, 85, 79, 75, 72, 63, 61, 62, 57, 52, 51, 45, 42, 41, 40, 43, 46, 50, 53, 56, 104, 58, 55, 54, 49, 47, 44, 48, 316, 315, 39, 103, 35, 36, 25, 24, 17, 16, 15, 18, 23, 26, 32, 27, 22, 19, 29, 30, 31, 28, 21, 20, 102, 11, 14, 10, 9, 6, 5, 1, 0, 2, 7, 8, 13, 12, 115, 114, 111, 110, 4, 3, 106, 105, 107, 112, 113, 109, 108, 210, 211, 215, 216, 219, 220, 117, 118, 224, 312, 230, 231, 238, 239, 240, 241, 138, 139, 143, 142, 249, 313, 253, 256, 260, 263, 266, 267, 262, 261, 255, 252, 250, 251, 246, 245, 242, 237, 232, 229, 228, 233, 236, 235, 234, 227, 226, 225, 221, 212, 217, 218, 214, 213, 222, 223, 243, 244, 247, 248, 317, 269, 270, 274, 275, 296, 297, 303, 304, 309, 308, 307, 302, 298, 299, 290, 284, 283, 278, 279, 272, 271, 314, 265, 264, 259, 257, 254, 258, 268, 164, 165, 170, 169, 280, 277, 276, 273, 282, 285, 289, 295, 288, 286, 281, 287, 291, 292, 293, 294, 191, 192, 199, 198, 300, 301, 305, 306, 310, 311, 204, 203, 202, 194, 193, 197, 195, 196, 200, 201, 205, 206, 99, 94, 93, 87, 86, 189, 187, 186, 182, 175, 172, 171, 176, 181, 183]</t>
+          <t>[271, 272, 279, 278, 283, 284, 290, 282, 285, 289, 295, 288, 286, 281, 276, 277, 280, 287, 291, 292, 293, 294, 191, 192, 198, 199, 204, 311, 310, 306, 305, 301, 300, 302, 298, 299, 307, 308, 309, 304, 303, 297, 296, 275, 274, 270, 269, 317, 248, 247, 244, 243, 223, 222, 213, 214, 218, 217, 212, 210, 211, 215, 216, 108, 109, 118, 117, 219, 220, 224, 312, 230, 231, 238, 239, 240, 241, 138, 139, 141, 140, 137, 132, 127, 124, 116, 123, 128, 131, 130, 129, 122, 120, 121, 113, 112, 107, 105, 106, 3, 4, 110, 111, 114, 115, 12, 13, 119, 207, 125, 126, 133, 134, 135, 136, 33, 34, 37, 38, 36, 35, 25, 24, 17, 15, 16, 8, 7, 2, 0, 1, 5, 6, 9, 10, 14, 102, 20, 21, 28, 31, 30, 29, 27, 22, 19, 11, 18, 23, 26, 32, 103, 39, 315, 316, 48, 44, 47, 49, 54, 55, 58, 104, 56, 53, 50, 46, 43, 40, 41, 42, 45, 51, 52, 57, 62, 61, 63, 66, 67, 70, 77, 81, 82, 83, 84, 90, 91, 95, 96, 100, 101, 92, 97, 98, 89, 88, 85, 78, 76, 71, 72, 75, 79, 80, 74, 73, 68, 69, 86, 87, 195, 93, 94, 99, 206, 205, 201, 200, 196, 197, 202, 203, 194, 193, 185, 179, 178, 173, 174, 167, 166, 168, 177, 180, 184, 190, 183, 181, 176, 188, 189, 187, 186, 182, 175, 172, 171, 64, 65, 60, 59, 163, 209, 160, 159, 154, 152, 149, 153, 144, 208, 148, 151, 155, 158, 161, 162, 157, 156, 150, 147, 145, 146, 143, 142, 249, 258, 254, 257, 259, 264, 265, 268, 164, 165, 170, 169, 273, 314, 266, 263, 260, 256, 253, 313, 242, 237, 232, 229, 221, 228, 233, 236, 227, 225, 226, 234, 235, 245, 246, 251, 250, 252, 255, 261, 262, 267]</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1126,7 +1126,7 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>1.141464948654175</v>
+        <v>1.132623195648193</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
@@ -1150,17 +1150,17 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>19598</v>
+        <v>19718</v>
       </c>
       <c r="E22" t="n">
-        <v>28.25076892873503</v>
+        <v>29.03605784961717</v>
       </c>
       <c r="F22" t="n">
-        <v>0.01464605331420898</v>
+        <v>0.01476001739501953</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>[85, 182, 371, 282, 45, 137, 176, 143, 197, 207, 77, 321, 350, 373, 291, 324, 301, 149, 323, 32, 193, 104, 354, 247, 317, 169, 217, 26, 125, 11, 42, 375, 130, 320, 62, 296, 219, 230, 290, 369, 142, 98, 385, 269, 81, 325, 105, 273, 367, 165, 19, 214, 226, 65, 21, 256, 366, 357, 91, 156, 338, 272, 55, 274, 202, 0, 200, 8, 3, 168, 44, 255, 160, 33, 285, 346, 177, 308, 237, 50, 164, 231, 89, 120, 374, 78, 348, 312, 161, 224, 260, 314, 286, 391, 113, 342, 40, 70, 126, 152, 184, 87, 243, 251, 101, 382, 258, 228, 174, 144, 180, 43, 127, 7, 334, 90, 148, 337, 192, 398, 364, 17, 304, 232, 181, 216, 187, 139, 133, 171, 266, 363, 69, 80, 240, 93, 234, 332, 60, 302, 333, 309, 103, 110, 370, 146, 289, 351, 132, 248, 238, 37, 54, 167, 39, 108, 245, 263, 111, 379, 96, 218, 73, 393, 49, 82, 295, 151, 179, 203, 209, 318, 191, 155, 358, 158, 84, 307, 189, 52, 397, 94, 368, 196, 28, 24, 199, 330, 388, 355, 186, 311, 86, 277, 347, 399, 288, 53, 394, 233, 356, 210, 154, 235, 262, 283, 76, 198, 204, 66, 16, 185, 316, 267, 172, 12, 18, 383, 297, 41, 390, 117, 195, 106, 159, 63, 6, 340, 68, 75, 396, 275, 250, 310, 129, 157, 306, 343, 326, 292, 147, 109, 59, 344, 253, 328, 61, 141, 112, 349, 100, 395, 319, 67, 252, 47, 123, 205, 122, 46, 34, 270, 183, 35, 278, 153, 71, 322, 118, 378, 345, 229, 212, 341, 48, 57, 135, 5, 150, 287, 97, 239, 23, 305, 88, 163, 116, 281, 201, 284, 213, 215, 335, 128, 119, 246, 221, 114, 303, 38, 294, 25, 327, 166, 300, 14, 20, 29, 315, 136, 299, 384, 138, 1, 121, 208, 264, 381, 72, 211, 280, 4, 254, 265, 134, 92, 329, 386, 194, 313, 389, 115, 331, 131, 271, 10, 99, 362, 244, 223, 58, 31, 361, 22, 190, 298, 359, 353, 107, 95, 178, 102, 56, 336, 376, 79, 227, 225, 259, 279, 140, 13, 51, 352, 124, 241, 30, 261, 387, 222, 249, 268, 27, 377, 36, 74, 175, 220, 9, 188, 145, 372, 392, 360, 206, 2, 15, 170, 293, 276, 236, 257, 339, 242, 380, 83, 64, 365, 173, 162]</t>
+          <t>[368, 196, 94, 52, 397, 83, 64, 365, 358, 158, 84, 307, 189, 155, 391, 113, 314, 286, 224, 260, 101, 382, 231, 89, 120, 374, 78, 348, 312, 161, 258, 228, 174, 144, 180, 43, 127, 7, 334, 90, 148, 337, 192, 398, 364, 17, 304, 232, 181, 216, 187, 139, 133, 171, 266, 363, 69, 80, 240, 93, 234, 332, 60, 323, 32, 193, 104, 354, 247, 317, 169, 217, 26, 125, 11, 42, 375, 130, 320, 62, 296, 219, 230, 290, 369, 142, 98, 385, 269, 81, 325, 105, 273, 367, 165, 19, 214, 226, 65, 21, 256, 366, 357, 91, 156, 338, 272, 55, 274, 202, 0, 200, 8, 3, 168, 44, 255, 160, 33, 285, 346, 177, 308, 237, 50, 164, 243, 87, 251, 184, 126, 152, 70, 40, 342, 339, 242, 186, 311, 86, 277, 347, 399, 288, 53, 394, 233, 356, 210, 154, 235, 262, 283, 76, 198, 204, 66, 16, 185, 316, 267, 172, 12, 18, 383, 297, 41, 390, 117, 195, 106, 159, 63, 6, 340, 68, 75, 396, 275, 250, 310, 129, 157, 306, 343, 326, 292, 147, 109, 59, 344, 253, 328, 61, 141, 112, 349, 100, 395, 319, 67, 252, 47, 123, 205, 122, 46, 34, 270, 183, 35, 278, 153, 71, 322, 118, 378, 345, 229, 212, 341, 48, 57, 135, 5, 150, 287, 97, 239, 23, 305, 88, 163, 116, 281, 201, 284, 213, 215, 335, 128, 119, 246, 221, 114, 303, 38, 294, 25, 327, 166, 300, 14, 20, 29, 315, 136, 299, 384, 138, 1, 121, 208, 264, 381, 72, 211, 280, 4, 254, 265, 134, 92, 329, 386, 194, 313, 389, 115, 331, 131, 271, 10, 99, 362, 244, 223, 58, 31, 361, 22, 190, 298, 359, 353, 107, 95, 178, 102, 56, 336, 376, 79, 227, 225, 259, 279, 140, 13, 51, 352, 124, 241, 30, 261, 387, 222, 249, 268, 27, 377, 36, 74, 110, 103, 111, 263, 108, 39, 245, 167, 54, 238, 37, 248, 132, 351, 289, 146, 370, 333, 309, 302, 379, 96, 218, 73, 393, 49, 82, 295, 151, 179, 203, 209, 318, 191, 380, 173, 199, 330, 388, 355, 24, 28, 162, 257, 236, 170, 293, 149, 137, 45, 85, 182, 371, 282, 301, 324, 197, 207, 77, 143, 176, 291, 373, 350, 321, 276, 175, 220, 9, 188, 145, 372, 392, 360, 206, 2, 15]</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1184,17 +1184,17 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16581</v>
+        <v>16616</v>
       </c>
       <c r="E23" t="n">
-        <v>8.507296642889864</v>
+        <v>8.73633924481382</v>
       </c>
       <c r="F23" t="n">
-        <v>1.817516803741455</v>
+        <v>1.668654203414917</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>[125, 130, 375, 42, 11, 320, 62, 296, 219, 74, 36, 325, 105, 81, 269, 385, 110, 370, 146, 289, 132, 248, 236, 257, 33, 285, 346, 284, 213, 177, 308, 237, 50, 164, 231, 382, 101, 251, 243, 87, 184, 126, 152, 70, 40, 342, 113, 391, 286, 314, 260, 224, 161, 312, 348, 78, 89, 120, 374, 37, 238, 54, 167, 39, 245, 108, 263, 379, 96, 218, 73, 139, 133, 171, 266, 363, 69, 80, 240, 93, 234, 332, 60, 323, 32, 193, 104, 354, 247, 317, 170, 293, 149, 137, 176, 143, 197, 207, 77, 45, 182, 282, 371, 85, 301, 324, 291, 373, 350, 321, 276, 187, 216, 181, 232, 304, 17, 364, 398, 337, 192, 148, 90, 334, 7, 127, 43, 180, 144, 174, 228, 258, 209, 318, 82, 49, 393, 151, 295, 179, 203, 191, 155, 358, 84, 158, 307, 189, 52, 94, 368, 196, 28, 162, 24, 199, 330, 355, 388, 173, 397, 365, 64, 83, 380, 339, 242, 186, 311, 86, 277, 347, 288, 399, 53, 394, 233, 88, 305, 23, 239, 97, 287, 150, 5, 135, 57, 48, 341, 212, 229, 345, 378, 118, 278, 153, 35, 183, 270, 71, 322, 159, 63, 6, 46, 122, 34, 205, 47, 252, 67, 319, 395, 100, 123, 190, 22, 349, 112, 141, 61, 328, 253, 361, 31, 58, 223, 244, 362, 99, 10, 131, 331, 389, 115, 2, 206, 360, 15, 392, 372, 145, 9, 188, 265, 254, 4, 280, 225, 227, 79, 259, 279, 140, 13, 51, 352, 124, 241, 30, 261, 220, 175, 377, 27, 268, 249, 222, 387, 376, 336, 102, 95, 178, 56, 273, 367, 165, 19, 226, 214, 65, 21, 366, 256, 107, 353, 359, 298, 384, 138, 1, 121, 208, 264, 381, 72, 211, 134, 92, 329, 386, 194, 313, 271, 344, 59, 147, 109, 292, 326, 343, 157, 306, 129, 310, 250, 275, 396, 75, 68, 340, 315, 117, 195, 106, 390, 41, 297, 383, 18, 12, 172, 163, 185, 16, 316, 267, 66, 204, 356, 198, 76, 283, 262, 235, 210, 154, 201, 281, 116, 335, 215, 294, 38, 303, 114, 221, 246, 119, 128, 25, 166, 327, 300, 14, 20, 29, 136, 299, 272, 55, 274, 338, 156, 91, 357, 202, 8, 200, 0, 3, 168, 255, 44, 160, 351, 111, 103, 98, 142, 333, 302, 309, 369, 290, 230, 169, 217, 26]</t>
+          <t>[77, 207, 197, 143, 176, 137, 45, 182, 282, 371, 85, 301, 324, 291, 373, 350, 321, 276, 363, 69, 80, 240, 93, 234, 332, 60, 323, 149, 293, 170, 32, 193, 302, 333, 309, 104, 354, 247, 317, 169, 217, 26, 125, 130, 375, 42, 11, 320, 62, 296, 219, 230, 290, 74, 36, 325, 105, 81, 269, 385, 98, 369, 142, 103, 110, 111, 370, 146, 289, 351, 132, 248, 160, 44, 255, 168, 3, 0, 200, 8, 202, 357, 91, 156, 338, 274, 55, 272, 299, 136, 29, 20, 14, 300, 327, 166, 25, 128, 119, 246, 221, 114, 303, 38, 294, 215, 335, 116, 281, 284, 213, 201, 154, 235, 262, 283, 76, 198, 210, 356, 204, 66, 267, 316, 16, 185, 163, 172, 12, 18, 383, 297, 41, 390, 106, 195, 117, 315, 340, 68, 75, 396, 275, 250, 310, 129, 306, 157, 343, 326, 292, 109, 147, 59, 344, 271, 313, 194, 386, 329, 92, 134, 211, 72, 381, 264, 208, 121, 1, 138, 384, 298, 359, 353, 107, 256, 366, 21, 65, 214, 226, 19, 165, 367, 273, 56, 178, 95, 102, 336, 376, 387, 222, 249, 268, 27, 377, 175, 220, 261, 30, 241, 124, 352, 51, 13, 140, 279, 259, 79, 227, 225, 280, 4, 254, 265, 188, 9, 145, 372, 392, 15, 360, 206, 2, 115, 389, 331, 131, 10, 99, 362, 244, 223, 58, 31, 361, 253, 328, 61, 141, 112, 349, 22, 190, 123, 100, 395, 319, 67, 252, 47, 205, 34, 122, 46, 6, 63, 159, 322, 71, 270, 183, 35, 153, 278, 118, 378, 345, 229, 212, 341, 48, 57, 135, 5, 150, 287, 97, 239, 23, 305, 88, 233, 394, 53, 399, 288, 347, 277, 86, 311, 186, 242, 339, 380, 83, 64, 365, 397, 173, 388, 355, 330, 199, 24, 162, 28, 196, 368, 94, 52, 189, 307, 158, 84, 358, 155, 191, 203, 179, 295, 151, 393, 49, 82, 318, 209, 258, 228, 174, 348, 78, 312, 161, 224, 260, 314, 286, 391, 113, 342, 40, 70, 152, 126, 184, 87, 243, 251, 101, 382, 231, 164, 50, 237, 308, 177, 346, 285, 33, 236, 257, 89, 120, 374, 37, 238, 127, 43, 180, 144, 7, 334, 90, 148, 192, 337, 398, 364, 17, 304, 232, 181, 216, 187, 266, 171, 133, 139, 73, 218, 96, 54, 167, 39, 245, 108, 263, 379]</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1218,17 +1218,17 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>18325</v>
+        <v>19166</v>
       </c>
       <c r="E24" t="n">
-        <v>19.92016229304365</v>
+        <v>25.42372881355932</v>
       </c>
       <c r="F24" t="n">
-        <v>60.00002908706665</v>
+        <v>60.00002884864807</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>[88, 394, 198, 76, 283, 210, 356, 154, 235, 262, 237, 164, 50, 231, 89, 120, 374, 78, 348, 312, 161, 260, 224, 286, 314, 113, 391, 40, 342, 70, 152, 126, 184, 243, 87, 251, 101, 382, 258, 228, 174, 144, 180, 43, 127, 7, 334, 148, 90, 192, 337, 398, 364, 304, 17, 232, 181, 216, 139, 187, 266, 171, 133, 363, 69, 80, 240, 93, 234, 332, 60, 323, 32, 193, 302, 333, 309, 317, 169, 217, 125, 26, 11, 375, 130, 42, 320, 62, 296, 219, 230, 290, 98, 103, 110, 385, 269, 81, 325, 105, 273, 165, 367, 19, 226, 214, 65, 256, 21, 366, 357, 202, 274, 55, 272, 156, 338, 136, 8, 200, 0, 3, 168, 255, 44, 160, 33, 285, 346, 177, 308, 213, 284, 201, 281, 116, 185, 16, 316, 267, 66, 233, 53, 399, 288, 347, 277, 86, 311, 186, 242, 339, 64, 83, 380, 365, 358, 84, 189, 307, 158, 397, 52, 94, 368, 196, 28, 162, 24, 330, 355, 388, 199, 173, 155, 191, 203, 209, 318, 82, 179, 295, 151, 49, 393, 73, 218, 96, 379, 263, 108, 245, 39, 167, 54, 238, 37, 248, 132, 351, 289, 146, 370, 111, 142, 369, 247, 354, 104, 170, 293, 149, 137, 45, 85, 182, 282, 371, 301, 324, 197, 77, 291, 373, 350, 321, 276, 207, 143, 176, 74, 36, 377, 27, 175, 220, 222, 387, 261, 124, 30, 241, 9, 188, 145, 372, 392, 15, 360, 206, 2, 92, 134, 265, 254, 4, 280, 225, 227, 279, 259, 140, 13, 352, 51, 376, 79, 336, 56, 178, 95, 353, 359, 298, 384, 138, 1, 121, 208, 264, 381, 72, 211, 329, 386, 194, 313, 115, 389, 271, 331, 131, 10, 99, 362, 244, 223, 58, 31, 361, 253, 344, 328, 61, 112, 349, 100, 395, 319, 67, 252, 123, 47, 46, 122, 205, 34, 270, 183, 35, 278, 153, 71, 322, 118, 378, 345, 229, 212, 341, 57, 48, 135, 5, 150, 106, 195, 159, 63, 68, 75, 396, 275, 250, 310, 129, 306, 157, 326, 343, 109, 147, 59, 292, 141, 22, 190, 6, 340, 315, 117, 390, 41, 297, 383, 18, 12, 172, 163, 166, 327, 25, 128, 119, 246, 221, 114, 303, 38, 294, 215, 335, 300, 14, 20, 29, 299, 91, 107, 102, 249, 268, 236, 257, 204, 305, 23, 97, 287, 239]</t>
+          <t>[222, 261, 124, 30, 241, 9, 188, 145, 372, 392, 15, 360, 206, 2, 92, 134, 265, 254, 4, 280, 227, 79, 279, 259, 140, 13, 352, 51, 376, 336, 249, 268, 27, 377, 36, 74, 219, 230, 290, 369, 98, 110, 385, 269, 81, 105, 325, 273, 367, 165, 19, 226, 214, 65, 256, 21, 366, 357, 91, 156, 338, 272, 55, 274, 202, 0, 8, 200, 3, 168, 255, 44, 160, 33, 285, 346, 177, 308, 237, 50, 164, 231, 89, 374, 120, 78, 348, 228, 258, 260, 224, 314, 286, 391, 113, 342, 40, 70, 152, 126, 184, 251, 87, 243, 101, 382, 161, 312, 180, 144, 174, 43, 127, 334, 7, 148, 90, 192, 337, 398, 364, 17, 304, 232, 181, 216, 139, 187, 133, 171, 266, 363, 69, 80, 240, 93, 332, 234, 60, 323, 32, 193, 104, 354, 247, 317, 169, 217, 26, 125, 130, 375, 42, 11, 320, 62, 296, 175, 220, 387, 225, 56, 102, 178, 95, 107, 298, 384, 138, 121, 1, 264, 208, 381, 72, 211, 329, 386, 194, 313, 115, 389, 271, 331, 131, 10, 99, 362, 244, 223, 58, 31, 61, 328, 59, 344, 253, 361, 22, 67, 100, 395, 123, 47, 252, 190, 34, 205, 46, 122, 270, 183, 71, 322, 153, 278, 35, 118, 378, 345, 212, 229, 341, 48, 57, 135, 5, 150, 159, 117, 315, 340, 68, 75, 396, 275, 250, 310, 129, 343, 157, 306, 109, 147, 292, 326, 141, 112, 349, 319, 6, 63, 106, 195, 390, 41, 297, 383, 18, 12, 172, 163, 316, 185, 16, 66, 204, 267, 356, 154, 210, 235, 262, 283, 76, 198, 233, 394, 53, 288, 399, 347, 277, 86, 311, 186, 242, 339, 380, 83, 64, 365, 358, 84, 158, 307, 189, 52, 94, 368, 196, 28, 162, 24, 199, 330, 355, 388, 173, 397, 155, 191, 179, 203, 209, 318, 82, 49, 295, 151, 393, 73, 218, 96, 379, 263, 108, 245, 39, 167, 54, 238, 37, 248, 132, 351, 289, 146, 370, 111, 103, 142, 309, 333, 302, 170, 293, 149, 176, 85, 182, 282, 371, 301, 324, 45, 137, 143, 207, 197, 77, 291, 373, 350, 321, 276, 257, 236, 213, 284, 201, 281, 116, 215, 335, 128, 119, 246, 221, 114, 303, 38, 294, 25, 327, 166, 300, 14, 20, 29, 136, 353, 359, 299, 287, 97, 239, 23, 305, 88]</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1252,17 +1252,17 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15689</v>
+        <v>15705</v>
       </c>
       <c r="E25" t="n">
-        <v>2.66998233099928</v>
+        <v>2.774687520450232</v>
       </c>
       <c r="F25" t="n">
-        <v>1.693090677261353</v>
+        <v>1.44023585319519</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>[311, 186, 355, 388, 330, 199, 24, 162, 28, 196, 368, 94, 52, 397, 189, 307, 158, 84, 358, 155, 191, 203, 209, 179, 295, 151, 304, 17, 232, 181, 216, 364, 393, 49, 82, 318, 174, 228, 258, 312, 161, 224, 260, 101, 382, 231, 89, 257, 236, 285, 346, 177, 308, 213, 284, 201, 281, 116, 215, 335, 128, 119, 246, 25, 327, 166, 163, 172, 12, 18, 383, 297, 41, 390, 106, 195, 117, 315, 340, 68, 75, 29, 20, 14, 300, 221, 114, 303, 38, 294, 33, 160, 44, 255, 168, 3, 0, 200, 8, 136, 299, 272, 55, 274, 338, 156, 91, 357, 202, 366, 21, 256, 65, 370, 146, 289, 351, 132, 248, 238, 37, 374, 120, 78, 348, 180, 144, 43, 127, 7, 334, 90, 148, 192, 337, 398, 96, 218, 73, 139, 187, 266, 171, 133, 363, 69, 80, 240, 93, 234, 332, 60, 323, 176, 143, 197, 77, 207, 276, 321, 350, 373, 291, 324, 301, 85, 371, 282, 182, 45, 137, 149, 293, 170, 32, 193, 104, 354, 247, 317, 169, 217, 26, 125, 130, 375, 42, 11, 320, 62, 296, 219, 230, 290, 369, 142, 333, 309, 302, 379, 54, 167, 39, 245, 108, 263, 111, 110, 103, 98, 385, 269, 74, 36, 377, 27, 268, 249, 222, 175, 220, 261, 30, 241, 124, 387, 376, 336, 105, 325, 81, 273, 367, 165, 19, 214, 226, 56, 178, 95, 102, 107, 353, 359, 298, 384, 138, 1, 121, 208, 264, 381, 72, 211, 329, 92, 134, 265, 254, 4, 280, 225, 227, 79, 259, 279, 140, 13, 51, 352, 9, 188, 145, 372, 392, 15, 360, 206, 2, 115, 389, 313, 386, 194, 271, 331, 131, 10, 99, 362, 244, 223, 58, 31, 361, 253, 61, 328, 344, 59, 147, 109, 292, 326, 343, 157, 306, 129, 310, 250, 275, 396, 319, 67, 395, 100, 349, 112, 141, 22, 190, 123, 47, 252, 46, 122, 205, 34, 270, 6, 63, 159, 150, 5, 322, 71, 153, 278, 183, 35, 118, 378, 345, 229, 212, 341, 48, 57, 135, 287, 97, 239, 23, 305, 88, 267, 316, 185, 16, 66, 204, 233, 394, 53, 288, 399, 198, 76, 283, 210, 356, 154, 235, 262, 237, 164, 50, 243, 87, 251, 184, 126, 152, 70, 40, 342, 113, 314, 286, 391, 365, 64, 83, 173, 380, 339, 242, 277, 347, 86]</t>
+          <t>[98, 385, 269, 81, 325, 105, 56, 178, 95, 102, 107, 353, 359, 298, 384, 138, 1, 121, 208, 264, 381, 72, 211, 4, 254, 265, 352, 51, 13, 140, 259, 279, 280, 225, 227, 79, 376, 336, 249, 222, 268, 27, 377, 36, 74, 219, 230, 290, 369, 142, 333, 309, 302, 193, 32, 323, 176, 143, 197, 77, 207, 276, 321, 350, 373, 291, 324, 301, 85, 371, 282, 182, 45, 137, 149, 293, 170, 104, 354, 247, 317, 169, 217, 26, 125, 130, 375, 42, 11, 320, 62, 296, 175, 220, 387, 261, 30, 241, 124, 9, 188, 145, 372, 392, 15, 360, 206, 2, 92, 134, 329, 386, 194, 313, 115, 389, 271, 331, 131, 10, 99, 362, 244, 223, 58, 31, 361, 253, 344, 59, 147, 292, 109, 343, 326, 328, 61, 141, 22, 190, 123, 47, 252, 46, 122, 205, 34, 270, 183, 35, 118, 278, 153, 71, 322, 341, 212, 378, 345, 229, 48, 57, 135, 5, 150, 159, 63, 6, 340, 315, 68, 75, 319, 67, 395, 100, 349, 112, 129, 157, 306, 310, 250, 275, 396, 299, 338, 156, 91, 357, 202, 274, 272, 55, 136, 29, 14, 300, 20, 117, 195, 106, 390, 41, 287, 97, 239, 23, 18, 383, 297, 12, 172, 163, 316, 267, 305, 88, 204, 66, 16, 185, 116, 166, 327, 25, 128, 119, 246, 221, 114, 303, 8, 200, 0, 3, 168, 44, 160, 255, 294, 38, 335, 215, 281, 284, 213, 201, 154, 235, 210, 356, 233, 394, 53, 288, 399, 198, 76, 283, 262, 308, 177, 346, 33, 285, 257, 236, 120, 374, 78, 89, 231, 164, 50, 237, 243, 87, 251, 184, 126, 152, 70, 40, 342, 113, 391, 365, 64, 83, 380, 339, 242, 86, 277, 347, 311, 186, 355, 388, 330, 199, 173, 24, 162, 28, 196, 368, 94, 52, 397, 189, 307, 158, 84, 358, 155, 191, 179, 295, 151, 393, 49, 82, 318, 209, 203, 258, 286, 314, 224, 260, 101, 382, 161, 312, 348, 228, 174, 144, 180, 43, 127, 7, 334, 90, 148, 192, 337, 398, 364, 17, 304, 232, 181, 216, 139, 187, 266, 171, 133, 363, 69, 80, 240, 93, 234, 60, 332, 218, 73, 96, 379, 263, 111, 245, 39, 108, 167, 54, 238, 37, 248, 132, 351, 289, 146, 65, 21, 366, 256, 226, 214, 19, 273, 367, 165, 370, 110, 103]</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1292,7 +1292,7 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>1.828637838363647</v>
+        <v>1.751811981201172</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
@@ -1316,17 +1316,17 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>133833</v>
+        <v>133901</v>
       </c>
       <c r="E27" t="n">
-        <v>24.82442150032178</v>
+        <v>24.887844278426</v>
       </c>
       <c r="F27" t="n">
-        <v>0.01753520965576172</v>
+        <v>0.01820993423461914</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>[265, 264, 263, 307, 306, 305, 304, 267, 266, 268, 269, 270, 271, 300, 301, 302, 303, 329, 330, 328, 327, 326, 325, 324, 323, 322, 321, 320, 319, 318, 317, 316, 314, 315, 255, 256, 257, 258, 313, 312, 311, 310, 309, 308, 262, 261, 260, 259, 244, 243, 242, 241, 240, 216, 217, 218, 219, 220, 236, 235, 234, 233, 232, 221, 222, 223, 189, 190, 183, 191, 182, 181, 180, 179, 178, 177, 176, 158, 157, 156, 155, 154, 153, 152, 150, 151, 142, 149, 141, 140, 139, 138, 137, 136, 135, 134, 133, 161, 162, 163, 164, 166, 165, 168, 169, 167, 170, 171, 173, 172, 203, 202, 201, 200, 199, 198, 197, 196, 195, 194, 193, 192, 237, 238, 239, 215, 214, 213, 212, 211, 210, 209, 249, 250, 208, 252, 251, 248, 247, 246, 245, 254, 253, 207, 206, 205, 204, 174, 175, 160, 159, 125, 123, 122, 124, 98, 127, 129, 130, 131, 132, 128, 126, 121, 120, 118, 117, 115, 114, 116, 119, 100, 99, 94, 95, 97, 96, 93, 92, 91, 101, 102, 113, 112, 103, 104, 105, 106, 87, 88, 89, 90, 69, 70, 71, 64, 65, 66, 67, 68, 18, 19, 20, 21, 23, 22, 24, 63, 25, 26, 28, 27, 62, 72, 73, 108, 107, 143, 145, 146, 147, 144, 184, 111, 110, 109, 74, 75, 60, 59, 58, 76, 77, 85, 86, 57, 56, 78, 79, 80, 81, 55, 54, 53, 52, 50, 49, 47, 46, 48, 45, 44, 42, 40, 39, 10, 9, 8, 7, 6, 5, 4, 3, 2, 1, 51, 0, 43, 41, 38, 37, 36, 35, 34, 33, 32, 16, 15, 14, 13, 12, 11, 31, 61, 30, 29, 17, 272, 273, 274, 275, 276, 277, 278, 293, 294, 295, 296, 297, 298, 299, 332, 333, 334, 335, 336, 337, 338, 359, 360, 361, 362, 363, 364, 365, 366, 367, 368, 377, 384, 385, 386, 387, 400, 399, 415, 414, 418, 419, 420, 413, 388, 389, 379, 378, 376, 375, 344, 345, 347, 348, 346, 349, 350, 352, 353, 351, 354, 355, 357, 358, 356, 291, 292, 290, 289, 288, 287, 286, 285, 284, 279, 231, 230, 224, 187, 188, 186, 229, 280, 281, 228, 227, 282, 283, 343, 342, 341, 340, 372, 371, 370, 382, 381, 383, 393, 394, 392, 397, 396, 395, 398, 391, 390, 380, 374, 373, 339, 225, 226, 185, 148, 82, 83, 84, 438, 434, 435, 436, 437, 433, 402, 407, 408, 410, 409, 424, 423, 425, 426, 429, 421, 422, 411, 412, 406, 405, 432, 431, 369, 331, 401, 403, 404, 416, 417, 427, 428, 430]</t>
+          <t>[100, 99, 94, 95, 97, 96, 98, 127, 129, 130, 131, 132, 166, 164, 163, 162, 161, 160, 159, 158, 157, 156, 155, 154, 153, 152, 150, 151, 142, 149, 183, 191, 182, 181, 180, 179, 178, 177, 176, 175, 174, 203, 202, 201, 200, 199, 198, 197, 196, 195, 194, 193, 192, 190, 189, 222, 223, 232, 233, 234, 235, 236, 237, 238, 239, 240, 216, 217, 218, 219, 220, 221, 270, 269, 268, 267, 266, 265, 264, 263, 307, 306, 305, 304, 303, 302, 301, 300, 271, 272, 273, 274, 275, 276, 277, 278, 293, 294, 295, 296, 297, 298, 299, 332, 333, 334, 335, 336, 337, 338, 359, 360, 361, 362, 363, 364, 365, 366, 367, 368, 377, 384, 385, 386, 387, 400, 399, 415, 414, 418, 419, 420, 413, 388, 389, 379, 378, 376, 375, 344, 345, 347, 348, 346, 349, 350, 352, 353, 351, 354, 355, 357, 358, 356, 291, 292, 290, 289, 288, 287, 286, 285, 284, 279, 231, 230, 224, 187, 188, 186, 229, 280, 281, 228, 227, 282, 283, 343, 342, 341, 340, 372, 371, 370, 382, 381, 383, 393, 394, 392, 397, 396, 395, 398, 391, 390, 380, 374, 373, 339, 225, 226, 185, 148, 82, 83, 84, 52, 53, 54, 55, 81, 80, 79, 78, 56, 57, 77, 76, 86, 85, 58, 59, 60, 75, 74, 61, 31, 30, 29, 28, 26, 25, 27, 62, 72, 73, 63, 24, 22, 23, 21, 20, 65, 66, 67, 68, 69, 70, 88, 87, 71, 89, 90, 103, 104, 105, 106, 107, 108, 145, 143, 146, 147, 144, 184, 111, 110, 109, 112, 113, 102, 114, 116, 119, 120, 118, 117, 115, 141, 140, 139, 138, 137, 136, 135, 134, 133, 128, 126, 125, 123, 122, 124, 121, 93, 92, 91, 101, 64, 19, 18, 17, 165, 168, 169, 167, 170, 171, 173, 172, 205, 206, 207, 204, 209, 210, 211, 212, 213, 214, 215, 241, 242, 243, 244, 245, 246, 247, 248, 249, 250, 208, 252, 251, 254, 253, 315, 314, 313, 312, 311, 310, 309, 308, 262, 261, 260, 259, 258, 257, 256, 255, 317, 316, 318, 319, 320, 321, 322, 323, 324, 325, 326, 327, 328, 330, 329, 331, 369, 401, 403, 404, 416, 417, 427, 428, 430, 405, 406, 412, 411, 422, 421, 426, 429, 423, 424, 409, 410, 408, 407, 402, 425, 432, 431, 433, 437, 436, 435, 434, 438, 50, 49, 47, 46, 48, 45, 44, 42, 40, 39, 10, 9, 8, 7, 6, 5, 4, 3, 2, 1, 51, 0, 43, 41, 38, 37, 36, 35, 34, 33, 32, 16, 15, 14, 13, 12, 11]</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1350,17 +1350,17 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>124778</v>
+        <v>132867</v>
       </c>
       <c r="E28" t="n">
-        <v>16.37893244541444</v>
+        <v>23.92344497607656</v>
       </c>
       <c r="F28" t="n">
-        <v>1.953552007675171</v>
+        <v>1.726657152175903</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>[413, 420, 419, 418, 388, 389, 379, 378, 376, 375, 344, 345, 347, 346, 348, 349, 350, 352, 351, 353, 354, 355, 357, 356, 358, 292, 291, 290, 289, 288, 287, 339, 286, 285, 284, 279, 231, 230, 224, 188, 187, 186, 229, 280, 281, 340, 373, 374, 380, 390, 391, 398, 395, 396, 397, 392, 394, 393, 383, 381, 382, 371, 370, 372, 341, 342, 343, 283, 282, 227, 228, 226, 225, 185, 148, 84, 83, 82, 52, 53, 54, 55, 81, 80, 79, 78, 56, 57, 33, 34, 35, 36, 11, 10, 37, 38, 39, 40, 41, 43, 42, 44, 45, 48, 46, 47, 49, 50, 51, 1, 2, 0, 3, 4, 5, 6, 7, 8, 9, 12, 13, 14, 15, 16, 32, 31, 30, 29, 27, 25, 26, 28, 62, 63, 24, 22, 23, 21, 20, 19, 18, 17, 93, 92, 91, 101, 90, 89, 70, 69, 68, 67, 66, 65, 64, 71, 87, 88, 103, 104, 105, 106, 143, 145, 146, 147, 144, 184, 189, 190, 183, 191, 182, 181, 180, 179, 177, 178, 154, 153, 152, 150, 149, 142, 151, 141, 140, 139, 118, 117, 115, 112, 113, 102, 114, 116, 119, 100, 99, 94, 95, 96, 97, 98, 127, 132, 131, 130, 129, 128, 126, 125, 123, 124, 122, 121, 120, 138, 155, 156, 157, 137, 136, 135, 134, 133, 161, 162, 163, 164, 166, 165, 168, 167, 169, 170, 171, 172, 173, 203, 175, 174, 160, 159, 158, 176, 198, 197, 196, 195, 194, 193, 192, 220, 219, 218, 217, 216, 215, 214, 213, 199, 200, 201, 202, 204, 205, 206, 207, 208, 252, 251, 254, 253, 315, 314, 313, 312, 311, 310, 309, 308, 307, 306, 305, 304, 303, 329, 302, 301, 300, 271, 270, 269, 268, 267, 266, 265, 264, 263, 262, 261, 260, 259, 258, 257, 256, 255, 246, 247, 248, 250, 249, 209, 210, 211, 212, 245, 244, 243, 242, 241, 240, 239, 238, 237, 236, 235, 234, 233, 232, 221, 222, 223, 272, 273, 274, 275, 297, 298, 299, 332, 331, 330, 328, 327, 326, 325, 324, 323, 322, 321, 320, 319, 318, 317, 316, 430, 428, 427, 417, 416, 404, 403, 401, 415, 414, 399, 400, 387, 386, 385, 384, 377, 368, 367, 366, 365, 364, 363, 362, 361, 360, 369, 359, 338, 337, 336, 335, 334, 333, 296, 295, 294, 293, 278, 277, 276, 109, 110, 111, 108, 107, 72, 73, 61, 74, 75, 60, 59, 58, 76, 77, 85, 86, 405, 406, 412, 411, 422, 421, 431, 432, 429, 426, 423, 424, 409, 410, 425, 408, 407, 402, 433, 437, 436, 435, 434, 438]</t>
+          <t>[65, 66, 67, 68, 69, 70, 71, 64, 23, 22, 21, 20, 19, 18, 17, 94, 95, 96, 97, 98, 127, 132, 131, 130, 129, 128, 126, 125, 123, 124, 122, 100, 99, 93, 92, 91, 101, 102, 112, 113, 114, 116, 119, 121, 120, 118, 117, 115, 138, 139, 140, 141, 151, 142, 149, 150, 152, 153, 154, 155, 156, 157, 137, 136, 135, 134, 133, 161, 162, 163, 164, 166, 165, 168, 167, 169, 170, 171, 172, 173, 203, 175, 174, 160, 159, 158, 176, 177, 178, 179, 180, 181, 182, 191, 183, 190, 189, 184, 144, 147, 146, 145, 143, 106, 105, 104, 103, 90, 89, 88, 87, 107, 108, 111, 110, 109, 369, 359, 338, 337, 336, 335, 299, 298, 297, 296, 295, 294, 293, 278, 277, 276, 275, 274, 273, 272, 223, 222, 221, 232, 233, 234, 235, 236, 237, 238, 239, 240, 241, 242, 243, 244, 245, 246, 247, 248, 250, 249, 209, 210, 211, 212, 213, 214, 215, 216, 217, 218, 219, 220, 192, 193, 194, 195, 196, 197, 198, 199, 200, 201, 202, 204, 205, 206, 207, 208, 252, 251, 254, 253, 255, 256, 257, 258, 259, 260, 261, 262, 263, 306, 307, 308, 309, 310, 311, 312, 313, 314, 315, 316, 317, 318, 319, 320, 321, 322, 323, 324, 325, 326, 327, 328, 303, 304, 305, 264, 265, 266, 267, 268, 269, 270, 271, 300, 301, 302, 329, 330, 331, 332, 333, 334, 360, 361, 362, 363, 364, 365, 366, 367, 368, 377, 384, 385, 386, 387, 400, 399, 415, 414, 418, 419, 420, 413, 388, 389, 379, 378, 376, 375, 344, 345, 347, 346, 348, 349, 350, 352, 351, 353, 354, 355, 357, 356, 358, 292, 291, 290, 289, 288, 287, 339, 286, 285, 284, 279, 231, 230, 224, 188, 187, 186, 229, 280, 281, 340, 373, 374, 380, 390, 391, 398, 395, 396, 397, 392, 394, 393, 383, 381, 382, 371, 370, 372, 341, 342, 343, 283, 282, 227, 228, 226, 225, 185, 148, 84, 83, 82, 52, 53, 54, 55, 81, 80, 79, 78, 56, 57, 33, 34, 35, 36, 11, 10, 37, 38, 39, 40, 41, 43, 42, 44, 45, 48, 46, 47, 49, 50, 51, 1, 2, 0, 3, 4, 5, 6, 7, 8, 9, 12, 13, 14, 15, 16, 32, 31, 30, 29, 28, 27, 26, 25, 24, 63, 73, 72, 62, 61, 74, 75, 60, 59, 58, 76, 77, 85, 86, 405, 406, 412, 411, 422, 421, 431, 432, 429, 426, 423, 424, 409, 410, 425, 408, 407, 402, 433, 437, 436, 435, 434, 438, 401, 403, 404, 416, 417, 427, 428, 430]</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1384,17 +1384,17 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>133978</v>
+        <v>128960</v>
       </c>
       <c r="E29" t="n">
-        <v>24.95966124774989</v>
+        <v>20.27943329882388</v>
       </c>
       <c r="F29" t="n">
-        <v>60.00000691413879</v>
+        <v>60.00002717971802</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>[159, 160, 161, 162, 163, 164, 166, 165, 168, 167, 169, 170, 171, 172, 173, 203, 202, 201, 200, 199, 198, 197, 196, 195, 194, 193, 192, 191, 182, 181, 178, 179, 180, 177, 176, 158, 157, 156, 155, 154, 153, 152, 150, 151, 149, 142, 183, 190, 189, 222, 223, 232, 233, 234, 235, 236, 237, 238, 239, 240, 216, 217, 218, 219, 220, 221, 270, 269, 268, 267, 266, 265, 264, 263, 307, 306, 305, 304, 303, 302, 301, 300, 271, 272, 273, 274, 275, 276, 277, 278, 293, 294, 295, 296, 297, 298, 299, 332, 333, 334, 335, 336, 337, 338, 359, 360, 361, 362, 363, 364, 365, 368, 369, 366, 377, 384, 385, 386, 387, 400, 399, 415, 414, 418, 419, 420, 413, 388, 389, 379, 378, 376, 375, 344, 345, 347, 348, 346, 349, 350, 351, 353, 352, 354, 355, 357, 358, 356, 291, 292, 290, 289, 288, 287, 286, 285, 284, 279, 231, 230, 224, 187, 188, 186, 229, 280, 281, 228, 227, 282, 283, 343, 342, 341, 340, 372, 371, 370, 382, 381, 383, 393, 394, 392, 397, 396, 395, 398, 391, 390, 380, 374, 373, 339, 225, 226, 185, 148, 84, 83, 82, 52, 53, 54, 55, 81, 80, 79, 78, 56, 57, 77, 85, 86, 76, 58, 59, 60, 75, 74, 61, 31, 30, 29, 28, 26, 25, 27, 62, 72, 73, 63, 24, 22, 23, 21, 20, 65, 64, 67, 68, 69, 89, 70, 71, 87, 88, 90, 103, 104, 105, 106, 107, 108, 143, 145, 146, 144, 184, 147, 109, 110, 111, 112, 113, 102, 114, 119, 116, 120, 118, 117, 115, 141, 140, 139, 138, 137, 136, 135, 134, 133, 128, 126, 125, 123, 122, 124, 98, 127, 129, 130, 131, 132, 96, 97, 95, 94, 99, 100, 121, 93, 92, 91, 101, 66, 19, 18, 17, 174, 175, 204, 205, 206, 207, 208, 250, 249, 209, 210, 211, 212, 213, 214, 215, 241, 242, 243, 244, 245, 246, 247, 248, 251, 252, 254, 253, 315, 314, 313, 312, 311, 310, 309, 308, 262, 261, 260, 259, 258, 257, 256, 255, 317, 316, 318, 319, 320, 321, 322, 323, 324, 325, 326, 327, 328, 330, 329, 331, 367, 401, 403, 404, 416, 417, 427, 428, 430, 405, 406, 412, 411, 422, 421, 429, 426, 423, 424, 409, 410, 402, 407, 408, 425, 432, 431, 433, 437, 436, 435, 434, 438, 50, 49, 47, 46, 48, 45, 44, 42, 40, 39, 10, 9, 8, 7, 6, 5, 4, 3, 0, 2, 51, 1, 43, 41, 38, 37, 36, 35, 34, 33, 32, 16, 15, 14, 13, 12, 11]</t>
+          <t>[349, 350, 352, 353, 351, 348, 347, 345, 344, 346, 287, 288, 289, 290, 291, 292, 358, 357, 355, 356, 354, 376, 375, 379, 378, 388, 389, 390, 391, 398, 397, 395, 396, 392, 393, 394, 383, 382, 381, 371, 370, 372, 373, 374, 380, 340, 341, 342, 343, 283, 282, 227, 228, 225, 226, 185, 148, 186, 187, 224, 230, 231, 279, 284, 285, 286, 339, 229, 280, 281, 188, 81, 80, 79, 78, 56, 57, 77, 85, 86, 76, 58, 59, 60, 75, 74, 61, 31, 30, 29, 28, 26, 25, 27, 62, 72, 73, 63, 24, 22, 23, 20, 21, 64, 65, 66, 68, 69, 70, 88, 87, 71, 89, 90, 103, 104, 105, 106, 107, 108, 145, 143, 146, 147, 144, 184, 189, 190, 183, 191, 182, 181, 180, 179, 178, 177, 176, 158, 157, 156, 155, 154, 153, 152, 150, 151, 142, 149, 141, 140, 139, 138, 137, 136, 135, 134, 133, 161, 162, 163, 164, 166, 165, 168, 169, 167, 170, 171, 172, 173, 203, 202, 201, 200, 199, 198, 197, 196, 195, 194, 193, 192, 220, 219, 218, 217, 216, 215, 214, 213, 212, 211, 210, 209, 249, 250, 208, 252, 251, 248, 247, 246, 245, 244, 243, 242, 241, 240, 239, 238, 237, 236, 235, 234, 233, 232, 221, 222, 223, 272, 273, 274, 275, 276, 277, 278, 293, 294, 295, 296, 297, 298, 299, 332, 333, 334, 335, 336, 337, 338, 359, 369, 360, 361, 363, 364, 365, 362, 367, 368, 377, 384, 385, 386, 387, 400, 399, 415, 414, 418, 419, 420, 413, 405, 406, 412, 411, 422, 421, 429, 426, 423, 424, 409, 410, 402, 407, 408, 425, 432, 431, 433, 437, 436, 435, 434, 438, 84, 83, 82, 52, 54, 53, 55, 46, 47, 49, 50, 51, 1, 2, 0, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 32, 33, 34, 35, 37, 36, 38, 41, 43, 44, 42, 40, 39, 45, 48, 109, 110, 111, 112, 113, 102, 114, 116, 119, 120, 118, 117, 115, 121, 122, 124, 123, 125, 126, 128, 129, 132, 131, 130, 127, 98, 97, 96, 95, 94, 99, 100, 93, 92, 91, 101, 67, 19, 18, 17, 159, 160, 174, 175, 204, 205, 206, 207, 254, 253, 315, 314, 313, 312, 311, 310, 309, 308, 307, 306, 263, 262, 261, 260, 259, 258, 257, 256, 255, 317, 316, 318, 319, 320, 321, 322, 323, 324, 325, 326, 327, 328, 330, 329, 302, 301, 303, 304, 305, 266, 265, 264, 267, 268, 269, 270, 271, 300, 331, 366, 401, 403, 404, 416, 417, 427, 428, 430]</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1418,17 +1418,17 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>108080</v>
+        <v>108308</v>
       </c>
       <c r="E30" t="n">
-        <v>0.8049096691755973</v>
+        <v>1.017562513407389</v>
       </c>
       <c r="F30" t="n">
-        <v>1.869689702987671</v>
+        <v>1.645426034927368</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>[165, 168, 167, 169, 170, 171, 172, 173, 203, 175, 174, 160, 159, 161, 162, 133, 134, 135, 136, 137, 138, 139, 140, 141, 115, 117, 118, 120, 121, 123, 125, 126, 128, 124, 122, 100, 119, 116, 114, 102, 113, 112, 103, 104, 105, 106, 107, 108, 109, 110, 111, 145, 143, 146, 147, 144, 184, 189, 223, 222, 232, 233, 234, 235, 221, 190, 183, 149, 142, 151, 150, 152, 153, 154, 155, 156, 157, 158, 176, 177, 178, 179, 180, 181, 182, 191, 192, 193, 194, 195, 196, 197, 198, 199, 200, 201, 202, 204, 205, 206, 207, 208, 252, 250, 249, 209, 210, 211, 212, 213, 214, 215, 216, 217, 218, 219, 220, 236, 237, 238, 239, 240, 241, 242, 243, 244, 245, 246, 247, 248, 251, 254, 253, 315, 255, 256, 257, 258, 259, 260, 261, 262, 263, 264, 265, 266, 267, 268, 269, 270, 271, 300, 301, 302, 303, 304, 305, 306, 307, 308, 309, 310, 311, 312, 313, 314, 316, 317, 318, 319, 320, 321, 322, 323, 324, 325, 326, 327, 328, 330, 329, 331, 332, 333, 334, 335, 336, 295, 296, 297, 298, 299, 272, 273, 274, 275, 276, 277, 278, 293, 294, 337, 338, 359, 369, 360, 361, 362, 363, 364, 365, 366, 367, 368, 377, 384, 385, 386, 387, 400, 399, 401, 403, 404, 416, 417, 427, 428, 430, 415, 414, 418, 419, 420, 413, 405, 406, 412, 411, 422, 421, 431, 432, 429, 426, 423, 425, 424, 409, 410, 408, 407, 402, 433, 437, 436, 435, 434, 438, 283, 343, 342, 341, 340, 372, 370, 371, 382, 381, 383, 393, 394, 392, 396, 395, 397, 398, 391, 390, 380, 374, 373, 389, 388, 378, 379, 375, 376, 349, 350, 352, 351, 353, 354, 355, 357, 356, 358, 292, 291, 290, 289, 288, 287, 348, 347, 345, 346, 344, 339, 286, 285, 284, 279, 231, 230, 224, 188, 187, 186, 229, 280, 281, 228, 282, 227, 226, 225, 185, 148, 84, 83, 82, 52, 53, 54, 55, 81, 80, 79, 78, 43, 41, 38, 39, 40, 42, 44, 45, 48, 46, 47, 49, 50, 51, 1, 2, 0, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 32, 33, 34, 35, 36, 37, 56, 57, 77, 85, 86, 76, 58, 59, 60, 75, 74, 61, 31, 30, 29, 28, 27, 26, 25, 62, 72, 73, 63, 24, 22, 20, 21, 23, 64, 65, 66, 19, 18, 17, 67, 68, 69, 70, 71, 87, 88, 89, 90, 101, 91, 92, 93, 99, 94, 95, 96, 97, 98, 127, 129, 130, 131, 132, 166, 164, 163]</t>
+          <t>[95, 94, 99, 100, 93, 92, 91, 101, 102, 114, 116, 119, 120, 118, 117, 115, 113, 112, 141, 140, 139, 138, 137, 136, 135, 134, 133, 162, 161, 160, 159, 158, 157, 156, 155, 154, 153, 152, 151, 142, 150, 149, 184, 144, 147, 146, 143, 145, 111, 110, 109, 108, 107, 106, 105, 104, 103, 90, 89, 88, 87, 71, 70, 69, 68, 67, 17, 18, 19, 20, 21, 66, 65, 64, 23, 22, 24, 63, 73, 72, 62, 25, 26, 27, 28, 29, 30, 31, 61, 74, 75, 60, 59, 58, 76, 86, 85, 77, 57, 56, 37, 36, 35, 34, 33, 32, 16, 15, 14, 13, 12, 11, 10, 9, 8, 7, 6, 5, 4, 3, 0, 2, 1, 51, 50, 49, 47, 46, 48, 45, 44, 42, 40, 39, 38, 41, 43, 78, 79, 80, 81, 55, 54, 53, 52, 82, 83, 84, 148, 185, 225, 226, 227, 282, 228, 281, 280, 229, 186, 187, 188, 224, 230, 231, 279, 284, 285, 286, 339, 287, 288, 289, 290, 291, 292, 358, 357, 355, 356, 354, 353, 352, 350, 351, 349, 348, 346, 344, 345, 347, 376, 375, 379, 378, 388, 389, 390, 391, 398, 395, 396, 397, 392, 394, 393, 383, 382, 370, 372, 371, 381, 380, 374, 373, 340, 341, 342, 343, 283, 438, 434, 435, 436, 437, 433, 402, 407, 408, 410, 409, 424, 425, 423, 426, 429, 432, 431, 421, 422, 411, 412, 406, 405, 413, 420, 419, 418, 414, 415, 430, 428, 427, 417, 416, 404, 403, 401, 399, 400, 387, 386, 385, 384, 377, 368, 367, 366, 365, 364, 363, 362, 361, 360, 369, 359, 338, 337, 336, 335, 334, 333, 332, 299, 298, 297, 296, 295, 294, 293, 278, 277, 276, 275, 274, 273, 272, 271, 270, 269, 268, 267, 266, 305, 304, 303, 301, 300, 302, 329, 331, 330, 328, 327, 326, 325, 324, 323, 322, 321, 320, 319, 318, 317, 316, 314, 313, 312, 311, 310, 309, 308, 307, 306, 265, 264, 263, 262, 261, 260, 259, 258, 257, 256, 255, 315, 253, 254, 251, 248, 247, 246, 245, 244, 243, 242, 241, 240, 239, 238, 237, 236, 235, 234, 233, 232, 222, 223, 189, 190, 183, 191, 182, 181, 180, 179, 178, 176, 177, 198, 197, 196, 195, 194, 193, 192, 221, 220, 219, 218, 217, 216, 215, 214, 213, 212, 211, 210, 209, 249, 250, 252, 208, 207, 206, 205, 204, 202, 201, 200, 199, 175, 174, 203, 173, 172, 171, 170, 169, 167, 168, 165, 163, 164, 166, 132, 131, 130, 129, 127, 128, 126, 125, 123, 121, 122, 124, 98, 97, 96]</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1458,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>2.275608062744141</v>
+        <v>2.148699283599854</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
@@ -1482,17 +1482,17 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>8585</v>
+        <v>8515</v>
       </c>
       <c r="E32" t="n">
-        <v>26.75328510261332</v>
+        <v>25.71976967370441</v>
       </c>
       <c r="F32" t="n">
-        <v>0.03786492347717285</v>
+        <v>0.04045295715332031</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>[174, 175, 176, 200, 201, 202, 178, 179, 156, 155, 154, 132, 131, 130, 107, 106, 108, 109, 86, 64, 63, 62, 61, 60, 37, 36, 35, 58, 57, 56, 55, 54, 53, 76, 75, 74, 97, 96, 95, 93, 92, 70, 69, 46, 47, 48, 71, 72, 73, 50, 49, 27, 28, 51, 52, 30, 31, 32, 10, 33, 34, 12, 11, 13, 14, 15, 38, 39, 40, 41, 18, 42, 19, 20, 44, 43, 66, 67, 68, 91, 90, 112, 111, 110, 133, 134, 135, 157, 158, 136, 159, 160, 137, 114, 113, 89, 88, 87, 65, 85, 84, 83, 82, 81, 59, 79, 78, 77, 99, 100, 122, 98, 119, 118, 94, 116, 115, 117, 140, 141, 142, 143, 120, 121, 145, 146, 123, 124, 125, 102, 101, 103, 104, 105, 128, 127, 150, 151, 152, 153, 129, 126, 148, 149, 172, 171, 170, 169, 168, 167, 144, 166, 165, 164, 163, 162, 161, 139, 138, 184, 185, 208, 207, 209, 232, 231, 230, 253, 254, 276, 277, 278, 279, 256, 281, 258, 257, 234, 233, 255, 210, 211, 188, 187, 186, 189, 190, 191, 192, 193, 194, 216, 215, 214, 213, 235, 212, 236, 237, 238, 239, 240, 217, 218, 219, 242, 243, 244, 266, 265, 264, 241, 263, 262, 285, 261, 260, 259, 282, 283, 305, 306, 329, 307, 330, 331, 332, 354, 353, 352, 351, 350, 349, 325, 326, 348, 347, 346, 345, 322, 323, 324, 300, 301, 302, 303, 280, 304, 327, 328, 375, 374, 396, 397, 398, 399, 400, 401, 424, 423, 446, 447, 470, 471, 472, 449, 450, 451, 452, 475, 476, 453, 454, 455, 456, 478, 479, 480, 504, 503, 525, 524, 523, 501, 500, 502, 526, 548, 549, 527, 528, 505, 482, 481, 458, 457, 434, 435, 436, 413, 412, 388, 411, 410, 387, 409, 386, 408, 407, 406, 405, 428, 427, 426, 425, 448, 404, 403, 402, 379, 378, 377, 355, 356, 357, 333, 334, 311, 310, 309, 308, 284, 286, 287, 288, 289, 267, 268, 245, 246, 247, 248, 226, 225, 224, 223, 199, 198, 197, 220, 196, 195, 173, 221, 222, 270, 271, 249, 250, 273, 274, 275, 298, 297, 320, 321, 343, 344, 367, 366, 389, 390, 365, 364, 363, 340, 339, 338, 337, 336, 335, 312, 313, 290, 314, 315, 316, 317, 295, 294, 293, 292, 291, 269, 272, 296, 319, 318, 342, 341, 362, 385, 384, 360, 359, 382, 358, 380, 381, 383, 361, 430, 431, 432, 433, 429, 474, 473, 496, 497, 498, 499, 477, 522, 521, 520, 519, 518, 495, 494, 493, 492, 515, 491, 490, 468, 469, 445, 467, 444, 443, 466, 442, 441, 440, 418, 417, 395, 420, 419, 421, 422, 376, 373, 372, 371, 394, 393, 392, 369, 370, 368, 391, 415, 416, 414, 438, 439, 462, 461, 460, 483, 484, 485, 463, 464, 465, 489, 488, 511, 510, 486, 508, 509, 507, 506, 529, 530, 531, 532, 555, 554, 553, 552, 556, 533, 534, 535, 536, 512, 514, 537, 538, 561, 560, 559, 558, 557, 562, 563, 564, 541, 542, 543, 545, 544, 567, 568, 569, 546, 547, 571, 572, 573, 550, 574, 551, 570, 566, 565, 539, 540, 517, 516, 513, 487, 437, 299, 147, 80, 29, 7, 6, 5, 3, 4, 26, 25, 24, 0, 23, 2, 1, 8, 9, 16, 17, 21, 22, 45, 182, 181, 180, 203, 204, 205, 206, 228, 229, 252, 251, 227, 183, 177, 459]</t>
+          <t>[35, 58, 57, 56, 55, 54, 53, 76, 75, 74, 97, 96, 95, 93, 92, 70, 69, 46, 47, 48, 71, 72, 73, 50, 49, 27, 28, 51, 52, 30, 31, 32, 10, 33, 34, 12, 11, 13, 14, 15, 38, 39, 40, 41, 18, 42, 19, 20, 44, 43, 66, 67, 68, 91, 90, 112, 111, 110, 133, 134, 135, 157, 158, 136, 159, 160, 137, 114, 113, 89, 88, 87, 86, 64, 63, 62, 61, 60, 37, 36, 59, 81, 82, 83, 84, 85, 109, 108, 107, 130, 131, 132, 154, 155, 177, 153, 152, 151, 150, 127, 129, 128, 104, 105, 103, 80, 78, 79, 77, 99, 100, 122, 98, 119, 118, 94, 116, 115, 117, 140, 141, 142, 143, 120, 121, 145, 146, 123, 124, 125, 102, 101, 126, 148, 149, 172, 171, 170, 169, 168, 167, 144, 166, 165, 164, 163, 162, 161, 139, 138, 184, 185, 208, 207, 209, 232, 231, 230, 253, 254, 276, 277, 278, 279, 256, 281, 258, 257, 234, 233, 255, 210, 211, 188, 187, 186, 189, 190, 191, 192, 193, 194, 216, 215, 214, 213, 235, 212, 236, 237, 238, 239, 240, 217, 218, 219, 242, 243, 244, 266, 265, 264, 241, 263, 262, 285, 261, 260, 259, 282, 283, 305, 306, 329, 307, 330, 331, 332, 354, 353, 352, 351, 350, 349, 325, 326, 348, 347, 346, 345, 322, 323, 324, 300, 301, 302, 303, 280, 304, 327, 328, 375, 374, 396, 397, 398, 399, 400, 401, 424, 423, 446, 447, 470, 471, 472, 449, 450, 451, 452, 475, 476, 453, 454, 455, 456, 478, 479, 480, 504, 503, 525, 524, 523, 501, 500, 502, 526, 548, 549, 527, 528, 505, 482, 481, 458, 457, 434, 435, 436, 413, 412, 388, 411, 410, 387, 409, 386, 408, 407, 406, 405, 428, 427, 426, 425, 448, 404, 403, 402, 379, 378, 377, 355, 356, 357, 333, 334, 311, 310, 309, 308, 284, 286, 287, 288, 289, 267, 268, 245, 246, 247, 248, 226, 225, 224, 223, 199, 198, 197, 220, 196, 195, 173, 174, 175, 176, 200, 201, 202, 178, 179, 156, 181, 180, 203, 204, 205, 206, 228, 229, 252, 251, 274, 273, 250, 249, 271, 270, 269, 291, 292, 314, 313, 290, 315, 316, 317, 295, 294, 293, 272, 296, 297, 320, 321, 343, 344, 367, 366, 389, 390, 365, 364, 363, 340, 339, 338, 337, 336, 335, 312, 359, 382, 358, 380, 381, 383, 384, 360, 361, 362, 385, 341, 342, 318, 319, 298, 275, 227, 183, 182, 222, 221, 147, 106, 65, 45, 22, 21, 17, 16, 9, 8, 7, 6, 5, 3, 4, 26, 25, 24, 0, 23, 2, 1, 29, 299, 370, 369, 392, 393, 371, 394, 372, 373, 376, 421, 420, 419, 418, 417, 395, 440, 441, 442, 466, 443, 444, 467, 445, 468, 469, 493, 492, 515, 491, 490, 489, 465, 464, 463, 462, 461, 460, 483, 484, 485, 486, 508, 509, 510, 487, 488, 511, 512, 536, 535, 559, 558, 560, 561, 538, 537, 514, 513, 516, 540, 517, 518, 495, 494, 496, 473, 474, 498, 497, 520, 521, 522, 499, 477, 429, 430, 431, 432, 433, 459, 551, 574, 550, 573, 572, 571, 570, 569, 546, 547, 545, 544, 567, 568, 566, 565, 564, 563, 562, 539, 541, 542, 543, 519, 534, 533, 556, 532, 531, 530, 529, 507, 506, 553, 552, 554, 555, 557, 439, 438, 437, 414, 415, 416, 391, 368, 422]</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1516,17 +1516,17 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>7378</v>
+        <v>7221</v>
       </c>
       <c r="E33" t="n">
-        <v>8.932526206998375</v>
+        <v>6.614498745016979</v>
       </c>
       <c r="F33" t="n">
-        <v>1.833070993423462</v>
+        <v>1.690006971359253</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>[146, 145, 168, 167, 144, 166, 165, 164, 163, 162, 139, 138, 161, 184, 185, 208, 207, 209, 210, 211, 186, 187, 188, 189, 190, 191, 192, 216, 217, 215, 214, 213, 236, 235, 212, 234, 233, 257, 258, 281, 279, 256, 255, 232, 231, 230, 253, 254, 276, 278, 277, 299, 300, 301, 302, 303, 280, 305, 283, 282, 259, 260, 284, 286, 308, 309, 356, 355, 354, 332, 331, 330, 307, 329, 306, 304, 327, 328, 352, 353, 377, 378, 379, 400, 399, 376, 375, 351, 350, 349, 326, 325, 324, 323, 322, 345, 346, 347, 348, 370, 369, 368, 391, 392, 393, 394, 371, 372, 373, 374, 396, 395, 418, 417, 416, 415, 414, 437, 438, 439, 462, 461, 460, 483, 484, 485, 463, 464, 465, 489, 490, 491, 513, 514, 537, 536, 512, 511, 488, 487, 486, 508, 509, 510, 533, 556, 532, 531, 507, 506, 529, 530, 553, 552, 554, 555, 557, 534, 535, 559, 558, 560, 561, 538, 539, 562, 563, 564, 541, 519, 543, 542, 565, 566, 568, 567, 544, 545, 547, 546, 569, 570, 571, 572, 573, 550, 574, 551, 549, 548, 526, 527, 528, 505, 482, 459, 434, 457, 458, 481, 504, 503, 525, 524, 523, 500, 501, 502, 480, 479, 478, 456, 455, 477, 499, 522, 521, 520, 497, 498, 474, 473, 496, 494, 495, 518, 517, 540, 516, 515, 492, 493, 469, 468, 445, 467, 444, 443, 466, 442, 441, 440, 419, 420, 397, 398, 421, 422, 423, 446, 447, 470, 471, 472, 449, 450, 451, 452, 475, 476, 453, 454, 429, 430, 431, 432, 433, 435, 436, 413, 412, 388, 411, 410, 387, 409, 386, 408, 407, 406, 405, 428, 427, 426, 448, 425, 424, 401, 402, 403, 404, 381, 383, 384, 360, 361, 362, 385, 363, 364, 340, 339, 338, 337, 312, 335, 336, 359, 382, 358, 380, 357, 333, 334, 311, 310, 287, 288, 289, 265, 241, 264, 263, 262, 285, 261, 237, 238, 239, 240, 218, 219, 242, 243, 244, 266, 267, 268, 245, 246, 247, 222, 223, 224, 248, 225, 226, 227, 250, 249, 271, 270, 269, 291, 292, 290, 313, 314, 315, 316, 317, 293, 294, 295, 319, 318, 342, 341, 365, 366, 389, 390, 367, 344, 343, 321, 320, 297, 296, 272, 273, 274, 298, 275, 251, 252, 229, 228, 204, 203, 205, 206, 183, 182, 181, 180, 156, 179, 178, 202, 201, 200, 199, 221, 198, 197, 220, 196, 195, 194, 193, 170, 169, 171, 149, 172, 173, 174, 175, 176, 151, 152, 153, 177, 155, 154, 132, 131, 130, 107, 106, 108, 109, 85, 86, 87, 88, 89, 112, 111, 110, 133, 134, 135, 157, 158, 136, 159, 160, 137, 114, 113, 90, 91, 67, 68, 45, 22, 21, 17, 16, 14, 13, 11, 12, 38, 15, 39, 40, 41, 18, 42, 19, 20, 44, 43, 66, 65, 64, 63, 62, 61, 60, 37, 36, 35, 58, 57, 56, 55, 54, 79, 78, 77, 99, 100, 122, 98, 119, 118, 95, 96, 97, 74, 75, 76, 53, 52, 30, 31, 32, 34, 33, 10, 9, 8, 7, 6, 5, 2, 1, 0, 23, 24, 25, 26, 3, 4, 29, 51, 28, 27, 49, 50, 73, 72, 71, 48, 47, 46, 69, 70, 92, 93, 115, 116, 94, 117, 140, 141, 142, 143, 120, 121, 123, 124, 102, 101, 80, 81, 59, 82, 83, 84, 105, 128, 104, 103, 125, 126, 127, 129, 150, 148, 147]</t>
+          <t>[382, 359, 360, 361, 339, 338, 337, 336, 335, 312, 311, 310, 309, 308, 331, 330, 307, 329, 328, 352, 351, 350, 373, 372, 371, 394, 393, 391, 368, 392, 369, 370, 347, 348, 349, 325, 326, 327, 304, 303, 302, 324, 346, 345, 322, 323, 299, 300, 301, 277, 276, 254, 278, 279, 256, 258, 257, 234, 233, 255, 253, 230, 231, 232, 209, 210, 212, 235, 213, 214, 215, 216, 194, 193, 192, 191, 190, 189, 188, 211, 187, 186, 185, 208, 207, 184, 161, 162, 139, 138, 140, 117, 94, 116, 115, 93, 92, 70, 69, 46, 47, 48, 71, 72, 73, 50, 49, 27, 28, 51, 29, 4, 3, 26, 25, 24, 23, 0, 1, 2, 5, 6, 7, 8, 9, 10, 33, 34, 32, 31, 30, 52, 55, 54, 53, 77, 76, 75, 74, 97, 96, 95, 118, 119, 120, 143, 142, 141, 163, 164, 165, 166, 144, 167, 168, 169, 170, 171, 172, 149, 148, 126, 147, 146, 145, 121, 123, 122, 98, 99, 100, 124, 125, 102, 101, 103, 104, 128, 106, 129, 127, 150, 151, 152, 153, 177, 155, 154, 132, 131, 130, 107, 108, 133, 110, 111, 112, 89, 88, 87, 109, 86, 85, 84, 83, 105, 82, 59, 81, 80, 78, 79, 56, 57, 58, 35, 36, 37, 60, 61, 62, 63, 64, 65, 66, 43, 44, 20, 19, 42, 18, 41, 40, 39, 15, 38, 12, 11, 13, 14, 16, 17, 21, 22, 45, 68, 67, 91, 90, 113, 114, 137, 160, 159, 136, 135, 134, 157, 158, 156, 179, 178, 202, 201, 200, 176, 175, 174, 173, 195, 196, 220, 197, 198, 199, 223, 224, 225, 226, 248, 247, 246, 245, 222, 221, 244, 243, 242, 219, 218, 217, 240, 239, 238, 237, 236, 259, 260, 282, 281, 280, 305, 283, 306, 284, 285, 261, 263, 262, 286, 287, 288, 289, 265, 264, 241, 266, 267, 268, 291, 290, 313, 314, 315, 316, 317, 295, 294, 293, 292, 269, 270, 271, 249, 250, 227, 204, 203, 180, 181, 182, 183, 206, 205, 228, 229, 252, 251, 274, 273, 272, 296, 275, 298, 297, 320, 321, 343, 344, 367, 390, 389, 366, 365, 319, 318, 342, 341, 364, 340, 363, 362, 385, 384, 383, 404, 426, 427, 428, 405, 406, 407, 408, 386, 409, 387, 410, 411, 388, 412, 413, 436, 459, 458, 457, 434, 435, 433, 432, 431, 430, 429, 454, 455, 456, 478, 479, 480, 481, 482, 504, 503, 502, 501, 500, 499, 477, 476, 453, 475, 452, 451, 450, 449, 472, 471, 470, 447, 446, 422, 421, 420, 419, 440, 441, 439, 463, 464, 442, 466, 443, 444, 467, 445, 468, 469, 493, 492, 515, 513, 491, 490, 489, 465, 487, 488, 511, 512, 536, 537, 514, 516, 539, 540, 541, 542, 543, 519, 517, 518, 495, 494, 496, 473, 474, 498, 497, 520, 521, 522, 523, 524, 525, 526, 548, 549, 527, 505, 528, 551, 574, 550, 573, 572, 571, 570, 569, 546, 547, 545, 544, 567, 568, 566, 565, 564, 563, 562, 538, 561, 560, 535, 559, 558, 557, 555, 554, 553, 552, 529, 506, 507, 530, 531, 532, 533, 556, 534, 510, 509, 508, 486, 485, 484, 483, 460, 461, 462, 438, 437, 414, 415, 416, 417, 418, 395, 396, 374, 375, 376, 397, 398, 399, 400, 401, 424, 423, 448, 425, 403, 402, 379, 378, 377, 353, 354, 332, 355, 356, 333, 334, 357, 358, 380, 381]</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1550,17 +1550,17 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>8375</v>
+        <v>8346</v>
       </c>
       <c r="E34" t="n">
-        <v>23.65273881588661</v>
+        <v>23.22456813819578</v>
       </c>
       <c r="F34" t="n">
-        <v>60.00002789497375</v>
+        <v>60.00003671646118</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>[400, 399, 398, 397, 396, 374, 373, 372, 371, 394, 393, 392, 369, 370, 347, 346, 345, 322, 323, 324, 300, 301, 302, 303, 280, 281, 258, 257, 234, 233, 255, 253, 230, 231, 232, 209, 210, 211, 188, 187, 186, 185, 208, 207, 184, 161, 162, 139, 138, 140, 117, 94, 116, 115, 92, 93, 70, 69, 46, 47, 48, 71, 72, 73, 50, 49, 27, 28, 51, 52, 30, 31, 32, 10, 33, 34, 12, 11, 13, 14, 15, 38, 39, 40, 41, 18, 42, 19, 20, 44, 43, 66, 67, 68, 91, 90, 112, 111, 110, 133, 134, 135, 157, 158, 136, 159, 160, 137, 114, 113, 89, 88, 87, 86, 64, 63, 62, 61, 60, 37, 36, 35, 58, 57, 56, 55, 54, 53, 76, 75, 74, 97, 96, 95, 118, 119, 120, 143, 142, 141, 163, 164, 165, 166, 144, 167, 168, 169, 170, 171, 172, 149, 148, 126, 147, 146, 145, 121, 123, 122, 98, 99, 100, 101, 102, 125, 124, 103, 104, 105, 83, 84, 85, 109, 108, 107, 130, 131, 132, 154, 155, 177, 153, 152, 151, 150, 127, 129, 128, 106, 82, 81, 59, 79, 78, 77, 80, 29, 7, 6, 5, 3, 4, 26, 25, 24, 0, 23, 2, 1, 8, 9, 16, 17, 21, 22, 45, 65, 156, 179, 178, 202, 201, 200, 176, 175, 174, 173, 195, 196, 220, 197, 198, 199, 221, 222, 245, 246, 247, 248, 226, 225, 224, 223, 244, 243, 242, 219, 218, 217, 240, 239, 238, 237, 236, 235, 212, 213, 214, 215, 216, 194, 193, 192, 191, 190, 189, 259, 260, 282, 283, 305, 306, 329, 307, 330, 331, 332, 354, 353, 352, 351, 350, 349, 325, 326, 348, 327, 304, 328, 375, 376, 377, 378, 379, 380, 358, 382, 359, 360, 361, 339, 338, 337, 336, 335, 312, 311, 310, 309, 308, 284, 285, 262, 261, 263, 264, 241, 265, 266, 267, 268, 291, 292, 314, 313, 290, 289, 288, 287, 286, 333, 334, 357, 356, 355, 402, 403, 404, 381, 383, 384, 362, 385, 363, 340, 364, 341, 342, 318, 319, 343, 344, 367, 366, 389, 388, 412, 411, 410, 387, 409, 386, 408, 407, 406, 405, 428, 427, 426, 425, 448, 449, 450, 451, 452, 475, 476, 453, 454, 455, 456, 478, 479, 480, 504, 503, 525, 524, 523, 501, 500, 502, 526, 548, 549, 527, 528, 505, 482, 481, 458, 457, 434, 435, 436, 413, 390, 365, 320, 297, 296, 295, 294, 293, 317, 316, 315, 269, 270, 271, 249, 250, 273, 274, 275, 298, 321, 272, 251, 252, 229, 228, 205, 206, 183, 182, 181, 180, 203, 204, 227, 432, 433, 431, 430, 429, 474, 473, 496, 497, 498, 499, 477, 522, 521, 520, 519, 518, 495, 494, 493, 492, 515, 491, 490, 468, 469, 445, 446, 447, 470, 471, 472, 423, 424, 401, 422, 444, 443, 466, 442, 441, 440, 418, 417, 395, 420, 419, 421, 467, 465, 489, 488, 511, 510, 486, 508, 509, 507, 506, 484, 460, 483, 461, 462, 439, 438, 437, 414, 415, 416, 391, 368, 299, 277, 278, 279, 256, 254, 276, 463, 464, 485, 487, 513, 514, 537, 536, 512, 535, 559, 558, 560, 561, 538, 539, 540, 517, 516, 562, 563, 564, 541, 542, 543, 545, 544, 567, 568, 569, 546, 547, 571, 572, 573, 550, 551, 574, 570, 566, 565, 534, 533, 556, 532, 531, 530, 529, 553, 552, 554, 555, 557, 459]</t>
+          <t>[403, 378, 377, 353, 354, 332, 355, 356, 357, 333, 334, 311, 310, 309, 308, 331, 330, 307, 329, 306, 305, 283, 282, 260, 284, 258, 257, 234, 233, 255, 253, 230, 231, 232, 209, 210, 211, 188, 187, 186, 185, 208, 207, 184, 161, 162, 139, 138, 140, 117, 94, 116, 115, 92, 93, 70, 69, 46, 47, 48, 71, 72, 73, 50, 49, 27, 28, 51, 52, 30, 31, 32, 10, 33, 34, 12, 11, 13, 14, 15, 38, 40, 39, 41, 18, 42, 19, 20, 44, 43, 66, 67, 68, 91, 90, 112, 111, 110, 133, 134, 135, 157, 158, 136, 159, 160, 137, 114, 113, 89, 88, 87, 86, 64, 63, 62, 61, 60, 37, 36, 35, 58, 57, 56, 55, 54, 53, 76, 75, 74, 97, 96, 95, 118, 119, 120, 143, 142, 141, 163, 164, 165, 166, 144, 167, 168, 169, 170, 171, 172, 149, 148, 126, 147, 146, 145, 121, 123, 122, 98, 99, 100, 102, 101, 125, 124, 103, 104, 105, 83, 84, 85, 109, 108, 107, 130, 131, 132, 154, 155, 177, 153, 152, 151, 150, 127, 129, 128, 106, 82, 81, 59, 80, 78, 77, 79, 29, 7, 6, 5, 3, 4, 26, 25, 24, 23, 0, 2, 1, 8, 9, 16, 17, 21, 22, 45, 65, 156, 179, 178, 202, 201, 200, 176, 175, 174, 173, 195, 196, 220, 197, 198, 199, 221, 222, 245, 246, 271, 248, 226, 225, 224, 223, 244, 243, 242, 219, 218, 217, 240, 239, 238, 237, 236, 235, 212, 213, 214, 215, 216, 194, 193, 192, 191, 190, 189, 256, 279, 278, 277, 301, 300, 299, 323, 322, 345, 346, 347, 348, 349, 325, 326, 327, 304, 303, 302, 324, 370, 369, 392, 393, 371, 394, 372, 373, 374, 396, 397, 398, 399, 400, 401, 424, 423, 446, 447, 470, 471, 472, 449, 450, 451, 452, 475, 476, 453, 454, 455, 456, 478, 479, 480, 504, 503, 525, 524, 523, 500, 501, 502, 526, 548, 549, 527, 528, 505, 482, 481, 458, 457, 434, 435, 436, 413, 412, 388, 411, 410, 387, 409, 386, 408, 407, 406, 405, 428, 427, 426, 425, 448, 404, 402, 379, 380, 358, 382, 359, 360, 361, 339, 338, 337, 336, 335, 312, 313, 290, 314, 315, 316, 317, 295, 294, 293, 292, 291, 268, 267, 266, 265, 264, 241, 263, 262, 285, 261, 286, 287, 288, 289, 269, 270, 247, 249, 250, 273, 274, 275, 298, 297, 320, 321, 343, 344, 367, 366, 389, 390, 365, 364, 363, 340, 341, 342, 318, 319, 296, 272, 251, 252, 229, 228, 205, 206, 183, 182, 181, 180, 203, 204, 227, 362, 385, 384, 383, 381, 429, 431, 432, 433, 459, 474, 473, 496, 497, 498, 499, 477, 522, 521, 520, 519, 518, 495, 494, 493, 492, 515, 491, 490, 468, 469, 445, 467, 444, 443, 466, 442, 441, 440, 418, 417, 395, 420, 419, 421, 422, 376, 375, 351, 352, 328, 350, 368, 391, 415, 416, 414, 438, 439, 462, 461, 460, 483, 484, 485, 463, 464, 465, 489, 488, 511, 510, 486, 508, 509, 507, 506, 529, 530, 531, 532, 555, 554, 553, 552, 556, 533, 534, 535, 536, 512, 514, 537, 538, 561, 560, 559, 557, 558, 562, 563, 564, 541, 542, 543, 545, 544, 567, 568, 569, 546, 570, 571, 572, 573, 550, 574, 551, 547, 566, 565, 539, 540, 517, 516, 513, 487, 437, 280, 281, 259, 254, 276, 430]</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1584,17 +1584,17 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>6936</v>
+        <v>7001</v>
       </c>
       <c r="E35" t="n">
-        <v>2.406614498745017</v>
+        <v>3.36630739701757</v>
       </c>
       <c r="F35" t="n">
-        <v>4.302642822265625</v>
+        <v>2.940769672393799</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>[383, 384, 385, 362, 363, 340, 364, 341, 342, 318, 319, 343, 344, 365, 367, 366, 389, 390, 412, 388, 411, 410, 387, 409, 386, 408, 407, 406, 405, 428, 427, 426, 448, 425, 424, 423, 422, 444, 443, 442, 466, 465, 489, 490, 467, 445, 446, 447, 470, 471, 472, 449, 450, 451, 474, 473, 496, 497, 498, 499, 477, 478, 456, 455, 454, 453, 476, 475, 452, 429, 430, 431, 432, 433, 434, 435, 413, 436, 459, 458, 457, 481, 482, 505, 528, 527, 526, 548, 549, 551, 574, 550, 573, 572, 571, 570, 569, 568, 546, 547, 523, 524, 525, 503, 504, 480, 479, 502, 501, 500, 522, 521, 520, 519, 543, 545, 567, 544, 566, 565, 542, 541, 564, 563, 562, 539, 516, 540, 517, 518, 495, 494, 493, 469, 468, 492, 515, 491, 513, 514, 537, 538, 561, 560, 559, 558, 557, 555, 554, 552, 553, 530, 529, 506, 507, 531, 532, 533, 556, 534, 535, 536, 512, 511, 488, 487, 510, 509, 508, 486, 485, 484, 483, 460, 461, 462, 463, 464, 441, 440, 439, 438, 437, 414, 415, 416, 417, 418, 395, 419, 420, 421, 397, 396, 374, 373, 372, 371, 394, 393, 391, 368, 392, 369, 370, 347, 346, 345, 322, 323, 299, 300, 324, 348, 325, 326, 349, 350, 351, 352, 328, 327, 304, 303, 302, 301, 277, 278, 279, 256, 281, 280, 282, 305, 283, 284, 306, 329, 307, 330, 331, 308, 309, 310, 311, 334, 333, 332, 354, 355, 356, 357, 336, 335, 312, 313, 290, 289, 288, 287, 286, 285, 262, 261, 260, 259, 258, 257, 233, 234, 212, 235, 236, 237, 213, 214, 215, 216, 194, 193, 192, 191, 190, 189, 188, 187, 186, 211, 210, 209, 232, 231, 255, 254, 276, 253, 230, 207, 208, 185, 184, 161, 162, 139, 138, 140, 117, 94, 116, 115, 93, 92, 70, 69, 46, 23, 24, 0, 1, 2, 3, 5, 6, 29, 7, 8, 9, 10, 33, 34, 12, 11, 13, 14, 16, 17, 40, 41, 18, 42, 19, 43, 44, 20, 21, 22, 45, 68, 91, 67, 66, 65, 64, 86, 85, 84, 83, 82, 81, 59, 60, 61, 62, 63, 39, 15, 38, 37, 36, 35, 58, 57, 56, 32, 31, 30, 52, 51, 28, 27, 4, 26, 25, 47, 48, 49, 50, 73, 72, 71, 95, 118, 119, 120, 143, 142, 141, 163, 164, 165, 166, 144, 167, 168, 169, 170, 171, 172, 149, 148, 147, 146, 145, 121, 123, 122, 100, 99, 98, 97, 96, 74, 75, 76, 77, 53, 54, 55, 79, 78, 80, 103, 101, 102, 125, 124, 126, 150, 127, 129, 151, 152, 153, 177, 155, 154, 132, 131, 130, 128, 104, 105, 106, 107, 108, 109, 87, 88, 89, 112, 90, 114, 137, 113, 111, 110, 133, 134, 135, 157, 158, 136, 160, 159, 182, 183, 206, 205, 228, 204, 203, 180, 181, 156, 179, 178, 202, 201, 200, 176, 175, 174, 173, 195, 196, 220, 197, 198, 199, 221, 223, 224, 225, 248, 226, 227, 229, 252, 251, 250, 249, 271, 270, 247, 246, 245, 222, 244, 243, 242, 219, 218, 217, 240, 238, 239, 263, 264, 241, 265, 266, 267, 268, 269, 272, 273, 274, 275, 298, 297, 321, 320, 296, 295, 317, 294, 293, 292, 291, 314, 315, 316, 339, 338, 337, 361, 360, 359, 382, 358, 380, 379, 378, 377, 353, 375, 376, 398, 399, 400, 401, 402, 403, 404, 381]</t>
+          <t>[15, 38, 37, 36, 35, 58, 57, 56, 55, 78, 79, 81, 82, 59, 60, 61, 62, 63, 64, 65, 66, 67, 68, 91, 89, 88, 111, 112, 90, 113, 114, 137, 160, 159, 136, 158, 157, 135, 134, 110, 133, 108, 109, 87, 86, 85, 84, 83, 106, 107, 130, 131, 132, 154, 155, 156, 179, 178, 202, 201, 225, 226, 227, 228, 204, 203, 180, 181, 182, 183, 206, 205, 229, 252, 251, 274, 275, 298, 297, 320, 321, 344, 343, 319, 318, 342, 341, 364, 365, 367, 366, 389, 390, 412, 388, 411, 410, 387, 409, 386, 408, 407, 406, 405, 428, 427, 426, 425, 448, 449, 450, 451, 474, 473, 496, 497, 498, 499, 477, 478, 456, 455, 454, 453, 476, 475, 452, 429, 430, 431, 432, 433, 434, 435, 413, 436, 459, 458, 457, 481, 482, 505, 528, 527, 526, 548, 549, 550, 551, 574, 573, 572, 571, 570, 569, 568, 546, 547, 524, 525, 503, 504, 480, 479, 502, 501, 500, 523, 522, 521, 520, 543, 545, 567, 544, 566, 565, 542, 541, 564, 563, 562, 539, 538, 561, 560, 535, 559, 558, 557, 556, 534, 533, 532, 555, 554, 552, 553, 530, 531, 529, 506, 507, 508, 509, 486, 510, 487, 488, 511, 512, 536, 537, 516, 540, 517, 519, 518, 495, 494, 472, 471, 470, 447, 446, 445, 467, 468, 469, 493, 492, 515, 514, 513, 491, 490, 489, 465, 466, 442, 443, 444, 422, 423, 424, 401, 402, 403, 404, 381, 383, 384, 385, 362, 363, 340, 339, 338, 337, 361, 360, 359, 382, 358, 380, 379, 378, 377, 353, 352, 351, 375, 374, 396, 397, 376, 400, 399, 398, 421, 420, 419, 440, 441, 464, 463, 485, 484, 483, 460, 461, 462, 439, 438, 437, 414, 415, 416, 417, 418, 395, 394, 371, 393, 392, 391, 368, 369, 370, 372, 373, 350, 349, 326, 325, 348, 347, 346, 345, 322, 323, 324, 299, 300, 301, 302, 303, 304, 327, 328, 329, 306, 305, 280, 282, 283, 284, 307, 330, 331, 332, 354, 355, 356, 357, 336, 335, 312, 334, 333, 311, 310, 309, 308, 286, 287, 288, 289, 290, 313, 314, 315, 316, 317, 293, 294, 295, 296, 272, 273, 250, 249, 271, 270, 269, 292, 291, 268, 267, 266, 265, 241, 264, 263, 262, 285, 261, 260, 259, 257, 258, 281, 256, 279, 278, 277, 276, 254, 253, 230, 207, 208, 185, 186, 187, 188, 211, 210, 209, 232, 231, 255, 233, 234, 212, 235, 236, 213, 214, 237, 238, 239, 240, 217, 218, 219, 242, 243, 244, 222, 245, 246, 247, 248, 224, 223, 221, 199, 198, 197, 220, 196, 195, 173, 174, 175, 176, 200, 177, 153, 152, 151, 150, 127, 129, 128, 104, 105, 80, 103, 101, 102, 125, 124, 123, 121, 120, 143, 142, 166, 144, 167, 168, 169, 145, 146, 147, 126, 148, 149, 172, 171, 170, 193, 194, 216, 215, 192, 191, 190, 189, 165, 164, 163, 162, 184, 161, 139, 138, 141, 140, 117, 118, 119, 98, 122, 100, 99, 77, 76, 75, 74, 97, 96, 95, 94, 116, 115, 93, 92, 70, 69, 46, 23, 0, 1, 2, 3, 4, 26, 25, 24, 47, 48, 71, 72, 73, 50, 49, 27, 28, 51, 52, 53, 54, 31, 30, 29, 7, 6, 5, 8, 9, 10, 32, 33, 34, 12, 11, 13, 14, 16, 17, 19, 20, 21, 22, 45, 44, 43, 42, 18, 41, 40, 39]</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1624,7 +1624,7 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>3.928619146347046</v>
+        <v>3.698168039321899</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
@@ -1648,17 +1648,17 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>65905</v>
+        <v>62314</v>
       </c>
       <c r="E37" t="n">
-        <v>34.74198560680406</v>
+        <v>27.40022898266274</v>
       </c>
       <c r="F37" t="n">
-        <v>0.05018496513366699</v>
+        <v>0.04893684387207031</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>[435, 430, 436, 422, 397, 388, 370, 364, 348, 342, 321, 309, 308, 292, 287, 275, 254, 248, 236, 225, 215, 232, 241, 221, 247, 251, 260, 268, 252, 227, 219, 214, 208, 207, 226, 224, 228, 243, 255, 259, 284, 304, 305, 312, 318, 333, 327, 311, 310, 320, 326, 350, 369, 377, 386, 365, 373, 378, 396, 395, 385, 402, 406, 413, 425, 419, 424, 431, 423, 414, 405, 401, 410, 394, 403, 407, 412, 433, 434, 429, 417, 411, 382, 367, 362, 353, 344, 338, 329, 315, 314, 332, 352, 359, 363, 366, 368, 374, 376, 379, 384, 392, 428, 418, 383, 381, 380, 375, 354, 343, 336, 319, 330, 331, 355, 360, 393, 356, 337, 607, 610, 606, 605, 601, 595, 596, 591, 597, 602, 594, 588, 587, 585, 584, 583, 577, 576, 573, 571, 569, 568, 562, 561, 564, 560, 563, 565, 558, 553, 554, 555, 557, 550, 549, 543, 551, 556, 559, 528, 509, 508, 133, 136, 507, 503, 501, 500, 502, 499, 504, 126, 125, 506, 505, 124, 127, 145, 144, 109, 95, 88, 87, 89, 94, 83, 76, 82, 96, 100, 107, 111, 106, 112, 122, 143, 153, 150, 158, 166, 167, 151, 146, 134, 123, 110, 108, 497, 494, 491, 482, 472, 483, 471, 56, 62, 51, 47, 61, 66, 71, 80, 81, 75, 67, 470, 467, 460, 459, 457, 456, 473, 455, 461, 465, 454, 451, 452, 450, 453, 448, 449, 442, 462, 463, 466, 468, 464, 458, 469, 34, 37, 38, 42, 46, 58, 70, 90, 104, 105, 121, 149, 154, 147, 148, 139, 120, 99, 92, 86, 113, 119, 103, 118, 114, 102, 97, 98, 93, 91, 74, 77, 84, 73, 68, 63, 45, 44, 49, 54, 50, 40, 52, 48, 57, 59, 69, 72, 85, 65, 55, 30, 27, 26, 25, 23, 440, 441, 443, 446, 447, 445, 444, 19, 18, 13, 17, 16, 20, 28, 15, 14, 21, 24, 32, 33, 35, 36, 39, 41, 53, 60, 64, 79, 78, 6, 5, 117, 131, 138, 129, 128, 130, 116, 137, 142, 162, 164, 156, 163, 141, 190, 196, 185, 178, 172, 168, 155, 140, 132, 115, 101, 180, 186, 191, 195, 197, 198, 199, 181, 187, 165, 157, 169, 171, 170, 161, 177, 184, 179, 176, 192, 188, 175, 152, 135, 160, 174, 193, 189, 182, 173, 183, 194, 200, 201, 202, 580, 229, 246, 257, 279, 592, 306, 297, 296, 302, 295, 301, 281, 278, 285, 282, 267, 256, 244, 233, 249, 272, 277, 291, 274, 283, 286, 313, 328, 339, 357, 351, 358, 300, 276, 270, 250, 242, 223, 211, 203, 205, 212, 216, 222, 245, 265, 273, 258, 266, 280, 598, 600, 589, 586, 581, 582, 578, 574, 570, 567, 511, 510, 159, 213, 316, 408, 622, 620, 618, 617, 616, 615, 613, 619, 612, 611, 609, 604, 603, 599, 590, 593, 579, 575, 656, 655, 654, 653, 627, 626, 572, 628, 552, 546, 545, 544, 547, 548, 542, 541, 540, 539, 538, 537, 536, 534, 535, 532, 531, 529, 523, 530, 533, 524, 522, 525, 526, 527, 521, 520, 519, 477, 476, 478, 479, 480, 481, 484, 488, 487, 485, 486, 490, 496, 498, 493, 492, 489, 495, 512, 513, 516, 517, 518, 515, 514, 474, 475, 43, 31, 29, 22, 12, 11, 9, 8, 10, 2, 1, 3, 4, 7, 206, 209, 217, 218, 234, 253, 261, 271, 263, 264, 240, 239, 230, 220, 238, 262, 289, 290, 298, 307, 317, 322, 335, 345, 341, 347, 361, 372, 391, 398, 400, 404, 415, 421, 439, 437, 420, 409, 416, 390, 371, 399, 438, 389, 346, 340, 323, 324, 334, 303, 299, 293, 288, 294, 325, 349, 387, 432, 204, 210, 231, 235, 237, 269, 426, 427, 624, 625, 623, 621, 614, 608, 566, 629, 630, 631, 632, 633, 634, 635, 639, 638, 637, 636, 640, 641, 642, 643, 644, 645, 646, 647, 648, 649, 650, 651, 652, 0]</t>
+          <t>[277, 291, 272, 274, 283, 286, 267, 282, 285, 278, 281, 295, 302, 301, 319, 330, 343, 354, 360, 355, 331, 306, 297, 296, 280, 273, 258, 266, 257, 246, 229, 580, 213, 212, 216, 222, 245, 265, 592, 279, 589, 598, 600, 601, 605, 606, 610, 607, 337, 356, 393, 381, 383, 380, 375, 367, 362, 353, 344, 338, 329, 315, 314, 332, 352, 359, 363, 366, 368, 374, 376, 379, 384, 394, 403, 407, 412, 433, 434, 429, 417, 411, 382, 392, 428, 418, 336, 316, 313, 328, 339, 333, 318, 312, 305, 304, 311, 327, 351, 357, 358, 373, 378, 396, 395, 385, 402, 406, 413, 425, 419, 424, 431, 423, 414, 405, 401, 386, 377, 365, 369, 350, 326, 320, 310, 300, 276, 270, 252, 268, 251, 247, 260, 241, 232, 221, 215, 225, 236, 248, 254, 275, 287, 292, 294, 309, 308, 321, 325, 342, 348, 364, 370, 388, 397, 422, 436, 430, 435, 387, 349, 334, 324, 323, 340, 346, 372, 391, 398, 400, 404, 415, 421, 439, 437, 420, 409, 416, 390, 371, 399, 438, 361, 345, 341, 347, 335, 322, 317, 307, 298, 290, 271, 261, 253, 239, 230, 220, 238, 262, 289, 269, 237, 231, 235, 210, 196, 190, 164, 162, 142, 137, 130, 128, 116, 129, 138, 131, 117, 141, 163, 156, 155, 168, 172, 178, 185, 195, 191, 186, 180, 181, 187, 165, 157, 169, 171, 170, 161, 148, 139, 147, 154, 149, 177, 184, 179, 166, 158, 150, 153, 143, 122, 112, 106, 107, 111, 100, 96, 82, 76, 83, 89, 94, 108, 88, 87, 95, 109, 127, 124, 505, 506, 125, 135, 126, 504, 502, 499, 501, 503, 500, 495, 492, 489, 484, 488, 487, 485, 480, 481, 490, 486, 491, 494, 497, 496, 498, 493, 514, 515, 518, 517, 516, 513, 512, 528, 509, 508, 133, 136, 507, 160, 174, 193, 189, 182, 173, 183, 194, 200, 201, 202, 570, 567, 511, 510, 159, 203, 205, 211, 244, 233, 249, 223, 228, 243, 255, 259, 284, 250, 242, 226, 224, 207, 214, 208, 219, 227, 167, 151, 146, 134, 123, 110, 81, 75, 71, 80, 66, 61, 47, 51, 62, 56, 67, 483, 471, 472, 482, 479, 478, 477, 476, 475, 457, 456, 473, 459, 460, 455, 461, 465, 467, 470, 468, 466, 464, 458, 453, 450, 452, 451, 454, 448, 449, 442, 462, 463, 469, 34, 37, 38, 42, 46, 58, 70, 90, 104, 105, 121, 120, 99, 92, 86, 113, 119, 103, 118, 114, 102, 97, 98, 93, 91, 74, 77, 84, 73, 68, 63, 45, 44, 49, 54, 50, 40, 52, 48, 57, 59, 69, 72, 85, 65, 55, 30, 27, 26, 25, 23, 440, 441, 443, 446, 447, 445, 444, 19, 18, 13, 17, 16, 20, 28, 15, 14, 21, 24, 32, 33, 35, 36, 39, 41, 53, 60, 64, 79, 78, 6, 5, 4, 3, 2, 1, 10, 9, 8, 7, 11, 12, 22, 29, 31, 43, 144, 145, 152, 175, 188, 192, 176, 256, 586, 581, 582, 578, 574, 573, 577, 576, 584, 583, 585, 588, 587, 590, 599, 603, 604, 609, 593, 594, 597, 596, 591, 595, 608, 602, 611, 612, 619, 624, 625, 427, 408, 622, 620, 618, 617, 616, 615, 613, 426, 623, 621, 614, 579, 575, 656, 655, 654, 653, 627, 562, 561, 564, 560, 563, 565, 558, 553, 554, 555, 557, 550, 549, 543, 551, 556, 559, 566, 548, 547, 546, 545, 544, 552, 628, 629, 630, 631, 632, 633, 634, 635, 639, 638, 637, 636, 640, 641, 642, 643, 644, 645, 646, 647, 648, 649, 650, 651, 652, 626, 572, 571, 569, 568, 542, 541, 540, 539, 538, 537, 536, 534, 535, 532, 531, 529, 523, 530, 533, 524, 522, 525, 526, 527, 521, 520, 519, 474, 115, 132, 140, 101, 197, 198, 199, 209, 217, 218, 234, 240, 264, 263, 288, 293, 299, 303, 389, 432, 410, 204, 206, 0]</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1682,17 +1682,17 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>54924</v>
+        <v>53910</v>
       </c>
       <c r="E38" t="n">
-        <v>12.29146221786065</v>
+        <v>10.21835132482826</v>
       </c>
       <c r="F38" t="n">
-        <v>1.810731887817383</v>
+        <v>1.679013967514038</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>[623, 621, 614, 611, 612, 619, 625, 624, 427, 426, 408, 622, 620, 618, 617, 616, 615, 613, 608, 605, 606, 610, 607, 600, 598, 601, 595, 591, 596, 597, 602, 594, 609, 604, 603, 599, 593, 590, 587, 588, 585, 579, 575, 656, 572, 626, 655, 654, 627, 653, 652, 651, 650, 649, 648, 647, 645, 646, 644, 643, 642, 641, 640, 636, 637, 638, 639, 635, 634, 633, 632, 631, 630, 629, 628, 552, 546, 545, 544, 547, 548, 553, 558, 554, 555, 557, 566, 565, 563, 560, 564, 561, 562, 568, 569, 571, 573, 577, 576, 584, 583, 582, 578, 574, 581, 586, 589, 279, 592, 306, 337, 356, 331, 330, 319, 301, 295, 302, 296, 297, 280, 273, 258, 266, 257, 246, 229, 580, 213, 212, 216, 222, 245, 265, 281, 278, 285, 282, 267, 256, 244, 233, 249, 277, 291, 272, 274, 283, 286, 313, 328, 339, 352, 363, 359, 366, 368, 374, 376, 379, 384, 392, 382, 367, 362, 353, 344, 338, 332, 314, 315, 329, 316, 336, 343, 354, 360, 355, 393, 381, 383, 375, 380, 418, 428, 411, 417, 429, 434, 433, 412, 407, 403, 394, 385, 395, 402, 406, 413, 425, 419, 424, 431, 432, 423, 414, 410, 396, 378, 357, 351, 358, 373, 405, 401, 386, 377, 365, 369, 387, 430, 435, 436, 422, 397, 388, 389, 370, 364, 349, 348, 342, 325, 321, 309, 308, 334, 324, 323, 340, 346, 372, 391, 398, 400, 404, 415, 421, 439, 437, 438, 420, 409, 416, 399, 371, 390, 347, 361, 345, 341, 335, 322, 317, 307, 298, 290, 271, 261, 253, 239, 230, 220, 238, 262, 289, 269, 237, 231, 235, 210, 196, 190, 185, 178, 172, 168, 155, 140, 132, 115, 101, 116, 130, 137, 142, 162, 164, 156, 163, 141, 117, 131, 138, 129, 128, 79, 78, 6, 5, 4, 64, 60, 53, 7, 41, 39, 36, 35, 33, 32, 24, 21, 28, 20, 18, 19, 443, 441, 440, 23, 22, 29, 27, 26, 25, 30, 31, 37, 34, 469, 463, 462, 464, 466, 468, 43, 38, 42, 46, 58, 55, 59, 69, 85, 72, 65, 57, 52, 48, 40, 50, 54, 49, 44, 45, 63, 68, 73, 77, 84, 74, 93, 98, 97, 91, 102, 114, 118, 103, 119, 113, 99, 92, 86, 70, 90, 105, 121, 104, 120, 139, 148, 147, 149, 154, 177, 184, 179, 207, 226, 224, 228, 242, 250, 270, 276, 252, 227, 219, 214, 208, 161, 170, 171, 169, 157, 165, 187, 181, 180, 186, 191, 195, 197, 198, 199, 206, 209, 217, 218, 234, 240, 263, 264, 303, 299, 293, 288, 287, 292, 294, 275, 254, 248, 236, 225, 204, 215, 221, 232, 241, 247, 251, 260, 268, 300, 310, 320, 326, 350, 311, 327, 333, 318, 312, 305, 304, 284, 259, 255, 243, 223, 176, 192, 188, 175, 211, 203, 205, 189, 182, 173, 183, 194, 200, 201, 202, 570, 567, 511, 510, 159, 174, 193, 160, 152, 135, 125, 506, 126, 504, 499, 502, 503, 501, 500, 507, 136, 133, 508, 509, 528, 559, 556, 551, 550, 549, 543, 542, 541, 540, 539, 538, 537, 536, 534, 535, 532, 531, 529, 523, 533, 530, 524, 522, 525, 526, 527, 521, 519, 520, 474, 477, 476, 479, 478, 515, 518, 517, 516, 513, 512, 514, 484, 489, 492, 495, 493, 488, 487, 481, 480, 485, 486, 490, 496, 498, 505, 124, 127, 145, 144, 109, 108, 110, 123, 134, 146, 151, 167, 166, 158, 150, 153, 143, 122, 112, 106, 111, 107, 100, 96, 81, 75, 80, 71, 66, 61, 47, 51, 62, 67, 82, 76, 83, 89, 94, 88, 87, 95, 497, 494, 491, 482, 472, 483, 471, 56, 470, 467, 460, 459, 457, 475, 456, 473, 455, 461, 465, 458, 453, 454, 451, 452, 450, 448, 449, 442, 446, 447, 445, 444, 13, 17, 16, 15, 14, 12, 11, 9, 8, 10, 3, 2, 1, 0]</t>
+          <t>[474, 520, 519, 521, 527, 526, 525, 522, 524, 530, 533, 523, 529, 531, 532, 535, 534, 536, 537, 538, 539, 540, 541, 542, 543, 549, 550, 554, 555, 557, 551, 556, 559, 528, 509, 508, 133, 136, 507, 500, 501, 503, 502, 499, 495, 492, 493, 498, 496, 490, 486, 485, 480, 481, 487, 488, 489, 484, 514, 512, 513, 516, 517, 518, 515, 478, 479, 477, 476, 475, 457, 456, 473, 455, 459, 460, 467, 465, 461, 454, 451, 452, 450, 453, 448, 449, 458, 464, 468, 466, 462, 442, 463, 469, 34, 37, 31, 30, 29, 22, 27, 26, 25, 23, 440, 441, 443, 446, 447, 445, 444, 19, 18, 13, 17, 16, 20, 28, 40, 48, 52, 57, 59, 55, 70, 58, 46, 42, 38, 43, 470, 51, 47, 61, 66, 71, 75, 62, 56, 471, 483, 472, 482, 491, 494, 497, 127, 124, 505, 506, 125, 504, 126, 135, 152, 160, 174, 193, 211, 245, 222, 216, 212, 205, 203, 189, 182, 159, 510, 511, 567, 173, 183, 194, 200, 201, 202, 213, 580, 229, 246, 257, 279, 592, 266, 258, 273, 280, 297, 306, 356, 337, 607, 610, 606, 605, 608, 613, 615, 616, 617, 618, 620, 622, 408, 619, 612, 611, 602, 594, 597, 596, 591, 595, 601, 600, 598, 589, 586, 581, 582, 578, 574, 570, 566, 558, 553, 548, 547, 544, 545, 546, 552, 628, 629, 630, 631, 632, 633, 634, 635, 639, 638, 637, 636, 640, 641, 642, 643, 644, 646, 645, 647, 648, 649, 650, 651, 652, 627, 562, 561, 564, 560, 563, 565, 568, 569, 571, 572, 626, 655, 654, 653, 656, 575, 579, 576, 573, 577, 583, 584, 585, 588, 587, 590, 593, 599, 603, 604, 609, 614, 621, 623, 625, 624, 427, 426, 393, 360, 355, 331, 330, 319, 336, 343, 354, 375, 380, 381, 383, 418, 428, 411, 417, 429, 434, 433, 412, 407, 403, 394, 384, 379, 376, 374, 368, 366, 359, 352, 363, 392, 382, 367, 362, 353, 344, 338, 332, 314, 315, 329, 316, 301, 295, 302, 296, 265, 281, 278, 285, 282, 267, 256, 244, 233, 249, 277, 291, 272, 274, 283, 286, 313, 328, 339, 357, 351, 358, 333, 318, 312, 305, 304, 327, 311, 310, 320, 326, 350, 369, 377, 386, 365, 373, 378, 396, 385, 395, 402, 406, 413, 425, 419, 410, 424, 431, 414, 405, 401, 423, 432, 435, 430, 436, 422, 397, 388, 387, 349, 364, 370, 348, 342, 308, 309, 321, 325, 294, 292, 287, 275, 254, 248, 236, 225, 215, 221, 232, 241, 247, 251, 260, 268, 300, 276, 270, 252, 227, 219, 214, 208, 184, 177, 179, 207, 224, 226, 242, 250, 284, 259, 255, 243, 228, 223, 176, 192, 188, 175, 145, 144, 109, 108, 95, 87, 88, 94, 89, 83, 76, 67, 82, 96, 110, 123, 134, 146, 151, 167, 166, 158, 150, 153, 143, 122, 112, 106, 111, 107, 100, 81, 80, 90, 104, 105, 121, 149, 154, 147, 148, 139, 120, 86, 92, 99, 113, 119, 103, 85, 72, 69, 65, 50, 54, 49, 44, 45, 63, 68, 73, 77, 84, 74, 93, 98, 97, 91, 102, 114, 118, 165, 157, 169, 161, 170, 171, 204, 187, 181, 180, 186, 191, 195, 197, 198, 199, 209, 217, 218, 234, 240, 263, 264, 288, 293, 299, 303, 323, 340, 346, 324, 334, 389, 372, 391, 398, 400, 404, 415, 421, 439, 437, 438, 420, 409, 416, 399, 371, 390, 361, 347, 341, 345, 335, 322, 317, 307, 298, 290, 271, 261, 253, 239, 230, 220, 238, 262, 289, 269, 237, 231, 235, 210, 206, 196, 190, 185, 178, 172, 168, 155, 140, 132, 115, 101, 116, 130, 137, 142, 162, 164, 156, 163, 141, 117, 131, 138, 129, 128, 79, 78, 6, 5, 4, 64, 60, 53, 7, 41, 39, 36, 35, 33, 32, 21, 15, 14, 24, 12, 11, 9, 8, 10, 3, 2, 1, 0]</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1716,17 +1716,17 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>61358</v>
+        <v>62012</v>
       </c>
       <c r="E39" t="n">
-        <v>25.44569839712136</v>
+        <v>26.78279358848544</v>
       </c>
       <c r="F39" t="n">
-        <v>60.00003385543823</v>
+        <v>60.00001907348633</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>[421, 415, 404, 400, 389, 398, 391, 372, 361, 345, 341, 347, 335, 322, 317, 307, 298, 290, 271, 261, 253, 239, 230, 220, 238, 262, 289, 269, 237, 231, 235, 210, 196, 190, 164, 162, 142, 137, 130, 128, 116, 129, 138, 131, 117, 141, 163, 156, 155, 168, 172, 178, 185, 195, 191, 186, 180, 181, 187, 165, 157, 169, 171, 170, 161, 148, 139, 147, 154, 149, 177, 184, 179, 166, 158, 150, 153, 143, 122, 112, 106, 107, 111, 100, 96, 82, 76, 83, 89, 94, 108, 88, 87, 95, 109, 127, 124, 505, 506, 125, 135, 126, 504, 502, 499, 501, 503, 500, 495, 492, 489, 484, 488, 487, 485, 480, 481, 490, 486, 491, 494, 497, 496, 498, 493, 514, 515, 518, 517, 516, 513, 512, 528, 509, 508, 133, 136, 507, 160, 174, 193, 189, 182, 173, 183, 194, 200, 201, 213, 580, 229, 246, 257, 279, 592, 306, 297, 296, 302, 295, 301, 285, 278, 281, 282, 267, 256, 244, 233, 249, 272, 277, 291, 274, 283, 286, 314, 315, 329, 338, 344, 353, 362, 367, 382, 392, 411, 417, 429, 434, 433, 412, 407, 403, 394, 379, 376, 374, 368, 366, 359, 363, 352, 332, 328, 313, 339, 333, 318, 312, 305, 304, 311, 327, 351, 357, 358, 373, 378, 396, 395, 385, 402, 406, 413, 425, 419, 424, 431, 423, 414, 405, 401, 386, 377, 365, 369, 350, 326, 320, 310, 300, 276, 270, 252, 247, 251, 268, 260, 241, 232, 221, 215, 225, 236, 248, 254, 275, 287, 292, 294, 309, 308, 321, 325, 342, 348, 364, 370, 388, 397, 422, 436, 430, 435, 387, 349, 334, 324, 323, 340, 346, 303, 299, 293, 288, 264, 263, 234, 218, 209, 217, 240, 206, 197, 198, 199, 204, 118, 114, 102, 97, 98, 91, 93, 74, 77, 84, 73, 68, 63, 45, 44, 49, 54, 50, 40, 52, 48, 57, 59, 69, 72, 85, 103, 119, 113, 99, 92, 86, 90, 104, 121, 105, 80, 71, 66, 61, 47, 51, 62, 56, 67, 483, 471, 472, 482, 479, 478, 477, 476, 475, 457, 456, 473, 459, 460, 455, 461, 465, 467, 470, 468, 466, 464, 458, 453, 450, 452, 451, 454, 448, 449, 442, 462, 463, 469, 34, 37, 38, 42, 46, 58, 70, 43, 31, 30, 27, 26, 25, 23, 440, 441, 443, 446, 447, 445, 444, 19, 18, 13, 17, 16, 20, 28, 15, 14, 21, 24, 32, 33, 35, 36, 39, 41, 53, 60, 64, 79, 78, 6, 5, 4, 3, 2, 1, 10, 8, 9, 7, 11, 12, 22, 29, 55, 65, 115, 132, 140, 101, 120, 75, 81, 110, 123, 134, 146, 151, 167, 176, 192, 188, 175, 152, 145, 144, 211, 203, 205, 212, 216, 222, 245, 265, 273, 258, 266, 280, 331, 355, 360, 354, 343, 330, 319, 336, 316, 375, 380, 383, 381, 393, 418, 428, 384, 410, 432, 439, 437, 420, 409, 416, 390, 371, 399, 438, 227, 219, 214, 208, 207, 226, 224, 228, 243, 255, 259, 284, 250, 242, 223, 159, 510, 511, 559, 556, 551, 550, 549, 543, 554, 555, 557, 566, 565, 563, 560, 564, 561, 562, 568, 569, 571, 572, 626, 655, 654, 653, 627, 651, 650, 649, 647, 648, 652, 628, 552, 546, 545, 544, 547, 548, 553, 558, 570, 567, 202, 581, 586, 589, 598, 600, 601, 605, 606, 610, 607, 337, 356, 615, 616, 617, 618, 620, 622, 408, 427, 426, 624, 625, 619, 612, 611, 602, 597, 596, 591, 595, 608, 613, 614, 621, 623, 609, 604, 603, 599, 593, 590, 587, 588, 594, 584, 583, 577, 576, 573, 574, 578, 582, 585, 579, 575, 656, 629, 630, 631, 632, 633, 634, 635, 639, 638, 637, 636, 640, 641, 642, 643, 644, 645, 646, 536, 537, 538, 539, 540, 541, 542, 535, 534, 532, 531, 529, 523, 530, 533, 524, 522, 525, 526, 527, 521, 520, 519, 474, 0]</t>
+          <t>[379, 374, 368, 376, 384, 394, 403, 407, 412, 433, 434, 429, 417, 392, 382, 367, 362, 353, 344, 338, 329, 315, 314, 332, 352, 359, 363, 366, 339, 328, 313, 286, 283, 274, 272, 277, 291, 249, 233, 244, 267, 256, 282, 285, 278, 281, 301, 295, 302, 319, 330, 343, 354, 360, 355, 331, 306, 280, 297, 296, 273, 258, 266, 257, 246, 229, 580, 213, 212, 216, 222, 245, 265, 592, 279, 589, 598, 600, 601, 605, 606, 610, 607, 337, 356, 393, 381, 383, 380, 375, 336, 316, 411, 428, 418, 426, 408, 622, 620, 618, 617, 616, 615, 613, 619, 612, 611, 602, 597, 596, 608, 595, 591, 594, 588, 587, 585, 584, 583, 576, 577, 573, 571, 569, 568, 562, 627, 561, 564, 563, 560, 558, 553, 554, 550, 557, 555, 549, 543, 551, 556, 559, 528, 509, 508, 133, 136, 507, 500, 126, 501, 504, 502, 499, 498, 125, 506, 505, 127, 124, 145, 144, 109, 95, 87, 88, 89, 94, 83, 76, 82, 96, 100, 107, 111, 106, 112, 122, 143, 153, 150, 158, 166, 167, 151, 146, 134, 108, 110, 123, 497, 494, 491, 482, 472, 483, 471, 56, 62, 51, 47, 61, 66, 71, 80, 81, 75, 67, 470, 467, 455, 460, 456, 473, 457, 459, 461, 465, 454, 451, 452, 450, 453, 448, 449, 442, 463, 462, 464, 458, 466, 468, 469, 34, 37, 38, 42, 46, 58, 70, 90, 104, 105, 121, 149, 154, 147, 148, 139, 120, 99, 92, 86, 113, 119, 103, 118, 114, 102, 91, 98, 97, 93, 84, 77, 74, 73, 68, 63, 45, 44, 49, 54, 50, 40, 48, 52, 55, 59, 69, 72, 85, 65, 57, 30, 27, 26, 25, 23, 440, 441, 443, 446, 447, 445, 444, 19, 18, 13, 17, 16, 20, 28, 21, 14, 15, 24, 32, 33, 35, 36, 39, 41, 53, 64, 8, 7, 60, 6, 5, 78, 131, 117, 141, 142, 128, 130, 116, 137, 129, 138, 162, 164, 163, 156, 190, 196, 191, 172, 168, 155, 140, 132, 101, 115, 180, 186, 178, 195, 197, 198, 199, 181, 187, 165, 157, 169, 171, 170, 161, 177, 179, 184, 208, 214, 219, 227, 252, 268, 276, 270, 250, 242, 226, 224, 228, 243, 255, 259, 284, 304, 305, 312, 318, 333, 327, 311, 310, 320, 326, 350, 369, 386, 377, 365, 373, 378, 396, 395, 385, 402, 406, 413, 425, 419, 424, 431, 423, 410, 414, 401, 405, 432, 435, 430, 436, 422, 397, 388, 370, 364, 348, 342, 308, 309, 321, 292, 287, 275, 254, 248, 236, 225, 215, 221, 241, 232, 247, 251, 260, 294, 325, 349, 387, 358, 351, 357, 300, 207, 223, 176, 192, 188, 175, 135, 152, 160, 174, 193, 189, 182, 173, 183, 194, 200, 201, 202, 570, 567, 511, 510, 159, 203, 205, 211, 496, 493, 490, 486, 485, 480, 481, 484, 488, 487, 489, 492, 503, 495, 514, 515, 518, 517, 516, 512, 513, 519, 520, 521, 527, 526, 525, 522, 524, 530, 533, 529, 531, 532, 535, 534, 536, 537, 538, 539, 540, 541, 542, 544, 545, 546, 547, 548, 552, 628, 629, 630, 631, 632, 633, 634, 635, 639, 638, 637, 636, 640, 641, 642, 643, 644, 645, 646, 647, 648, 649, 650, 651, 652, 653, 654, 655, 626, 572, 575, 656, 579, 590, 593, 603, 599, 604, 609, 614, 621, 623, 625, 624, 427, 586, 581, 582, 578, 574, 565, 566, 523, 474, 477, 478, 479, 476, 475, 43, 31, 29, 22, 12, 11, 2, 0, 1, 10, 9, 3, 4, 79, 185, 209, 217, 218, 234, 240, 261, 253, 271, 264, 263, 239, 230, 220, 238, 262, 289, 290, 298, 307, 317, 322, 335, 345, 341, 347, 361, 372, 391, 389, 400, 415, 404, 421, 439, 437, 420, 438, 416, 390, 371, 399, 409, 398, 346, 340, 323, 324, 334, 303, 299, 293, 204, 206, 210, 235, 231, 237, 269, 288]</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1750,17 +1750,17 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>50372</v>
+        <v>50094</v>
       </c>
       <c r="E40" t="n">
-        <v>2.984952567877003</v>
+        <v>2.416584887144259</v>
       </c>
       <c r="F40" t="n">
-        <v>4.497404098510742</v>
+        <v>4.537860155105591</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>[84, 74, 77, 73, 68, 63, 45, 44, 49, 54, 50, 40, 65, 72, 85, 69, 59, 57, 52, 48, 55, 86, 92, 99, 113, 119, 103, 118, 114, 102, 91, 97, 98, 93, 115, 140, 132, 101, 116, 137, 142, 130, 128, 129, 138, 131, 117, 141, 163, 156, 164, 162, 155, 168, 172, 178, 185, 190, 196, 210, 235, 231, 237, 269, 289, 262, 238, 239, 230, 220, 218, 234, 253, 261, 271, 290, 298, 307, 317, 322, 335, 345, 341, 347, 371, 399, 390, 416, 409, 420, 438, 437, 439, 421, 415, 404, 400, 389, 398, 391, 372, 361, 340, 346, 334, 324, 323, 303, 299, 293, 288, 264, 263, 240, 217, 209, 206, 199, 198, 197, 195, 191, 186, 180, 181, 187, 165, 157, 204, 215, 225, 236, 248, 254, 275, 287, 292, 294, 325, 321, 309, 308, 342, 348, 349, 364, 370, 388, 397, 422, 436, 435, 430, 387, 386, 377, 365, 369, 350, 326, 320, 310, 300, 276, 270, 268, 260, 241, 232, 221, 247, 251, 252, 227, 219, 214, 208, 207, 224, 226, 242, 250, 243, 228, 223, 255, 259, 284, 305, 304, 311, 327, 312, 318, 333, 357, 351, 358, 373, 378, 396, 410, 414, 405, 401, 432, 423, 431, 424, 419, 425, 413, 406, 402, 395, 385, 394, 403, 407, 412, 433, 434, 429, 417, 411, 428, 418, 393, 381, 383, 380, 375, 353, 344, 338, 362, 367, 382, 392, 384, 379, 376, 374, 368, 366, 359, 363, 352, 339, 328, 313, 332, 314, 315, 329, 316, 336, 343, 354, 360, 355, 356, 337, 607, 610, 606, 605, 608, 595, 601, 600, 598, 589, 586, 581, 582, 578, 574, 573, 577, 576, 583, 584, 585, 588, 594, 591, 596, 597, 602, 611, 612, 619, 613, 615, 616, 617, 618, 620, 622, 408, 426, 427, 624, 625, 623, 621, 614, 609, 604, 603, 599, 593, 590, 587, 579, 575, 656, 655, 654, 626, 572, 571, 569, 568, 627, 653, 652, 651, 650, 649, 648, 647, 645, 646, 644, 643, 642, 641, 640, 636, 637, 638, 639, 635, 634, 633, 632, 631, 630, 629, 628, 552, 562, 561, 564, 560, 565, 563, 558, 553, 548, 547, 546, 545, 544, 542, 541, 540, 539, 538, 537, 536, 534, 535, 532, 531, 529, 523, 533, 530, 524, 522, 525, 526, 527, 521, 519, 520, 474, 475, 476, 477, 478, 479, 472, 482, 491, 494, 497, 498, 496, 490, 486, 485, 480, 481, 487, 488, 493, 495, 492, 489, 484, 514, 515, 518, 517, 516, 513, 512, 528, 559, 556, 551, 543, 549, 550, 554, 555, 557, 566, 570, 567, 511, 173, 183, 194, 200, 201, 202, 213, 580, 229, 246, 257, 279, 592, 306, 331, 330, 319, 301, 295, 302, 296, 297, 280, 266, 258, 273, 265, 281, 278, 285, 282, 267, 256, 286, 283, 274, 272, 291, 277, 249, 233, 244, 211, 245, 222, 216, 212, 205, 203, 189, 182, 159, 510, 509, 508, 500, 501, 503, 502, 499, 504, 126, 507, 133, 136, 160, 174, 193, 152, 135, 125, 506, 505, 124, 127, 144, 145, 175, 188, 192, 176, 151, 167, 153, 143, 150, 158, 166, 179, 184, 177, 154, 149, 147, 161, 170, 171, 169, 148, 139, 120, 104, 90, 70, 58, 46, 42, 38, 43, 47, 61, 66, 71, 75, 81, 80, 105, 121, 112, 122, 106, 111, 107, 100, 82, 96, 110, 123, 146, 134, 109, 95, 87, 88, 108, 94, 89, 83, 76, 67, 483, 471, 56, 62, 51, 470, 467, 465, 461, 460, 459, 457, 456, 473, 455, 454, 451, 452, 450, 453, 448, 449, 458, 464, 466, 468, 469, 34, 37, 31, 463, 462, 442, 446, 447, 443, 441, 440, 23, 25, 26, 27, 30, 29, 22, 445, 444, 19, 18, 13, 17, 16, 20, 28, 15, 14, 21, 24, 12, 11, 9, 8, 7, 33, 32, 35, 36, 39, 41, 53, 60, 64, 79, 78, 6, 5, 4, 3, 10, 2, 1, 0]</t>
+          <t>[594, 590, 593, 599, 603, 604, 609, 614, 621, 623, 619, 625, 624, 427, 426, 408, 622, 620, 618, 617, 616, 615, 613, 612, 611, 608, 605, 606, 610, 607, 337, 356, 355, 360, 354, 375, 380, 383, 381, 393, 418, 428, 411, 417, 429, 434, 433, 412, 407, 403, 394, 385, 395, 396, 402, 406, 413, 425, 424, 419, 410, 414, 431, 423, 432, 405, 401, 378, 373, 358, 351, 357, 333, 327, 311, 318, 312, 305, 304, 284, 259, 255, 243, 228, 223, 249, 277, 291, 272, 274, 283, 286, 313, 328, 339, 359, 352, 363, 366, 368, 374, 376, 379, 384, 392, 382, 367, 362, 353, 344, 338, 332, 314, 315, 329, 316, 336, 343, 319, 330, 331, 306, 592, 297, 296, 302, 295, 301, 281, 278, 285, 282, 267, 256, 244, 233, 211, 193, 174, 160, 136, 133, 508, 509, 510, 159, 182, 189, 203, 205, 212, 216, 222, 245, 265, 273, 280, 258, 266, 257, 246, 229, 580, 213, 202, 201, 200, 194, 183, 173, 511, 567, 570, 566, 557, 555, 554, 550, 549, 543, 551, 556, 559, 528, 512, 513, 516, 517, 518, 514, 515, 478, 479, 472, 471, 483, 482, 491, 494, 497, 496, 498, 493, 490, 486, 485, 480, 481, 487, 488, 484, 489, 492, 495, 500, 501, 503, 507, 126, 504, 502, 499, 506, 125, 135, 152, 175, 188, 192, 176, 146, 134, 144, 145, 127, 124, 505, 109, 95, 87, 88, 108, 123, 110, 96, 100, 107, 111, 106, 105, 121, 112, 122, 143, 151, 167, 153, 150, 158, 166, 179, 184, 177, 154, 149, 147, 139, 148, 161, 170, 171, 169, 157, 165, 187, 204, 215, 225, 236, 248, 275, 287, 292, 294, 254, 241, 232, 221, 247, 251, 260, 268, 252, 227, 219, 214, 208, 207, 224, 226, 242, 250, 270, 276, 300, 310, 320, 326, 350, 369, 365, 377, 386, 387, 430, 435, 436, 422, 397, 388, 370, 364, 349, 348, 342, 325, 321, 309, 308, 288, 293, 299, 303, 323, 324, 334, 346, 340, 335, 345, 361, 372, 391, 398, 389, 400, 404, 415, 421, 439, 437, 438, 420, 409, 416, 390, 399, 371, 347, 341, 322, 317, 307, 298, 290, 262, 289, 269, 237, 231, 235, 210, 220, 230, 238, 239, 253, 261, 271, 263, 264, 240, 234, 217, 209, 218, 206, 199, 198, 197, 195, 191, 181, 180, 186, 185, 178, 168, 172, 196, 190, 164, 162, 155, 140, 115, 132, 137, 142, 156, 163, 141, 117, 131, 138, 129, 128, 130, 116, 101, 84, 77, 73, 68, 63, 74, 93, 98, 97, 91, 102, 114, 118, 119, 113, 103, 85, 72, 65, 57, 59, 52, 48, 55, 69, 86, 92, 99, 120, 104, 90, 70, 58, 61, 66, 71, 80, 81, 75, 82, 94, 89, 83, 76, 67, 56, 62, 51, 47, 43, 38, 42, 46, 37, 34, 469, 31, 30, 27, 26, 25, 440, 23, 22, 29, 40, 50, 54, 49, 44, 45, 41, 39, 36, 35, 32, 33, 7, 53, 60, 64, 79, 78, 6, 5, 4, 3, 0, 1, 2, 10, 8, 9, 11, 12, 24, 21, 14, 15, 28, 20, 16, 17, 13, 18, 19, 444, 445, 447, 443, 441, 446, 442, 463, 462, 466, 468, 464, 458, 449, 448, 453, 450, 452, 451, 454, 461, 465, 470, 467, 460, 459, 455, 473, 456, 457, 475, 476, 477, 474, 520, 519, 521, 527, 526, 525, 522, 524, 530, 533, 523, 529, 531, 532, 535, 534, 536, 537, 538, 539, 540, 541, 542, 544, 545, 546, 547, 548, 553, 558, 563, 565, 560, 564, 561, 562, 568, 569, 571, 572, 626, 627, 649, 650, 651, 628, 552, 629, 630, 631, 632, 633, 635, 634, 636, 637, 638, 639, 640, 641, 642, 643, 644, 646, 645, 647, 648, 652, 653, 654, 655, 656, 575, 579, 587, 588, 585, 584, 583, 576, 577, 573, 574, 578, 582, 581, 586, 589, 279, 598, 600, 601, 595, 591, 596, 597, 602]</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1790,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>5.124148845672607</v>
+        <v>4.870475053787231</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
@@ -1814,17 +1814,17 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11267</v>
+        <v>11244</v>
       </c>
       <c r="E42" t="n">
-        <v>27.94685441744265</v>
+        <v>27.68566886213945</v>
       </c>
       <c r="F42" t="n">
-        <v>0.07969903945922852</v>
+        <v>0.0596611499786377</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>[370, 364, 352, 345, 338, 322, 318, 326, 334, 316, 293, 301, 288, 304, 312, 327, 343, 357, 365, 388, 391, 404, 425, 429, 423, 419, 407, 408, 409, 418, 416, 410, 417, 433, 436, 447, 440, 434, 430, 438, 456, 455, 448, 459, 472, 476, 482, 490, 499, 500, 506, 504, 520, 535, 534, 540, 541, 557, 564, 569, 576, 583, 590, 586, 602, 608, 621, 635, 629, 632, 613, 600, 599, 604, 588, 609, 617, 638, 630, 653, 652, 645, 650, 665, 668, 660, 648, 656, 680, 690, 691, 697, 712, 706, 718, 719, 720, 725, 739, 747, 765, 773, 772, 776, 778, 767, 756, 758, 757, 742, 738, 731, 735, 744, 734, 717, 704, 708, 687, 677, 670, 678, 684, 679, 689, 674, 659, 654, 644, 647, 651, 658, 664, 671, 682, 696, 703, 724, 733, 737, 746, 760, 771, 764, 759, 775, 732, 736, 753, 754, 748, 749, 762, 769, 761, 726, 729, 730, 722, 740, 745, 741, 751, 755, 763, 750, 727, 714, 702, 695, 693, 669, 675, 673, 667, 666, 663, 672, 661, 649, 641, 631, 628, 614, 603, 605, 592, 581, 591, 594, 607, 601, 584, 582, 573, 566, 548, 545, 537, 549, 554, 522, 515, 503, 502, 509, 497, 501, 508, 524, 527, 536, 543, 531, 544, 558, 572, 571, 570, 574, 542, 526, 521, 523, 513, 519, 492, 488, 479, 473, 486, 496, 495, 493, 475, 463, 469, 468, 466, 514, 512, 518, 517, 530, 539, 546, 538, 560, 568, 561, 578, 585, 593, 579, 567, 575, 559, 547, 532, 525, 510, 498, 471, 481, 483, 484, 465, 457, 451, 452, 444, 435, 428, 422, 400, 389, 386, 381, 396, 406, 424, 442, 437, 421, 432, 454, 462, 485, 491, 507, 511, 516, 505, 529, 533, 550, 553, 596, 597, 589, 598, 587, 577, 565, 562, 563, 555, 528, 551, 556, 612, 618, 640, 643, 633, 626, 611, 610, 625, 637, 639, 623, 595, 616, 627, 620, 606, 683, 698, 694, 685, 709, 699, 700, 688, 692, 707, 701, 715, 723, 716, 713, 710, 711, 728, 743, 752, 766, 770, 774, 782, 781, 780, 779, 686, 681, 676, 657, 655, 662, 642, 634, 624, 622, 619, 615, 636, 646, 580, 552, 487, 474, 464, 449, 445, 431, 413, 414, 399, 401, 415, 385, 380, 379, 374, 359, 353, 350, 347, 339, 337, 336, 348, 360, 361, 341, 333, 323, 319, 297, 308, 295, 296, 303, 313, 314, 328, 340, 354, 356, 366, 393, 412, 405, 403, 398, 395, 378, 377, 397, 411, 402, 387, 384, 367, 372, 382, 363, 325, 317, 311, 300, 286, 281, 282, 287, 307, 309, 262, 259, 243, 228, 227, 219, 202, 188, 190, 196, 187, 182, 200, 212, 220, 225, 236, 250, 252, 261, 274, 256, 294, 310, 302, 291, 280, 268, 249, 232, 231, 239, 257, 258, 267, 255, 266, 285, 298, 290, 305, 292, 306, 299, 289, 315, 331, 324, 349, 346, 344, 332, 320, 321, 329, 335, 371, 369, 376, 392, 375, 390, 458, 439, 446, 453, 450, 470, 480, 478, 460, 461, 443, 441, 427, 420, 426, 467, 477, 489, 373, 368, 330, 283, 278, 260, 244, 251, 240, 270, 271, 246, 237, 217, 213, 222, 206, 191, 177, 173, 165, 157, 144, 147, 141, 121, 113, 108, 105, 100, 78, 83, 86, 74, 65, 72, 90, 95, 103, 112, 118, 130, 131, 140, 129, 128, 143, 149, 125, 120, 123, 117, 137, 156, 168, 162, 175, 178, 197, 199, 205, 216, 224, 211, 210, 208, 218, 209, 172, 164, 163, 181, 189, 139, 127, 111, 115, 132, 136, 142, 151, 160, 161, 155, 150, 135, 126, 152, 159, 154, 146, 138, 122, 116, 109, 114, 99, 79, 69, 66, 80, 93, 82, 75, 97, 94, 88, 73, 76, 63, 70, 84, 98, 101, 104, 107, 85, 81, 61, 49, 53, 41, 50, 31, 25, 20, 15, 26, 23, 27, 33, 42, 37, 39, 5, 12, 10, 3, 59, 54, 43, 68, 77, 89, 92, 91, 102, 71, 67, 60, 58, 35, 19, 7, 18, 29, 4, 2, 9, 8, 11, 17, 6, 1, 22, 16, 36, 44, 56, 51, 48, 55, 87, 96, 106, 110, 119, 64, 46, 52, 57, 62, 38, 28, 32, 47, 30, 21, 34, 13, 153, 158, 166, 167, 169, 180, 176, 193, 198, 192, 170, 148, 133, 134, 233, 253, 264, 263, 279, 284, 223, 207, 201, 203, 186, 183, 195, 194, 174, 179, 185, 171, 184, 214, 215, 235, 241, 234, 238, 245, 254, 275, 276, 269, 265, 229, 230, 226, 221, 248, 247, 273, 272, 277, 242, 204, 145, 124, 40, 45, 24, 14, 0, 342, 351, 358, 355, 362, 383, 394, 494, 705, 721, 768, 777]</t>
+          <t>[552, 558, 572, 571, 570, 574, 564, 569, 576, 583, 590, 586, 602, 608, 621, 635, 629, 632, 613, 600, 599, 604, 588, 609, 617, 638, 630, 653, 652, 645, 650, 665, 668, 660, 648, 656, 680, 690, 691, 697, 712, 706, 718, 719, 720, 725, 739, 747, 765, 773, 772, 776, 778, 767, 756, 758, 757, 742, 738, 731, 735, 744, 734, 717, 704, 708, 687, 677, 670, 678, 684, 679, 689, 674, 659, 654, 644, 647, 651, 658, 664, 671, 682, 696, 703, 724, 733, 737, 746, 760, 771, 764, 759, 775, 732, 736, 753, 754, 748, 749, 762, 769, 761, 726, 729, 730, 722, 740, 745, 741, 751, 755, 763, 750, 727, 714, 702, 695, 693, 669, 675, 673, 667, 666, 663, 672, 661, 649, 641, 631, 628, 614, 603, 605, 592, 581, 591, 594, 607, 601, 584, 582, 573, 566, 548, 545, 537, 549, 554, 522, 515, 503, 502, 509, 497, 501, 508, 524, 527, 536, 543, 531, 544, 519, 513, 523, 521, 526, 542, 557, 541, 540, 535, 534, 555, 563, 562, 565, 577, 587, 598, 589, 597, 596, 585, 593, 579, 567, 575, 559, 547, 532, 525, 510, 498, 471, 481, 483, 484, 465, 457, 451, 452, 444, 435, 428, 422, 400, 389, 386, 381, 396, 406, 424, 442, 437, 421, 432, 425, 429, 423, 419, 407, 408, 409, 418, 416, 410, 417, 433, 436, 447, 440, 434, 430, 438, 456, 455, 448, 459, 472, 476, 482, 490, 499, 500, 506, 504, 520, 493, 495, 496, 486, 488, 479, 473, 458, 445, 431, 413, 414, 399, 401, 415, 385, 380, 379, 374, 359, 353, 350, 347, 339, 337, 336, 348, 360, 361, 341, 333, 323, 319, 297, 308, 295, 296, 303, 313, 314, 328, 340, 354, 356, 366, 393, 412, 405, 403, 398, 395, 378, 377, 397, 411, 402, 387, 384, 367, 372, 382, 363, 325, 317, 311, 300, 286, 281, 282, 287, 307, 309, 262, 259, 243, 228, 227, 219, 202, 188, 190, 196, 187, 182, 200, 212, 220, 225, 236, 250, 252, 261, 274, 256, 294, 310, 302, 291, 280, 268, 249, 232, 231, 239, 257, 258, 267, 255, 266, 285, 298, 290, 305, 292, 306, 299, 289, 315, 331, 324, 322, 318, 326, 334, 316, 293, 301, 288, 304, 312, 327, 343, 357, 365, 370, 364, 352, 345, 338, 349, 346, 344, 332, 320, 321, 329, 335, 371, 369, 376, 392, 375, 391, 388, 404, 454, 462, 485, 491, 507, 511, 516, 505, 529, 533, 550, 553, 561, 578, 568, 560, 538, 539, 546, 530, 517, 518, 512, 514, 528, 551, 556, 612, 618, 640, 643, 633, 626, 611, 610, 625, 637, 639, 623, 595, 616, 627, 620, 606, 683, 698, 694, 685, 709, 699, 700, 688, 692, 707, 701, 715, 723, 716, 713, 710, 711, 728, 743, 752, 766, 770, 774, 782, 781, 780, 779, 686, 681, 676, 657, 655, 662, 642, 634, 624, 622, 619, 615, 636, 646, 580, 492, 487, 474, 464, 449, 439, 446, 453, 450, 470, 480, 478, 460, 461, 443, 441, 427, 420, 426, 467, 477, 489, 373, 368, 330, 283, 278, 260, 244, 251, 240, 270, 271, 246, 237, 217, 213, 222, 206, 191, 177, 173, 165, 157, 144, 147, 141, 121, 113, 108, 105, 100, 78, 83, 86, 74, 65, 72, 90, 95, 103, 112, 118, 130, 131, 140, 129, 128, 143, 149, 125, 120, 123, 117, 137, 156, 168, 162, 175, 178, 197, 199, 205, 216, 224, 211, 210, 208, 218, 209, 172, 164, 163, 181, 189, 139, 127, 111, 115, 132, 136, 142, 151, 160, 161, 155, 150, 135, 126, 152, 159, 154, 146, 138, 122, 116, 109, 114, 99, 79, 69, 66, 80, 93, 82, 75, 97, 94, 88, 73, 76, 63, 70, 84, 98, 101, 104, 107, 85, 81, 61, 49, 53, 41, 50, 31, 25, 20, 15, 26, 23, 27, 33, 42, 37, 39, 5, 12, 10, 3, 59, 54, 43, 68, 77, 89, 92, 91, 102, 71, 67, 60, 58, 35, 19, 7, 18, 29, 4, 2, 9, 8, 11, 17, 6, 1, 22, 16, 36, 44, 56, 51, 48, 55, 87, 96, 106, 110, 119, 64, 46, 52, 57, 62, 38, 28, 32, 47, 30, 21, 34, 13, 153, 158, 166, 167, 169, 180, 176, 193, 198, 192, 170, 148, 133, 134, 233, 253, 264, 263, 279, 284, 390, 463, 469, 468, 466, 475, 494, 394, 383, 362, 351, 342, 355, 358, 276, 275, 254, 245, 238, 235, 241, 234, 214, 215, 204, 194, 195, 183, 186, 201, 207, 223, 242, 248, 247, 230, 229, 226, 221, 203, 174, 179, 185, 171, 184, 145, 124, 40, 45, 24, 14, 0, 265, 269, 272, 277, 273, 705, 721, 768, 777]</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -1848,17 +1848,17 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>9435</v>
+        <v>9318</v>
       </c>
       <c r="E43" t="n">
-        <v>7.142857142857142</v>
+        <v>5.814217578923461</v>
       </c>
       <c r="F43" t="n">
-        <v>1.8973228931427</v>
+        <v>1.667813062667847</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>[703, 696, 677, 670, 654, 659, 643, 640, 618, 612, 598, 587, 577, 565, 562, 563, 555, 576, 569, 564, 557, 541, 540, 535, 534, 520, 504, 506, 500, 528, 551, 517, 518, 514, 512, 494, 472, 476, 482, 490, 499, 466, 468, 469, 463, 475, 493, 495, 496, 486, 488, 479, 473, 458, 447, 440, 434, 430, 438, 456, 455, 448, 459, 432, 421, 425, 429, 423, 419, 404, 391, 388, 396, 406, 400, 389, 386, 381, 355, 358, 342, 327, 343, 357, 365, 370, 364, 375, 392, 407, 408, 409, 418, 416, 410, 417, 433, 436, 415, 401, 399, 414, 413, 431, 445, 449, 464, 474, 487, 492, 513, 519, 523, 521, 526, 542, 552, 558, 572, 571, 570, 574, 588, 604, 613, 600, 599, 583, 590, 586, 602, 608, 606, 616, 627, 620, 621, 635, 629, 632, 630, 638, 617, 609, 614, 628, 631, 641, 649, 663, 672, 661, 653, 652, 645, 650, 665, 668, 660, 648, 656, 680, 691, 690, 697, 721, 738, 742, 731, 705, 689, 674, 679, 684, 678, 687, 708, 704, 717, 735, 744, 734, 746, 733, 724, 737, 768, 777, 760, 771, 764, 759, 757, 775, 758, 756, 767, 778, 776, 772, 773, 765, 747, 739, 725, 720, 709, 694, 698, 719, 718, 754, 753, 736, 732, 712, 706, 683, 685, 688, 699, 700, 692, 726, 729, 730, 722, 740, 745, 749, 748, 761, 762, 769, 779, 780, 781, 782, 774, 770, 766, 752, 743, 750, 763, 755, 751, 741, 715, 707, 701, 693, 695, 702, 714, 723, 727, 716, 728, 711, 713, 710, 686, 681, 676, 657, 655, 619, 622, 624, 634, 642, 662, 669, 675, 673, 667, 666, 646, 636, 615, 605, 603, 580, 592, 581, 591, 594, 607, 601, 584, 582, 573, 566, 548, 544, 531, 543, 536, 527, 524, 508, 501, 497, 509, 545, 537, 549, 554, 522, 515, 503, 502, 489, 478, 480, 470, 477, 467, 453, 446, 439, 426, 450, 441, 460, 461, 443, 427, 420, 395, 398, 393, 412, 405, 403, 366, 356, 354, 340, 368, 373, 378, 377, 397, 411, 402, 387, 384, 367, 372, 382, 363, 347, 339, 337, 336, 348, 360, 361, 341, 330, 333, 323, 319, 297, 308, 295, 296, 303, 328, 313, 314, 284, 279, 264, 263, 246, 260, 278, 283, 271, 270, 240, 251, 244, 237, 253, 233, 217, 198, 192, 170, 134, 133, 148, 141, 121, 113, 108, 105, 100, 78, 83, 86, 74, 65, 72, 95, 90, 103, 112, 118, 130, 131, 144, 147, 167, 169, 176, 180, 193, 213, 222, 206, 191, 177, 173, 165, 157, 166, 158, 153, 140, 129, 128, 102, 91, 81, 85, 67, 58, 60, 49, 61, 53, 41, 50, 71, 92, 89, 77, 68, 43, 54, 59, 33, 42, 37, 39, 5, 12, 10, 3, 27, 23, 26, 25, 20, 15, 31, 13, 21, 34, 30, 35, 19, 7, 29, 18, 4, 2, 9, 8, 11, 32, 28, 38, 62, 57, 52, 46, 64, 45, 40, 17, 6, 1, 22, 16, 0, 14, 24, 55, 48, 51, 36, 44, 56, 69, 66, 80, 79, 99, 96, 87, 109, 116, 122, 114, 126, 152, 135, 150, 155, 161, 160, 151, 142, 136, 132, 115, 119, 110, 106, 93, 82, 75, 97, 94, 88, 73, 76, 47, 63, 70, 84, 98, 101, 104, 107, 111, 127, 139, 137, 117, 125, 120, 123, 143, 149, 164, 163, 156, 168, 162, 175, 178, 197, 207, 223, 242, 226, 221, 203, 201, 186, 183, 195, 194, 174, 159, 154, 146, 138, 124, 145, 171, 179, 185, 184, 214, 234, 241, 265, 269, 276, 275, 277, 272, 254, 245, 238, 235, 215, 204, 229, 230, 247, 248, 273, 298, 324, 331, 315, 306, 299, 289, 292, 305, 290, 285, 266, 255, 267, 257, 258, 239, 231, 232, 249, 268, 280, 291, 302, 310, 294, 274, 256, 261, 252, 250, 236, 225, 220, 212, 200, 209, 218, 208, 210, 211, 224, 216, 205, 199, 189, 181, 172, 182, 187, 196, 190, 188, 202, 219, 227, 228, 243, 259, 262, 282, 287, 307, 309, 281, 286, 300, 311, 317, 325, 350, 353, 359, 374, 379, 380, 385, 390, 376, 369, 371, 335, 329, 321, 320, 332, 344, 346, 349, 352, 345, 338, 322, 318, 326, 334, 316, 293, 301, 288, 304, 312, 351, 362, 383, 394, 422, 428, 435, 471, 498, 481, 483, 484, 465, 457, 452, 451, 444, 424, 442, 437, 454, 462, 485, 491, 507, 511, 516, 533, 529, 505, 510, 525, 532, 547, 559, 575, 595, 623, 639, 637, 625, 610, 593, 585, 579, 567, 550, 553, 561, 578, 568, 560, 538, 530, 539, 546, 556, 589, 597, 596, 611, 626, 633, 644, 647, 651, 658, 664, 671, 682]</t>
+          <t>[757, 742, 738, 731, 721, 705, 684, 679, 689, 697, 690, 691, 680, 674, 659, 643, 640, 618, 648, 656, 660, 668, 665, 650, 645, 635, 629, 632, 613, 604, 600, 599, 583, 590, 586, 602, 608, 621, 620, 627, 616, 606, 577, 565, 562, 563, 555, 576, 569, 564, 557, 541, 540, 535, 534, 520, 504, 506, 500, 466, 499, 490, 482, 476, 472, 459, 448, 455, 456, 438, 468, 469, 463, 475, 493, 495, 496, 486, 488, 479, 473, 458, 447, 440, 434, 430, 409, 408, 407, 392, 376, 369, 371, 390, 418, 416, 410, 417, 433, 436, 415, 401, 399, 414, 413, 431, 445, 449, 464, 474, 487, 492, 513, 519, 523, 521, 526, 542, 552, 558, 572, 571, 570, 574, 588, 609, 617, 638, 630, 652, 653, 661, 649, 641, 631, 628, 614, 603, 580, 592, 605, 615, 636, 646, 669, 675, 673, 667, 666, 663, 672, 692, 700, 699, 688, 685, 694, 698, 683, 706, 712, 718, 719, 754, 753, 736, 732, 756, 758, 775, 767, 778, 776, 772, 773, 765, 747, 739, 725, 720, 709, 726, 729, 730, 722, 740, 745, 749, 748, 761, 762, 769, 779, 780, 781, 782, 774, 770, 766, 752, 743, 750, 763, 755, 751, 741, 715, 707, 701, 693, 695, 702, 714, 723, 727, 716, 728, 711, 713, 710, 686, 681, 676, 657, 655, 662, 642, 634, 624, 622, 619, 601, 607, 594, 591, 581, 566, 573, 582, 584, 554, 549, 537, 545, 548, 544, 531, 543, 536, 527, 524, 508, 501, 497, 509, 502, 522, 515, 503, 489, 478, 480, 470, 477, 467, 453, 446, 439, 426, 450, 441, 460, 461, 443, 427, 420, 395, 398, 393, 412, 405, 403, 366, 356, 354, 340, 330, 368, 373, 378, 377, 397, 411, 402, 387, 384, 367, 372, 382, 380, 385, 379, 374, 359, 353, 350, 363, 347, 339, 337, 336, 348, 360, 361, 341, 333, 323, 319, 297, 308, 295, 296, 303, 328, 313, 314, 284, 279, 264, 263, 246, 260, 278, 283, 271, 270, 240, 251, 244, 237, 253, 233, 217, 198, 192, 170, 134, 133, 148, 141, 121, 113, 108, 105, 100, 78, 83, 86, 74, 65, 72, 95, 90, 103, 112, 118, 130, 131, 144, 147, 167, 169, 176, 180, 193, 213, 222, 206, 191, 177, 173, 165, 157, 166, 158, 153, 140, 129, 128, 102, 91, 81, 85, 67, 58, 60, 49, 61, 53, 41, 50, 71, 92, 89, 77, 68, 43, 54, 59, 33, 42, 37, 39, 5, 12, 10, 3, 27, 23, 26, 25, 20, 15, 31, 13, 21, 34, 30, 35, 19, 7, 29, 18, 4, 2, 9, 8, 11, 32, 28, 38, 62, 57, 52, 46, 64, 80, 66, 69, 79, 56, 44, 36, 40, 45, 17, 6, 1, 22, 16, 0, 14, 24, 51, 48, 55, 87, 96, 99, 114, 109, 122, 116, 124, 145, 138, 146, 154, 159, 152, 126, 135, 150, 155, 161, 160, 151, 142, 136, 132, 115, 119, 110, 106, 93, 82, 75, 97, 94, 88, 73, 76, 47, 63, 70, 84, 98, 101, 104, 107, 111, 127, 139, 137, 117, 125, 120, 123, 143, 149, 164, 163, 156, 168, 162, 175, 178, 197, 207, 201, 186, 203, 221, 226, 230, 229, 247, 248, 242, 223, 239, 231, 232, 249, 268, 280, 258, 257, 267, 255, 266, 285, 298, 273, 272, 277, 275, 276, 254, 245, 238, 235, 215, 204, 194, 195, 183, 174, 185, 179, 171, 184, 214, 234, 241, 265, 269, 288, 304, 312, 301, 293, 316, 334, 326, 318, 322, 324, 331, 315, 306, 305, 290, 292, 289, 299, 291, 302, 310, 294, 274, 256, 261, 252, 250, 236, 225, 220, 212, 200, 209, 218, 208, 210, 211, 224, 216, 205, 199, 189, 181, 172, 182, 187, 196, 190, 188, 202, 219, 227, 228, 243, 259, 262, 282, 287, 307, 309, 281, 286, 300, 311, 317, 325, 335, 329, 321, 320, 332, 344, 346, 349, 345, 352, 338, 364, 370, 365, 357, 343, 327, 342, 355, 358, 351, 362, 383, 394, 389, 381, 386, 400, 406, 396, 388, 391, 404, 375, 419, 423, 429, 425, 432, 421, 424, 422, 428, 435, 444, 451, 457, 465, 452, 442, 437, 454, 462, 485, 484, 483, 481, 471, 498, 510, 505, 516, 511, 507, 491, 494, 517, 518, 512, 514, 528, 551, 556, 546, 539, 530, 538, 560, 568, 578, 561, 553, 533, 529, 550, 525, 532, 547, 559, 575, 567, 579, 595, 623, 639, 637, 625, 610, 593, 585, 596, 597, 589, 598, 587, 612, 611, 626, 633, 644, 654, 678, 670, 704, 708, 687, 677, 647, 651, 658, 664, 671, 682, 696, 703, 724, 737, 733, 746, 760, 768, 777, 771, 764, 759, 744, 734, 717, 735]</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -1882,17 +1882,17 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11051</v>
+        <v>10947</v>
       </c>
       <c r="E44" t="n">
-        <v>25.49398137633432</v>
+        <v>24.31296843061549</v>
       </c>
       <c r="F44" t="n">
-        <v>60.00002312660217</v>
+        <v>60.00001692771912</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>[1, 6, 17, 11, 8, 9, 2, 4, 18, 29, 7, 19, 35, 30, 21, 34, 13, 31, 25, 20, 15, 26, 23, 27, 33, 42, 37, 39, 5, 12, 10, 3, 59, 54, 43, 68, 77, 89, 92, 91, 102, 71, 53, 41, 50, 61, 49, 60, 58, 67, 81, 85, 84, 98, 70, 63, 47, 38, 28, 32, 57, 52, 46, 64, 82, 93, 97, 75, 62, 73, 76, 88, 94, 111, 115, 132, 136, 142, 151, 160, 161, 155, 150, 135, 126, 152, 159, 154, 146, 138, 122, 116, 109, 114, 99, 79, 69, 66, 80, 45, 40, 44, 56, 51, 48, 55, 87, 96, 106, 110, 119, 139, 127, 107, 104, 101, 117, 125, 120, 123, 143, 149, 164, 163, 172, 181, 189, 205, 216, 224, 232, 231, 239, 257, 258, 249, 268, 280, 289, 299, 306, 292, 305, 290, 285, 298, 318, 326, 334, 316, 293, 301, 288, 304, 312, 327, 343, 357, 365, 370, 364, 352, 345, 338, 322, 324, 331, 315, 320, 332, 344, 346, 349, 369, 376, 392, 407, 408, 409, 418, 416, 410, 417, 433, 436, 447, 440, 434, 430, 438, 456, 455, 448, 459, 472, 476, 482, 490, 499, 500, 506, 504, 520, 535, 534, 540, 541, 557, 564, 569, 576, 583, 590, 586, 602, 608, 621, 635, 629, 632, 613, 600, 599, 604, 588, 609, 617, 638, 630, 653, 652, 645, 650, 665, 668, 660, 648, 656, 680, 690, 691, 697, 712, 706, 718, 719, 720, 725, 739, 747, 765, 773, 772, 776, 778, 767, 756, 758, 757, 742, 738, 731, 735, 744, 734, 717, 704, 708, 687, 677, 670, 678, 684, 679, 689, 674, 659, 654, 644, 647, 651, 658, 664, 671, 682, 696, 703, 724, 733, 737, 746, 760, 771, 764, 759, 775, 732, 736, 753, 754, 748, 749, 762, 769, 761, 726, 729, 730, 722, 740, 745, 741, 751, 755, 763, 750, 727, 714, 702, 695, 693, 669, 675, 673, 667, 666, 663, 672, 661, 649, 641, 631, 628, 614, 603, 605, 592, 581, 591, 594, 607, 601, 584, 582, 573, 566, 548, 545, 549, 537, 554, 522, 515, 503, 502, 509, 497, 501, 508, 524, 527, 536, 543, 531, 544, 489, 572, 571, 570, 574, 542, 526, 521, 523, 513, 519, 492, 488, 479, 473, 486, 496, 495, 493, 475, 463, 469, 468, 466, 514, 512, 518, 517, 530, 539, 546, 538, 560, 568, 561, 578, 585, 593, 579, 567, 575, 559, 547, 532, 525, 510, 498, 471, 481, 483, 484, 465, 457, 451, 452, 444, 435, 428, 422, 400, 389, 386, 381, 396, 406, 424, 442, 437, 421, 432, 425, 429, 423, 419, 404, 391, 388, 375, 371, 374, 379, 385, 380, 382, 372, 367, 384, 387, 402, 414, 413, 399, 401, 415, 431, 445, 458, 449, 464, 474, 487, 467, 477, 470, 480, 478, 460, 461, 443, 441, 427, 420, 398, 395, 378, 377, 361, 360, 348, 336, 337, 339, 347, 350, 353, 359, 335, 329, 321, 302, 291, 294, 310, 317, 311, 300, 286, 281, 282, 287, 307, 309, 319, 323, 333, 341, 330, 308, 297, 283, 278, 260, 244, 251, 240, 219, 227, 228, 243, 225, 220, 212, 200, 187, 182, 196, 190, 188, 202, 191, 177, 173, 165, 157, 144, 147, 141, 121, 113, 108, 105, 100, 78, 83, 86, 74, 65, 72, 90, 95, 103, 112, 118, 130, 131, 140, 129, 128, 153, 158, 166, 167, 169, 180, 176, 193, 198, 192, 170, 148, 133, 134, 217, 213, 222, 206, 246, 237, 263, 264, 279, 284, 253, 233, 296, 295, 303, 313, 314, 328, 340, 354, 356, 366, 393, 412, 405, 403, 373, 368, 397, 411, 426, 446, 453, 450, 439, 363, 325, 274, 261, 250, 252, 236, 256, 259, 262, 270, 271, 209, 208, 210, 211, 218, 199, 197, 178, 175, 162, 168, 156, 137, 186, 201, 207, 223, 242, 255, 266, 267, 248, 247, 230, 229, 245, 254, 275, 276, 269, 265, 241, 235, 238, 234, 214, 215, 204, 194, 195, 183, 203, 221, 226, 273, 272, 277, 342, 351, 358, 355, 362, 383, 394, 454, 462, 485, 491, 507, 511, 516, 505, 529, 533, 550, 553, 596, 597, 589, 598, 587, 577, 565, 562, 563, 555, 528, 551, 556, 612, 618, 640, 643, 633, 626, 611, 610, 625, 637, 639, 623, 595, 616, 627, 620, 606, 683, 698, 694, 685, 709, 699, 700, 688, 692, 707, 701, 715, 723, 716, 713, 710, 711, 728, 743, 752, 766, 770, 774, 782, 781, 780, 779, 686, 681, 676, 657, 655, 662, 642, 634, 624, 622, 619, 615, 636, 646, 580, 552, 558, 390, 494, 705, 721, 768, 777, 184, 171, 179, 185, 174, 145, 124, 36, 22, 16, 24, 14, 0]</t>
+          <t>[642, 634, 624, 622, 619, 601, 584, 582, 573, 566, 581, 591, 594, 607, 615, 605, 592, 603, 614, 628, 631, 641, 649, 661, 653, 652, 645, 650, 665, 668, 660, 648, 656, 680, 690, 691, 697, 712, 706, 718, 719, 720, 725, 739, 747, 765, 773, 772, 776, 778, 767, 756, 758, 757, 742, 738, 731, 735, 744, 734, 717, 704, 708, 687, 677, 670, 678, 684, 679, 689, 674, 659, 654, 644, 647, 651, 658, 664, 671, 682, 696, 703, 724, 733, 737, 746, 760, 771, 764, 759, 775, 732, 736, 753, 754, 748, 749, 762, 769, 761, 726, 729, 730, 722, 740, 745, 741, 751, 755, 763, 750, 727, 714, 702, 695, 693, 669, 675, 673, 667, 666, 663, 672, 692, 700, 699, 688, 709, 694, 698, 683, 685, 635, 629, 632, 613, 600, 599, 583, 590, 586, 602, 608, 621, 620, 627, 616, 606, 587, 598, 589, 597, 596, 585, 593, 579, 567, 575, 559, 547, 532, 525, 510, 498, 471, 481, 483, 484, 465, 457, 451, 452, 444, 435, 428, 422, 400, 389, 386, 381, 396, 406, 424, 442, 437, 421, 432, 425, 429, 423, 419, 407, 408, 409, 418, 416, 410, 417, 433, 436, 447, 440, 434, 430, 438, 456, 455, 448, 459, 472, 476, 482, 490, 499, 500, 506, 504, 520, 535, 534, 540, 541, 557, 564, 569, 576, 555, 563, 562, 565, 577, 551, 556, 546, 539, 530, 538, 560, 568, 561, 578, 553, 533, 529, 550, 516, 511, 507, 491, 485, 462, 454, 494, 512, 518, 517, 514, 528, 466, 468, 469, 463, 475, 493, 495, 496, 486, 488, 479, 473, 458, 445, 431, 413, 414, 399, 401, 415, 385, 380, 379, 374, 359, 353, 350, 347, 339, 337, 336, 348, 360, 361, 341, 333, 323, 319, 297, 308, 295, 296, 303, 313, 314, 328, 340, 354, 356, 366, 393, 412, 405, 403, 398, 395, 378, 377, 397, 411, 402, 387, 384, 367, 372, 382, 363, 325, 317, 311, 300, 286, 281, 282, 287, 307, 309, 262, 259, 243, 228, 227, 219, 202, 188, 190, 196, 187, 182, 200, 212, 220, 225, 236, 250, 252, 261, 274, 256, 294, 310, 302, 291, 280, 268, 249, 232, 231, 239, 257, 258, 267, 255, 266, 285, 298, 290, 305, 292, 306, 299, 289, 315, 331, 324, 322, 318, 326, 334, 316, 293, 301, 288, 304, 312, 327, 343, 357, 365, 370, 364, 352, 345, 338, 349, 346, 344, 332, 320, 321, 329, 335, 371, 369, 376, 392, 375, 391, 388, 404, 390, 449, 464, 474, 487, 492, 513, 519, 523, 521, 526, 542, 552, 558, 572, 571, 570, 574, 588, 609, 617, 638, 630, 604, 580, 536, 543, 524, 527, 508, 501, 497, 477, 467, 453, 446, 439, 426, 420, 427, 441, 460, 461, 443, 478, 480, 470, 450, 502, 503, 515, 522, 537, 545, 548, 544, 531, 509, 549, 554, 489, 373, 368, 330, 283, 278, 260, 244, 251, 240, 270, 271, 246, 237, 217, 213, 222, 206, 191, 177, 173, 165, 157, 144, 147, 141, 121, 113, 108, 105, 100, 78, 83, 86, 74, 65, 72, 90, 95, 103, 112, 118, 130, 131, 140, 129, 128, 143, 149, 125, 120, 123, 117, 137, 156, 168, 162, 175, 178, 197, 199, 205, 216, 224, 211, 210, 208, 218, 209, 172, 164, 163, 181, 189, 139, 127, 111, 115, 132, 136, 142, 151, 160, 161, 155, 150, 135, 126, 152, 159, 154, 146, 138, 122, 116, 109, 114, 99, 79, 69, 66, 80, 93, 82, 75, 97, 94, 88, 73, 76, 63, 70, 84, 98, 101, 104, 107, 85, 81, 61, 49, 53, 41, 50, 31, 25, 20, 15, 26, 23, 27, 33, 42, 37, 39, 5, 12, 10, 3, 59, 54, 43, 68, 77, 89, 92, 91, 102, 71, 67, 60, 58, 35, 19, 7, 18, 29, 4, 2, 9, 8, 11, 17, 6, 1, 22, 16, 36, 44, 56, 51, 48, 55, 87, 96, 106, 110, 119, 64, 46, 52, 57, 62, 38, 28, 32, 47, 30, 21, 34, 13, 153, 158, 166, 167, 169, 180, 176, 193, 198, 192, 170, 148, 133, 134, 233, 253, 264, 263, 279, 284, 223, 207, 201, 203, 186, 183, 195, 194, 174, 179, 185, 171, 184, 214, 215, 235, 241, 234, 238, 245, 254, 275, 276, 269, 265, 229, 230, 226, 221, 248, 247, 273, 272, 277, 242, 204, 145, 124, 40, 45, 24, 14, 0, 342, 351, 358, 355, 362, 383, 394, 505, 595, 623, 637, 639, 625, 610, 626, 633, 640, 643, 618, 612, 611, 705, 721, 768, 777, 779, 780, 781, 782, 774, 770, 766, 752, 743, 728, 713, 710, 711, 716, 686, 681, 676, 657, 655, 662, 646, 636, 701, 707, 715, 723]</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -1916,17 +1916,17 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>9090</v>
+        <v>9095</v>
       </c>
       <c r="E45" t="n">
-        <v>3.225073813309107</v>
+        <v>3.281853281853282</v>
       </c>
       <c r="F45" t="n">
-        <v>5.401305675506592</v>
+        <v>5.176591157913208</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>[654, 679, 689, 705, 684, 678, 670, 677, 687, 708, 704, 717, 734, 744, 735, 731, 742, 738, 721, 697, 691, 690, 674, 680, 656, 648, 660, 665, 668, 683, 698, 694, 685, 688, 692, 700, 699, 709, 720, 719, 718, 706, 712, 732, 736, 753, 754, 747, 739, 725, 726, 748, 749, 745, 740, 729, 730, 722, 715, 707, 701, 723, 741, 751, 755, 763, 750, 727, 714, 716, 713, 710, 711, 728, 743, 752, 766, 770, 774, 782, 781, 780, 779, 769, 762, 761, 765, 773, 772, 776, 778, 767, 756, 758, 775, 757, 759, 764, 771, 760, 777, 768, 746, 733, 737, 724, 703, 696, 682, 671, 664, 658, 651, 647, 644, 633, 626, 611, 597, 596, 585, 593, 610, 625, 637, 639, 623, 595, 579, 567, 575, 559, 547, 532, 525, 510, 498, 481, 471, 435, 428, 422, 444, 451, 452, 457, 465, 483, 484, 485, 462, 454, 437, 442, 424, 421, 432, 425, 429, 423, 419, 438, 430, 434, 440, 447, 433, 436, 415, 401, 399, 413, 414, 402, 387, 384, 367, 372, 382, 363, 380, 385, 379, 374, 359, 353, 350, 347, 339, 337, 336, 348, 360, 361, 341, 330, 333, 323, 319, 308, 297, 283, 278, 260, 271, 270, 262, 259, 243, 228, 227, 219, 240, 251, 244, 246, 237, 217, 213, 222, 206, 191, 202, 188, 190, 196, 187, 182, 158, 143, 149, 123, 120, 125, 117, 137, 139, 127, 111, 107, 104, 101, 98, 84, 70, 63, 47, 38, 28, 32, 57, 52, 46, 64, 45, 40, 66, 80, 69, 79, 99, 106, 110, 93, 82, 75, 62, 73, 76, 88, 94, 97, 115, 132, 136, 142, 119, 135, 126, 152, 161, 155, 150, 151, 160, 186, 178, 175, 162, 168, 156, 163, 164, 172, 181, 189, 205, 199, 197, 216, 224, 218, 211, 210, 208, 209, 200, 212, 220, 225, 236, 250, 252, 261, 256, 274, 286, 281, 282, 287, 307, 309, 300, 311, 294, 291, 302, 310, 317, 325, 335, 329, 321, 320, 332, 344, 369, 376, 371, 390, 410, 417, 416, 418, 409, 408, 407, 392, 375, 349, 346, 331, 324, 338, 345, 352, 364, 370, 404, 391, 388, 396, 406, 400, 386, 381, 389, 394, 383, 362, 351, 358, 355, 342, 327, 343, 357, 365, 334, 326, 316, 318, 322, 298, 285, 273, 248, 247, 272, 277, 275, 276, 293, 301, 312, 304, 288, 269, 265, 234, 214, 184, 171, 179, 185, 204, 215, 235, 241, 238, 245, 254, 229, 230, 226, 221, 242, 255, 266, 267, 290, 305, 292, 315, 306, 299, 289, 280, 268, 249, 232, 231, 258, 257, 239, 223, 207, 201, 203, 183, 195, 194, 174, 159, 154, 146, 138, 145, 124, 116, 122, 114, 109, 96, 87, 55, 48, 51, 56, 44, 36, 24, 14, 0, 16, 22, 1, 6, 17, 11, 8, 9, 2, 4, 18, 29, 7, 19, 35, 30, 34, 21, 13, 31, 15, 20, 25, 26, 23, 27, 33, 3, 10, 12, 5, 39, 37, 42, 65, 74, 86, 83, 78, 100, 105, 108, 113, 95, 72, 59, 54, 43, 50, 41, 53, 61, 49, 60, 58, 67, 85, 81, 71, 91, 102, 92, 68, 77, 89, 90, 103, 112, 118, 121, 133, 134, 148, 141, 147, 144, 130, 131, 140, 129, 128, 153, 166, 157, 165, 177, 173, 167, 169, 193, 180, 176, 170, 192, 198, 233, 253, 284, 279, 264, 263, 295, 296, 303, 313, 314, 328, 340, 354, 356, 366, 393, 403, 405, 412, 398, 395, 373, 368, 378, 377, 397, 411, 426, 439, 446, 453, 450, 420, 427, 441, 443, 460, 461, 489, 478, 480, 470, 467, 477, 497, 509, 502, 503, 515, 522, 554, 549, 537, 545, 548, 573, 566, 544, 531, 543, 536, 527, 524, 508, 501, 487, 474, 464, 449, 431, 445, 458, 475, 463, 469, 468, 466, 456, 455, 448, 459, 472, 476, 482, 490, 499, 500, 514, 528, 551, 556, 546, 539, 538, 530, 517, 518, 512, 494, 491, 507, 511, 516, 505, 529, 533, 550, 553, 561, 578, 560, 568, 589, 598, 587, 577, 565, 562, 563, 555, 534, 535, 540, 541, 520, 506, 504, 493, 495, 496, 486, 473, 479, 488, 492, 513, 519, 523, 521, 526, 542, 552, 558, 572, 580, 603, 614, 631, 628, 636, 615, 605, 592, 581, 591, 594, 607, 582, 584, 601, 619, 622, 624, 634, 642, 646, 669, 662, 655, 657, 676, 681, 686, 695, 702, 693, 675, 673, 667, 666, 663, 672, 661, 653, 652, 645, 650, 635, 629, 632, 613, 604, 630, 638, 649, 641, 617, 609, 588, 571, 570, 574, 557, 564, 569, 576, 600, 599, 583, 590, 586, 602, 608, 621, 620, 627, 606, 616, 618, 612, 640, 643, 659]</t>
+          <t>[738, 742, 731, 721, 697, 690, 691, 712, 706, 698, 694, 685, 709, 699, 700, 688, 692, 672, 663, 666, 667, 673, 675, 669, 646, 636, 615, 605, 592, 580, 603, 614, 628, 631, 641, 649, 661, 653, 652, 645, 650, 665, 668, 683, 660, 648, 656, 680, 674, 679, 689, 705, 684, 678, 670, 677, 687, 708, 704, 717, 734, 735, 744, 759, 764, 771, 777, 768, 760, 746, 733, 737, 724, 703, 696, 682, 671, 664, 658, 651, 647, 644, 654, 659, 643, 640, 633, 626, 611, 612, 618, 616, 627, 620, 606, 587, 598, 589, 597, 596, 593, 585, 579, 610, 625, 637, 639, 623, 595, 575, 567, 559, 547, 532, 525, 510, 498, 471, 481, 483, 484, 485, 491, 494, 476, 482, 490, 499, 500, 506, 504, 520, 541, 540, 555, 535, 534, 528, 514, 512, 518, 517, 507, 511, 516, 505, 529, 533, 550, 553, 561, 578, 568, 560, 538, 530, 539, 546, 556, 551, 577, 565, 562, 563, 586, 602, 608, 621, 635, 629, 632, 630, 638, 617, 609, 604, 613, 600, 599, 590, 583, 576, 569, 564, 557, 574, 570, 588, 571, 572, 558, 552, 542, 526, 521, 523, 519, 513, 492, 488, 479, 473, 486, 496, 495, 493, 475, 463, 469, 468, 466, 456, 455, 448, 459, 472, 462, 454, 437, 442, 424, 452, 465, 457, 451, 444, 435, 428, 422, 394, 383, 362, 351, 342, 358, 355, 381, 386, 389, 400, 406, 396, 388, 391, 404, 421, 432, 425, 429, 423, 419, 438, 430, 434, 440, 447, 458, 445, 431, 413, 414, 402, 399, 401, 415, 436, 433, 417, 410, 416, 418, 409, 408, 407, 390, 371, 369, 376, 392, 375, 364, 370, 365, 357, 343, 327, 316, 334, 326, 318, 322, 338, 352, 345, 349, 346, 331, 324, 305, 290, 298, 285, 266, 255, 242, 248, 247, 273, 272, 277, 293, 301, 312, 304, 288, 276, 275, 254, 245, 238, 241, 269, 265, 234, 235, 215, 214, 184, 171, 179, 185, 204, 229, 230, 226, 221, 223, 207, 201, 203, 186, 183, 195, 194, 174, 159, 154, 146, 138, 145, 124, 116, 122, 109, 114, 126, 152, 161, 155, 150, 135, 106, 110, 119, 132, 136, 142, 151, 160, 175, 178, 197, 199, 189, 205, 216, 224, 232, 231, 239, 267, 257, 258, 249, 268, 280, 289, 292, 315, 306, 299, 291, 302, 321, 320, 332, 344, 329, 335, 325, 317, 310, 294, 311, 300, 286, 281, 274, 256, 236, 261, 250, 252, 218, 211, 210, 208, 209, 200, 212, 220, 225, 243, 228, 227, 219, 202, 188, 190, 196, 187, 182, 172, 181, 164, 163, 156, 168, 162, 139, 127, 115, 111, 107, 104, 101, 98, 84, 70, 63, 47, 76, 73, 88, 94, 97, 75, 82, 93, 64, 80, 66, 69, 79, 99, 96, 87, 55, 48, 51, 56, 44, 36, 24, 14, 0, 16, 22, 1, 6, 17, 40, 45, 46, 52, 57, 62, 38, 28, 32, 11, 8, 9, 2, 4, 18, 29, 7, 19, 30, 35, 58, 60, 67, 85, 81, 71, 50, 41, 53, 61, 49, 34, 21, 13, 31, 15, 20, 25, 26, 23, 27, 3, 10, 12, 5, 39, 37, 42, 33, 59, 54, 43, 68, 77, 89, 90, 95, 72, 65, 74, 86, 83, 78, 100, 105, 108, 113, 121, 118, 112, 103, 92, 91, 102, 128, 123, 120, 125, 117, 137, 149, 143, 158, 166, 153, 140, 129, 131, 130, 144, 147, 141, 148, 133, 134, 170, 192, 198, 193, 180, 176, 169, 167, 173, 165, 157, 177, 191, 206, 213, 217, 233, 253, 237, 263, 264, 279, 284, 314, 313, 303, 296, 295, 283, 278, 260, 246, 222, 244, 240, 251, 271, 270, 262, 259, 282, 287, 309, 307, 319, 297, 308, 323, 333, 330, 341, 361, 360, 348, 336, 337, 339, 347, 350, 353, 359, 374, 379, 385, 380, 363, 382, 372, 367, 384, 387, 377, 378, 368, 373, 354, 340, 328, 356, 366, 393, 403, 405, 412, 398, 395, 397, 411, 426, 420, 427, 441, 443, 461, 460, 480, 478, 489, 503, 502, 509, 497, 477, 467, 470, 450, 453, 446, 439, 449, 464, 474, 487, 501, 508, 524, 527, 536, 543, 531, 544, 548, 545, 549, 537, 522, 515, 554, 573, 566, 581, 591, 594, 607, 582, 584, 601, 619, 622, 624, 634, 642, 662, 655, 657, 676, 681, 686, 710, 713, 711, 728, 716, 727, 723, 714, 702, 695, 693, 701, 707, 715, 722, 729, 730, 745, 740, 741, 751, 750, 743, 752, 766, 770, 774, 782, 781, 763, 755, 780, 779, 769, 762, 749, 726, 748, 761, 765, 773, 772, 776, 778, 753, 754, 747, 739, 725, 720, 719, 718, 736, 732, 756, 758, 767, 775, 757]</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -1956,7 +1956,7 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>7.242475748062134</v>
+        <v>7.016586780548096</v>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
@@ -1980,17 +1980,17 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>330152</v>
+        <v>318302</v>
       </c>
       <c r="E47" t="n">
-        <v>27.44967090659924</v>
+        <v>22.87517612769982</v>
       </c>
       <c r="F47" t="n">
-        <v>0.1292600631713867</v>
+        <v>0.1052649021148682</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>[496, 495, 494, 493, 492, 482, 483, 491, 490, 489, 485, 486, 487, 488, 499, 498, 497, 500, 501, 506, 507, 508, 509, 510, 511, 512, 484, 481, 480, 478, 479, 477, 476, 471, 470, 475, 473, 474, 472, 458, 457, 456, 455, 454, 452, 451, 450, 449, 447, 448, 584, 583, 582, 581, 580, 576, 577, 574, 575, 587, 588, 589, 593, 592, 594, 595, 596, 598, 597, 599, 600, 601, 602, 603, 604, 607, 605, 606, 608, 609, 610, 611, 626, 627, 625, 624, 991, 632, 633, 634, 635, 636, 637, 638, 639, 372, 371, 370, 369, 368, 377, 367, 366, 365, 364, 363, 362, 361, 360, 359, 351, 350, 349, 348, 345, 346, 347, 353, 357, 358, 352, 344, 343, 340, 341, 337, 338, 339, 390, 391, 389, 388, 392, 386, 385, 384, 382, 383, 394, 393, 387, 378, 380, 379, 381, 399, 400, 398, 396, 395, 397, 334, 336, 335, 342, 356, 354, 355, 659, 660, 661, 655, 654, 656, 657, 658, 641, 642, 643, 652, 651, 653, 646, 645, 644, 647, 649, 648, 650, 621, 620, 622, 623, 616, 617, 618, 619, 729, 730, 731, 614, 615, 613, 612, 628, 629, 630, 631, 440, 438, 437, 439, 441, 442, 443, 444, 446, 445, 433, 432, 431, 430, 429, 428, 427, 460, 461, 462, 463, 465, 464, 459, 423, 424, 425, 426, 418, 419, 417, 420, 421, 422, 404, 405, 406, 409, 415, 416, 414, 413, 412, 411, 410, 408, 407, 401, 402, 403, 286, 287, 285, 284, 283, 298, 299, 297, 296, 990, 304, 305, 306, 307, 308, 309, 310, 311, 44, 43, 42, 41, 40, 49, 39, 38, 37, 36, 35, 34, 33, 32, 31, 23, 22, 21, 20, 17, 18, 19, 25, 29, 30, 24, 16, 15, 12, 13, 9, 10, 11, 62, 63, 61, 60, 64, 58, 57, 56, 54, 55, 66, 65, 59, 50, 52, 51, 53, 71, 72, 70, 68, 67, 69, 6, 8, 7, 14, 28, 26, 27, 331, 332, 333, 327, 326, 328, 329, 330, 313, 314, 315, 324, 323, 325, 318, 317, 316, 319, 321, 320, 322, 293, 292, 294, 295, 288, 289, 290, 291, 312, 48, 47, 46, 45, 83, 82, 81, 77, 78, 79, 80, 87, 88, 86, 85, 84, 89, 91, 90, 97, 96, 95, 94, 93, 92, 76, 98, 132, 133, 134, 135, 137, 136, 131, 129, 128, 127, 126, 124, 123, 122, 121, 119, 120, 256, 255, 254, 253, 252, 248, 249, 246, 247, 259, 260, 261, 265, 264, 266, 267, 268, 270, 269, 271, 272, 273, 274, 275, 276, 279, 277, 278, 280, 281, 282, 300, 301, 302, 303, 112, 110, 109, 111, 113, 114, 115, 116, 118, 117, 105, 104, 103, 102, 101, 100, 99, 993, 106, 107, 108, 125, 146, 145, 147, 143, 142, 148, 149, 150, 151, 141, 144, 130, 138, 139, 140, 152, 153, 154, 155, 163, 162, 161, 157, 158, 159, 160, 171, 170, 169, 172, 173, 178, 179, 180, 181, 182, 183, 184, 156, 164, 165, 166, 167, 168, 994, 251, 250, 242, 243, 244, 245, 262, 263, 230, 231, 229, 227, 228, 226, 225, 224, 223, 222, 221, 219, 218, 217, 216, 211, 215, 214, 213, 212, 210, 208, 207, 206, 205, 204, 203, 202, 200, 197, 198, 199, 196, 193, 192, 191, 188, 187, 238, 237, 239, 240, 241, 185, 186, 194, 195, 201, 995, 176, 177, 174, 175, 189, 190, 236, 235, 234, 233, 232, 220, 209, 503, 502, 505, 504, 998, 529, 523, 522, 521, 520, 519, 516, 515, 566, 565, 567, 568, 569, 513, 514, 517, 518, 564, 563, 562, 561, 560, 548, 547, 546, 545, 544, 539, 543, 542, 541, 540, 538, 536, 535, 534, 533, 532, 531, 530, 528, 525, 526, 527, 524, 537, 825, 826, 827, 816, 815, 814, 813, 817, 818, 819, 811, 810, 820, 821, 822, 823, 824, 552, 553, 554, 555, 556, 558, 591, 590, 573, 572, 571, 570, 578, 579, 997, 586, 585, 453, 996, 434, 435, 436, 374, 375, 373, 376, 640, 726, 728, 727, 723, 724, 725, 722, 711, 710, 712, 708, 707, 706, 705, 696, 697, 698, 699, 700, 967, 966, 965, 964, 963, 962, 961, 960, 992, 952, 953, 955, 954, 939, 938, 937, 936, 935, 933, 934, 932, 940, 941, 942, 943, 944, 945, 946, 947, 948, 949, 950, 951, 976, 977, 978, 975, 973, 972, 974, 971, 970, 980, 979, 981, 985, 984, 983, 982, 986, 969, 968, 692, 691, 690, 689, 688, 687, 679, 678, 677, 676, 673, 674, 675, 681, 685, 686, 680, 672, 671, 668, 669, 665, 666, 667, 718, 719, 717, 716, 720, 714, 713, 715, 694, 693, 695, 704, 703, 702, 701, 739, 738, 737, 733, 734, 735, 736, 743, 744, 742, 741, 740, 745, 747, 746, 753, 752, 751, 750, 749, 748, 732, 754, 788, 789, 790, 791, 793, 792, 787, 785, 784, 783, 782, 780, 779, 778, 777, 775, 776, 912, 911, 910, 909, 908, 904, 905, 902, 903, 915, 916, 917, 921, 920, 922, 923, 924, 926, 925, 927, 928, 929, 930, 931, 956, 957, 958, 959, 768, 766, 765, 767, 769, 770, 771, 772, 774, 773, 761, 760, 759, 758, 757, 756, 755, 999, 762, 763, 764, 781, 802, 801, 803, 799, 798, 804, 805, 806, 807, 797, 800, 786, 794, 795, 796, 808, 809, 1000, 907, 906, 898, 899, 900, 901, 918, 919, 886, 887, 885, 883, 884, 882, 881, 880, 879, 878, 877, 875, 874, 873, 872, 867, 871, 870, 869, 868, 866, 864, 863, 862, 861, 860, 859, 858, 856, 853, 854, 855, 852, 849, 848, 847, 844, 843, 894, 893, 895, 896, 897, 841, 842, 850, 851, 857, 1001, 837, 838, 839, 840, 812, 836, 835, 834, 829, 828, 830, 833, 832, 831, 551, 550, 549, 559, 557, 469, 468, 467, 466, 257, 258, 75, 74, 73, 0, 1, 4, 2, 3, 5, 662, 664, 663, 670, 721, 709, 684, 682, 683, 987, 988, 989, 913, 914, 888, 889, 890, 876, 891, 892, 845, 846, 865]</t>
+          <t>[841, 896, 895, 893, 894, 844, 847, 845, 846, 892, 891, 890, 889, 888, 876, 875, 874, 873, 872, 867, 871, 870, 869, 868, 866, 864, 863, 862, 861, 860, 859, 858, 856, 853, 854, 855, 852, 849, 848, 843, 842, 850, 851, 857, 1001, 837, 838, 839, 840, 814, 813, 817, 818, 819, 811, 810, 820, 821, 822, 823, 824, 552, 553, 554, 555, 556, 592, 593, 594, 595, 596, 598, 597, 587, 588, 589, 573, 572, 571, 590, 591, 558, 559, 557, 560, 561, 562, 548, 547, 546, 545, 544, 539, 543, 542, 541, 540, 538, 536, 535, 534, 533, 532, 531, 530, 528, 525, 526, 527, 524, 521, 520, 519, 516, 515, 566, 565, 567, 568, 569, 513, 514, 522, 523, 529, 998, 509, 510, 511, 512, 486, 485, 489, 490, 491, 483, 482, 492, 493, 494, 495, 496, 224, 225, 226, 227, 228, 264, 265, 266, 267, 268, 270, 269, 259, 260, 261, 245, 244, 243, 262, 263, 230, 231, 229, 232, 233, 234, 220, 219, 218, 217, 216, 211, 215, 214, 213, 212, 210, 208, 207, 206, 205, 204, 203, 202, 200, 197, 198, 199, 196, 193, 192, 191, 188, 187, 238, 237, 239, 240, 241, 185, 186, 194, 195, 201, 995, 181, 182, 183, 184, 158, 157, 161, 162, 163, 155, 154, 164, 165, 166, 167, 168, 160, 159, 171, 170, 169, 172, 173, 178, 179, 180, 177, 174, 176, 175, 156, 153, 152, 150, 151, 149, 148, 143, 142, 147, 145, 146, 144, 130, 129, 128, 127, 126, 124, 123, 122, 121, 119, 120, 256, 255, 254, 253, 252, 248, 249, 246, 247, 251, 250, 242, 236, 235, 190, 189, 221, 222, 223, 498, 497, 499, 488, 487, 484, 481, 480, 478, 479, 477, 476, 471, 470, 475, 473, 474, 472, 458, 457, 456, 455, 454, 452, 451, 450, 449, 447, 448, 584, 583, 582, 581, 580, 576, 577, 574, 575, 579, 578, 570, 564, 563, 518, 517, 549, 550, 551, 826, 825, 827, 816, 815, 812, 809, 808, 806, 807, 805, 804, 799, 798, 803, 801, 802, 800, 786, 785, 784, 783, 782, 780, 779, 778, 777, 775, 776, 912, 911, 910, 909, 908, 904, 905, 902, 903, 915, 916, 917, 921, 920, 922, 923, 924, 926, 925, 927, 928, 929, 930, 931, 932, 935, 933, 934, 936, 937, 938, 939, 954, 955, 953, 952, 992, 960, 961, 962, 963, 964, 965, 966, 967, 700, 699, 698, 697, 696, 705, 695, 694, 693, 692, 691, 690, 689, 688, 687, 679, 678, 677, 676, 673, 674, 675, 681, 685, 686, 680, 672, 671, 668, 669, 665, 666, 667, 718, 719, 717, 716, 720, 714, 713, 712, 710, 711, 722, 721, 715, 706, 708, 707, 709, 727, 728, 726, 724, 723, 725, 662, 664, 663, 670, 684, 682, 683, 987, 988, 989, 983, 982, 984, 985, 986, 969, 970, 971, 980, 979, 981, 974, 973, 972, 975, 977, 976, 978, 949, 948, 950, 951, 944, 945, 946, 947, 943, 942, 941, 940, 956, 957, 958, 959, 768, 766, 765, 767, 769, 770, 771, 772, 774, 773, 761, 760, 759, 758, 757, 756, 755, 788, 789, 790, 791, 793, 792, 787, 751, 752, 753, 754, 746, 747, 745, 748, 749, 750, 732, 733, 734, 737, 743, 744, 742, 741, 740, 739, 738, 736, 735, 729, 730, 731, 614, 615, 613, 612, 611, 626, 627, 625, 624, 991, 632, 633, 634, 635, 636, 637, 638, 639, 372, 371, 370, 369, 368, 377, 367, 366, 365, 364, 363, 362, 361, 360, 359, 351, 350, 349, 348, 345, 346, 347, 353, 357, 358, 352, 344, 343, 340, 341, 337, 338, 339, 390, 391, 389, 388, 392, 386, 385, 384, 382, 383, 394, 393, 387, 378, 380, 379, 381, 399, 400, 398, 396, 395, 397, 334, 336, 335, 342, 356, 354, 355, 659, 660, 661, 655, 654, 656, 657, 658, 641, 642, 643, 652, 651, 653, 646, 645, 644, 647, 649, 648, 650, 621, 620, 622, 623, 616, 617, 618, 619, 640, 376, 375, 374, 373, 411, 410, 409, 405, 406, 407, 408, 415, 416, 414, 413, 412, 417, 419, 418, 425, 424, 423, 422, 421, 420, 404, 426, 460, 461, 462, 463, 465, 464, 459, 427, 428, 429, 430, 431, 432, 433, 445, 443, 444, 446, 442, 441, 440, 438, 437, 439, 631, 630, 629, 628, 610, 609, 608, 607, 605, 606, 604, 603, 602, 601, 600, 599, 796, 795, 794, 797, 1000, 907, 906, 898, 899, 900, 901, 918, 919, 886, 887, 885, 883, 884, 882, 881, 880, 879, 878, 877, 897, 914, 913, 781, 999, 762, 763, 764, 702, 703, 701, 704, 968, 436, 435, 434, 996, 453, 585, 586, 997, 469, 468, 467, 466, 272, 271, 273, 274, 275, 276, 279, 277, 278, 280, 281, 282, 283, 298, 299, 297, 296, 990, 304, 305, 306, 307, 308, 309, 310, 311, 44, 43, 42, 41, 40, 49, 39, 38, 37, 36, 35, 34, 33, 32, 31, 23, 22, 21, 20, 17, 18, 19, 25, 29, 30, 24, 16, 15, 12, 13, 9, 10, 11, 62, 63, 61, 60, 64, 58, 57, 56, 54, 55, 66, 65, 59, 50, 52, 51, 53, 71, 72, 70, 68, 67, 69, 6, 8, 7, 14, 28, 26, 27, 331, 332, 333, 327, 326, 328, 329, 330, 313, 314, 315, 324, 323, 325, 318, 317, 316, 319, 321, 320, 322, 293, 292, 294, 295, 288, 289, 290, 291, 401, 402, 403, 286, 287, 285, 284, 300, 301, 302, 303, 112, 110, 109, 111, 113, 114, 115, 116, 118, 117, 105, 104, 103, 102, 101, 100, 99, 132, 133, 134, 135, 137, 136, 131, 95, 96, 97, 98, 90, 91, 89, 92, 93, 94, 76, 77, 78, 81, 87, 88, 86, 85, 84, 83, 82, 80, 79, 73, 74, 75, 138, 139, 140, 141, 994, 258, 257, 125, 993, 106, 107, 108, 46, 47, 45, 48, 312, 4, 2, 3, 5, 1, 0, 209, 500, 501, 506, 507, 508, 505, 502, 504, 503, 537, 828, 829, 834, 835, 836, 833, 830, 832, 831, 865]</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2014,17 +2014,17 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>287541</v>
+        <v>284703</v>
       </c>
       <c r="E48" t="n">
-        <v>11.00040533498041</v>
+        <v>9.904842787932598</v>
       </c>
       <c r="F48" t="n">
-        <v>1.89176607131958</v>
+        <v>1.632656097412109</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>[424, 423, 425, 426, 418, 419, 417, 420, 421, 422, 404, 405, 406, 409, 415, 416, 414, 413, 412, 436, 435, 434, 996, 430, 429, 428, 427, 460, 461, 462, 463, 465, 464, 459, 458, 457, 456, 455, 454, 452, 453, 474, 472, 473, 475, 476, 477, 478, 479, 471, 470, 469, 468, 467, 466, 272, 271, 273, 274, 275, 276, 277, 278, 279, 280, 281, 282, 300, 301, 302, 303, 112, 110, 109, 111, 113, 114, 115, 117, 116, 118, 105, 104, 103, 102, 993, 106, 107, 108, 84, 85, 82, 83, 47, 46, 45, 44, 43, 42, 41, 48, 40, 49, 39, 38, 37, 36, 35, 34, 33, 32, 31, 23, 22, 16, 15, 10, 11, 62, 61, 63, 64, 60, 59, 58, 65, 66, 55, 54, 56, 57, 50, 52, 51, 53, 72, 70, 71, 67, 68, 69, 6, 7, 8, 9, 13, 12, 14, 17, 18, 19, 20, 21, 24, 25, 30, 29, 28, 26, 27, 331, 332, 333, 327, 326, 328, 329, 330, 313, 314, 315, 324, 325, 323, 322, 321, 293, 292, 291, 290, 289, 288, 295, 294, 320, 319, 318, 317, 316, 312, 311, 310, 309, 308, 307, 306, 305, 304, 990, 296, 297, 299, 298, 283, 284, 285, 286, 287, 403, 402, 401, 407, 408, 410, 411, 375, 374, 373, 637, 636, 635, 634, 633, 632, 991, 624, 625, 627, 626, 611, 612, 613, 614, 615, 731, 730, 729, 619, 618, 617, 616, 623, 622, 620, 621, 648, 649, 650, 647, 644, 645, 646, 643, 652, 651, 653, 642, 640, 638, 639, 372, 371, 370, 369, 376, 368, 365, 366, 367, 377, 378, 379, 380, 385, 384, 381, 382, 383, 394, 393, 392, 386, 387, 388, 389, 391, 390, 339, 338, 343, 344, 350, 351, 359, 360, 361, 362, 363, 364, 641, 658, 657, 656, 654, 655, 661, 660, 659, 355, 354, 356, 357, 358, 353, 352, 349, 348, 347, 346, 345, 342, 340, 341, 337, 336, 335, 334, 397, 396, 395, 399, 400, 398, 5, 3, 2, 4, 1, 0, 141, 140, 139, 138, 75, 74, 73, 79, 80, 78, 77, 81, 87, 86, 88, 76, 92, 93, 94, 95, 96, 97, 91, 89, 90, 98, 132, 133, 134, 135, 137, 136, 131, 99, 100, 101, 128, 129, 130, 144, 145, 146, 147, 143, 142, 148, 149, 150, 151, 152, 153, 154, 164, 165, 168, 167, 166, 162, 163, 155, 156, 157, 161, 159, 160, 171, 170, 169, 172, 173, 174, 175, 176, 177, 178, 179, 180, 158, 184, 183, 182, 181, 995, 202, 203, 205, 204, 206, 207, 208, 210, 211, 215, 216, 218, 220, 233, 232, 234, 236, 235, 217, 190, 189, 238, 237, 239, 241, 240, 187, 188, 191, 192, 193, 196, 197, 198, 199, 200, 201, 195, 194, 186, 185, 250, 251, 994, 252, 253, 254, 255, 125, 127, 126, 124, 123, 122, 121, 119, 120, 256, 257, 258, 248, 247, 246, 249, 242, 231, 229, 230, 263, 262, 243, 244, 245, 261, 260, 259, 269, 270, 268, 267, 266, 265, 264, 228, 227, 226, 225, 224, 223, 222, 221, 219, 213, 214, 212, 209, 503, 504, 505, 502, 500, 501, 506, 507, 508, 509, 510, 511, 512, 484, 483, 491, 490, 489, 485, 486, 487, 488, 499, 497, 498, 496, 495, 494, 493, 492, 482, 481, 480, 997, 579, 578, 570, 571, 572, 573, 590, 591, 558, 559, 557, 555, 556, 594, 598, 596, 595, 593, 592, 589, 588, 587, 575, 574, 577, 576, 580, 581, 582, 583, 584, 585, 586, 597, 599, 600, 601, 448, 447, 449, 450, 451, 431, 432, 433, 446, 444, 445, 443, 442, 441, 439, 437, 438, 440, 631, 630, 629, 628, 610, 609, 608, 607, 606, 605, 604, 603, 602, 794, 795, 796, 797, 798, 799, 803, 802, 801, 800, 786, 785, 784, 757, 756, 755, 787, 792, 793, 791, 790, 789, 788, 751, 752, 753, 754, 746, 747, 745, 748, 749, 750, 732, 733, 734, 735, 736, 707, 708, 712, 713, 714, 715, 694, 693, 692, 691, 690, 689, 688, 718, 719, 717, 716, 720, 721, 722, 711, 710, 709, 728, 726, 727, 723, 724, 725, 662, 663, 664, 665, 666, 667, 668, 669, 670, 671, 672, 677, 676, 673, 674, 675, 681, 686, 680, 678, 679, 687, 685, 684, 682, 683, 987, 988, 989, 983, 982, 984, 985, 986, 969, 970, 981, 979, 980, 971, 974, 973, 972, 975, 978, 977, 976, 949, 948, 950, 951, 947, 946, 945, 944, 943, 942, 941, 940, 939, 954, 955, 953, 952, 992, 960, 961, 962, 963, 964, 965, 966, 967, 968, 700, 699, 698, 697, 696, 705, 695, 706, 704, 703, 701, 702, 739, 738, 737, 743, 744, 742, 741, 740, 764, 763, 762, 999, 758, 759, 760, 761, 773, 774, 772, 771, 770, 769, 767, 765, 766, 768, 959, 958, 957, 956, 938, 937, 936, 935, 934, 933, 932, 931, 930, 929, 928, 927, 925, 926, 924, 923, 922, 920, 921, 917, 916, 902, 903, 915, 914, 913, 912, 776, 775, 777, 778, 779, 780, 782, 783, 781, 911, 910, 909, 908, 904, 905, 906, 907, 1000, 805, 804, 806, 807, 808, 809, 810, 820, 821, 822, 826, 825, 828, 829, 827, 816, 815, 814, 813, 817, 818, 819, 811, 812, 840, 839, 838, 837, 857, 851, 850, 842, 841, 896, 897, 895, 893, 894, 843, 844, 847, 845, 892, 891, 876, 889, 890, 888, 898, 899, 900, 901, 918, 919, 886, 887, 885, 884, 883, 882, 881, 880, 879, 878, 877, 875, 869, 870, 871, 868, 866, 867, 872, 874, 873, 846, 848, 849, 852, 856, 853, 854, 855, 863, 864, 865, 862, 860, 861, 859, 858, 1001, 836, 835, 834, 833, 832, 830, 831, 537, 532, 531, 530, 998, 529, 523, 522, 514, 513, 568, 569, 567, 565, 566, 515, 516, 517, 519, 520, 521, 524, 528, 525, 526, 527, 533, 534, 535, 536, 538, 540, 541, 542, 543, 539, 544, 546, 545, 518, 564, 563, 562, 560, 561, 548, 547, 549, 550, 551, 552, 553, 554, 824, 823]</t>
+          <t>[592, 593, 594, 595, 596, 598, 599, 600, 601, 602, 603, 604, 605, 606, 607, 608, 609, 610, 628, 629, 630, 631, 440, 438, 437, 439, 441, 442, 443, 444, 446, 445, 433, 432, 431, 451, 450, 449, 447, 448, 584, 585, 586, 597, 587, 588, 589, 573, 572, 571, 570, 578, 579, 577, 574, 575, 576, 580, 581, 582, 583, 453, 452, 454, 455, 456, 457, 458, 472, 473, 474, 475, 471, 470, 469, 468, 467, 466, 272, 271, 273, 274, 275, 403, 287, 286, 285, 284, 276, 277, 278, 279, 280, 281, 282, 283, 298, 299, 297, 296, 990, 304, 305, 306, 307, 308, 309, 310, 316, 317, 319, 322, 321, 320, 293, 294, 295, 292, 291, 290, 289, 288, 401, 402, 407, 408, 409, 406, 405, 415, 416, 414, 426, 424, 425, 418, 419, 417, 404, 420, 421, 422, 423, 460, 461, 462, 463, 465, 464, 459, 427, 428, 429, 430, 996, 434, 435, 436, 412, 413, 410, 411, 376, 368, 369, 370, 371, 375, 374, 373, 372, 639, 640, 643, 646, 647, 645, 644, 638, 637, 636, 635, 634, 633, 632, 991, 624, 625, 627, 626, 611, 612, 613, 614, 615, 616, 617, 618, 619, 620, 623, 622, 621, 648, 649, 650, 651, 652, 653, 642, 641, 658, 657, 656, 654, 655, 661, 660, 659, 355, 354, 356, 357, 358, 353, 347, 346, 345, 342, 341, 340, 343, 344, 348, 349, 350, 352, 351, 359, 360, 361, 362, 363, 364, 365, 366, 367, 377, 378, 379, 380, 387, 388, 392, 386, 385, 384, 381, 382, 383, 394, 393, 391, 389, 390, 339, 338, 337, 336, 335, 334, 397, 396, 395, 399, 400, 398, 5, 3, 2, 4, 1, 0, 73, 74, 75, 94, 95, 96, 97, 98, 90, 89, 91, 93, 92, 76, 77, 78, 81, 87, 88, 86, 85, 84, 83, 82, 79, 80, 51, 52, 56, 57, 58, 59, 38, 37, 36, 35, 34, 33, 32, 62, 63, 61, 60, 64, 65, 66, 55, 54, 53, 72, 70, 71, 67, 68, 69, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 21, 20, 17, 18, 19, 25, 30, 24, 22, 23, 31, 29, 28, 26, 27, 331, 332, 333, 327, 326, 328, 329, 330, 313, 314, 325, 324, 323, 318, 315, 312, 311, 44, 43, 42, 41, 40, 49, 39, 50, 48, 47, 46, 45, 108, 107, 106, 993, 102, 103, 104, 105, 117, 114, 113, 111, 109, 110, 112, 303, 300, 301, 302, 115, 116, 118, 123, 124, 122, 121, 119, 120, 256, 257, 258, 248, 249, 247, 246, 244, 245, 243, 242, 250, 251, 994, 252, 253, 254, 255, 125, 146, 147, 145, 144, 130, 129, 128, 127, 126, 101, 100, 99, 132, 133, 134, 135, 131, 136, 137, 138, 139, 140, 141, 142, 143, 148, 149, 150, 151, 152, 153, 154, 164, 165, 168, 167, 166, 162, 163, 155, 156, 157, 161, 159, 160, 171, 170, 169, 172, 173, 174, 175, 176, 177, 178, 179, 180, 158, 184, 183, 182, 181, 995, 202, 203, 205, 204, 206, 207, 208, 209, 503, 504, 505, 502, 500, 501, 506, 507, 508, 509, 510, 511, 512, 486, 487, 488, 499, 498, 497, 212, 215, 214, 213, 223, 222, 221, 219, 218, 216, 211, 210, 217, 190, 191, 192, 193, 196, 197, 198, 199, 200, 201, 195, 194, 186, 185, 240, 241, 239, 237, 238, 187, 188, 189, 236, 235, 220, 233, 234, 232, 231, 229, 230, 263, 262, 261, 260, 259, 269, 270, 268, 267, 266, 265, 264, 228, 227, 226, 225, 224, 496, 495, 494, 493, 492, 482, 483, 491, 490, 489, 485, 484, 481, 480, 479, 478, 476, 477, 997, 998, 529, 523, 522, 514, 513, 568, 569, 567, 565, 566, 515, 516, 519, 520, 521, 524, 525, 526, 527, 528, 530, 531, 533, 532, 534, 535, 518, 517, 564, 563, 548, 561, 562, 560, 559, 557, 558, 590, 591, 556, 555, 554, 553, 552, 551, 550, 549, 547, 546, 545, 544, 539, 543, 542, 541, 540, 538, 536, 537, 825, 826, 827, 816, 815, 814, 813, 817, 818, 822, 823, 824, 821, 820, 810, 819, 811, 812, 840, 839, 838, 837, 836, 835, 834, 829, 828, 830, 831, 832, 833, 1001, 858, 859, 861, 855, 854, 853, 856, 852, 857, 851, 850, 842, 841, 896, 897, 895, 893, 894, 843, 849, 848, 847, 844, 845, 846, 892, 891, 890, 888, 889, 876, 874, 873, 872, 867, 866, 864, 863, 862, 860, 865, 868, 871, 870, 869, 875, 877, 878, 879, 880, 881, 882, 883, 884, 885, 887, 886, 919, 920, 921, 922, 923, 924, 926, 927, 928, 929, 930, 931, 932, 933, 934, 935, 936, 937, 938, 956, 957, 958, 959, 768, 766, 765, 767, 769, 770, 771, 772, 774, 773, 761, 760, 758, 759, 779, 778, 777, 775, 776, 912, 913, 914, 925, 915, 916, 917, 901, 918, 898, 899, 900, 902, 903, 905, 904, 908, 909, 910, 911, 781, 780, 782, 783, 784, 785, 786, 800, 801, 802, 803, 799, 798, 804, 805, 1000, 907, 906, 809, 808, 806, 807, 797, 796, 795, 794, 793, 792, 787, 755, 756, 757, 999, 762, 763, 764, 702, 701, 703, 697, 698, 699, 700, 968, 967, 966, 965, 964, 963, 962, 961, 960, 992, 952, 953, 955, 954, 939, 940, 941, 942, 943, 944, 945, 946, 947, 951, 950, 948, 949, 976, 977, 978, 975, 972, 973, 974, 971, 980, 979, 981, 970, 969, 986, 985, 984, 982, 983, 989, 988, 987, 683, 682, 684, 685, 686, 681, 680, 677, 676, 675, 674, 673, 670, 668, 669, 665, 664, 663, 662, 725, 724, 723, 727, 726, 728, 709, 707, 708, 706, 713, 712, 710, 711, 722, 721, 720, 714, 715, 716, 717, 719, 718, 667, 666, 671, 672, 678, 679, 687, 688, 689, 690, 691, 692, 693, 694, 695, 705, 696, 704, 739, 738, 736, 735, 729, 730, 734, 737, 743, 744, 741, 740, 742, 754, 752, 751, 753, 746, 747, 745, 733, 732, 748, 749, 750, 789, 788, 790, 791, 731]</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2048,17 +2048,17 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>331848</v>
+        <v>316906</v>
       </c>
       <c r="E49" t="n">
-        <v>28.10438340828814</v>
+        <v>22.33627362041344</v>
       </c>
       <c r="F49" t="n">
-        <v>60.00002813339233</v>
+        <v>60.00003409385681</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>[564, 563, 518, 517, 519, 516, 515, 520, 521, 522, 514, 513, 568, 567, 565, 566, 569, 570, 571, 572, 573, 589, 588, 587, 575, 574, 577, 576, 580, 581, 582, 583, 584, 585, 586, 597, 598, 596, 595, 593, 592, 594, 556, 555, 557, 559, 558, 591, 590, 560, 561, 562, 548, 547, 546, 545, 544, 539, 543, 542, 541, 540, 538, 536, 535, 534, 533, 532, 531, 530, 528, 525, 526, 527, 524, 523, 529, 998, 509, 510, 511, 512, 486, 485, 489, 490, 491, 483, 482, 492, 493, 494, 495, 496, 224, 225, 226, 227, 228, 264, 265, 266, 267, 268, 270, 269, 259, 260, 261, 245, 244, 243, 262, 263, 230, 231, 229, 232, 233, 234, 220, 219, 218, 217, 216, 211, 215, 214, 213, 212, 210, 208, 207, 206, 205, 204, 203, 202, 200, 197, 198, 199, 196, 193, 192, 191, 188, 187, 238, 237, 239, 240, 241, 185, 186, 194, 195, 201, 995, 181, 182, 183, 184, 158, 157, 161, 162, 163, 155, 154, 164, 165, 166, 167, 168, 160, 159, 171, 170, 169, 172, 173, 178, 179, 180, 177, 174, 176, 175, 156, 153, 152, 150, 151, 149, 148, 143, 142, 147, 145, 146, 144, 130, 129, 128, 127, 126, 124, 123, 122, 121, 119, 120, 256, 255, 254, 253, 252, 248, 249, 246, 247, 251, 250, 242, 236, 235, 190, 189, 221, 222, 223, 498, 497, 499, 488, 487, 484, 481, 480, 478, 479, 477, 476, 471, 470, 475, 473, 474, 472, 458, 457, 456, 455, 454, 452, 451, 450, 449, 447, 448, 453, 431, 430, 432, 433, 445, 443, 444, 446, 442, 441, 440, 438, 437, 439, 631, 630, 629, 628, 610, 609, 608, 607, 605, 606, 604, 611, 626, 627, 625, 624, 991, 632, 633, 634, 635, 636, 637, 638, 639, 372, 371, 370, 369, 368, 377, 367, 366, 365, 364, 363, 362, 361, 360, 359, 351, 350, 349, 348, 345, 346, 347, 353, 357, 358, 352, 344, 343, 340, 341, 337, 338, 339, 390, 391, 389, 388, 392, 386, 385, 384, 382, 383, 394, 393, 387, 378, 380, 379, 381, 399, 400, 398, 396, 395, 397, 334, 336, 335, 342, 356, 354, 355, 659, 660, 661, 655, 654, 656, 657, 658, 641, 642, 643, 652, 651, 653, 646, 645, 644, 647, 649, 648, 650, 621, 620, 622, 623, 616, 617, 618, 619, 729, 730, 731, 614, 615, 613, 612, 603, 602, 601, 600, 599, 796, 795, 794, 793, 792, 787, 785, 784, 783, 782, 780, 779, 778, 777, 775, 776, 912, 911, 910, 909, 908, 904, 905, 902, 903, 915, 916, 917, 921, 920, 922, 923, 924, 926, 925, 927, 928, 929, 930, 931, 932, 935, 933, 934, 936, 937, 938, 939, 954, 955, 953, 952, 992, 960, 961, 962, 963, 964, 965, 966, 967, 700, 699, 698, 697, 696, 705, 695, 694, 693, 692, 691, 690, 689, 688, 687, 679, 678, 677, 676, 673, 674, 675, 681, 685, 686, 680, 672, 671, 668, 669, 665, 666, 667, 718, 719, 717, 716, 720, 714, 713, 712, 710, 711, 722, 721, 715, 706, 708, 707, 709, 727, 728, 726, 724, 723, 725, 662, 664, 663, 670, 684, 682, 683, 987, 988, 989, 983, 982, 984, 985, 986, 969, 970, 971, 980, 979, 981, 974, 973, 972, 975, 977, 976, 978, 949, 948, 950, 951, 944, 945, 946, 947, 943, 942, 941, 940, 956, 957, 958, 959, 768, 766, 765, 767, 769, 770, 771, 772, 774, 773, 761, 760, 759, 758, 757, 756, 755, 788, 789, 790, 791, 750, 751, 752, 753, 754, 746, 747, 745, 748, 749, 732, 733, 734, 737, 743, 744, 742, 741, 740, 739, 738, 736, 735, 704, 703, 702, 701, 968, 764, 763, 762, 999, 786, 800, 801, 802, 803, 799, 798, 804, 805, 806, 807, 797, 808, 809, 810, 811, 819, 818, 817, 813, 814, 815, 816, 827, 826, 825, 828, 829, 834, 835, 836, 837, 838, 839, 840, 812, 820, 821, 822, 823, 824, 552, 553, 554, 551, 550, 549, 537, 831, 830, 833, 832, 1001, 857, 851, 850, 849, 848, 847, 844, 843, 894, 893, 895, 896, 897, 841, 842, 845, 846, 892, 891, 890, 889, 888, 876, 875, 874, 873, 872, 867, 871, 870, 869, 868, 866, 864, 863, 862, 861, 860, 859, 858, 856, 853, 854, 855, 852, 865, 877, 878, 879, 880, 881, 882, 883, 884, 886, 919, 918, 901, 900, 899, 898, 906, 907, 1000, 914, 913, 781, 887, 885, 578, 579, 997, 469, 468, 467, 466, 465, 464, 459, 427, 428, 429, 996, 434, 435, 436, 412, 413, 414, 416, 415, 405, 406, 409, 410, 411, 408, 407, 401, 402, 403, 286, 287, 285, 284, 283, 298, 299, 297, 296, 990, 304, 305, 306, 307, 308, 309, 310, 311, 44, 43, 42, 41, 40, 49, 39, 38, 37, 36, 35, 34, 33, 32, 31, 23, 22, 21, 20, 17, 18, 19, 25, 29, 30, 24, 16, 15, 12, 13, 9, 10, 11, 62, 63, 61, 60, 64, 58, 57, 56, 54, 55, 66, 65, 59, 50, 52, 51, 53, 71, 72, 70, 68, 67, 69, 6, 8, 7, 14, 28, 26, 27, 331, 332, 333, 327, 326, 328, 329, 330, 313, 314, 315, 324, 323, 325, 318, 317, 316, 319, 321, 320, 322, 293, 292, 294, 295, 288, 289, 290, 291, 312, 48, 47, 46, 45, 83, 82, 81, 77, 78, 79, 80, 87, 88, 86, 85, 84, 89, 91, 90, 97, 96, 95, 94, 93, 92, 76, 98, 132, 133, 134, 135, 137, 136, 131, 99, 100, 101, 102, 103, 104, 105, 117, 115, 116, 118, 114, 113, 112, 110, 109, 111, 303, 302, 301, 300, 282, 281, 280, 279, 277, 278, 276, 275, 274, 273, 272, 271, 258, 257, 125, 993, 106, 107, 108, 74, 73, 75, 138, 139, 140, 141, 994, 209, 500, 501, 506, 507, 508, 505, 502, 504, 503, 463, 462, 461, 460, 423, 424, 425, 426, 418, 419, 417, 420, 421, 422, 404, 375, 374, 373, 376, 640, 4, 2, 3, 5, 1, 0]</t>
+          <t>[1000, 805, 804, 799, 798, 803, 801, 802, 800, 786, 785, 784, 783, 782, 780, 779, 778, 777, 775, 776, 912, 911, 910, 909, 908, 904, 905, 902, 903, 915, 916, 917, 921, 920, 922, 923, 924, 926, 925, 927, 928, 929, 930, 931, 932, 935, 933, 934, 936, 937, 938, 939, 954, 955, 953, 952, 992, 960, 961, 962, 963, 964, 965, 966, 967, 700, 699, 698, 697, 696, 705, 695, 694, 693, 692, 691, 690, 689, 688, 687, 679, 678, 677, 676, 673, 674, 675, 681, 685, 686, 680, 672, 671, 668, 669, 665, 666, 667, 718, 719, 717, 716, 720, 714, 713, 712, 710, 711, 722, 721, 715, 706, 708, 707, 709, 727, 728, 726, 724, 723, 725, 662, 664, 663, 670, 684, 682, 683, 987, 988, 989, 983, 982, 984, 985, 986, 969, 970, 971, 980, 979, 981, 974, 973, 972, 975, 977, 976, 978, 949, 948, 950, 951, 944, 945, 946, 947, 943, 942, 941, 940, 956, 957, 958, 959, 768, 766, 765, 767, 769, 770, 771, 772, 774, 773, 761, 760, 759, 758, 757, 756, 755, 788, 789, 790, 791, 793, 792, 787, 751, 752, 753, 754, 746, 747, 745, 748, 749, 750, 732, 733, 734, 737, 743, 744, 742, 741, 740, 739, 738, 736, 735, 729, 730, 731, 614, 615, 613, 612, 611, 626, 627, 625, 624, 991, 632, 633, 634, 635, 636, 637, 638, 639, 372, 371, 370, 369, 368, 377, 367, 366, 365, 364, 363, 362, 361, 360, 359, 351, 350, 349, 348, 345, 346, 347, 353, 357, 358, 352, 344, 343, 340, 341, 337, 338, 339, 390, 391, 389, 388, 392, 386, 385, 384, 382, 383, 394, 393, 387, 378, 380, 379, 381, 399, 400, 398, 396, 395, 397, 334, 336, 335, 342, 356, 354, 355, 659, 660, 661, 655, 654, 656, 657, 658, 641, 642, 643, 652, 651, 653, 646, 645, 644, 647, 649, 648, 650, 621, 620, 622, 623, 616, 617, 618, 619, 640, 376, 375, 374, 373, 411, 410, 409, 405, 406, 407, 408, 415, 416, 414, 413, 412, 417, 419, 418, 425, 424, 423, 422, 421, 420, 404, 426, 460, 461, 462, 463, 465, 464, 459, 457, 456, 455, 454, 452, 451, 450, 449, 447, 448, 584, 583, 582, 581, 580, 576, 577, 574, 575, 587, 588, 589, 593, 592, 594, 595, 596, 598, 597, 599, 600, 601, 602, 603, 604, 607, 605, 606, 608, 609, 610, 628, 629, 630, 631, 440, 438, 437, 439, 441, 442, 443, 444, 446, 445, 433, 432, 431, 430, 429, 428, 427, 996, 434, 435, 436, 453, 474, 473, 475, 471, 470, 476, 477, 478, 479, 469, 472, 458, 466, 467, 468, 272, 271, 270, 268, 267, 265, 264, 266, 228, 227, 229, 231, 230, 263, 262, 245, 244, 243, 242, 241, 240, 239, 237, 238, 188, 191, 189, 190, 236, 235, 234, 233, 232, 220, 219, 218, 217, 216, 211, 215, 214, 213, 212, 210, 208, 207, 206, 205, 204, 203, 202, 200, 197, 198, 199, 196, 193, 192, 187, 186, 194, 195, 201, 995, 181, 182, 183, 184, 158, 157, 161, 162, 163, 155, 154, 164, 165, 166, 167, 168, 160, 159, 171, 170, 169, 172, 173, 178, 179, 180, 177, 174, 176, 175, 156, 153, 152, 150, 151, 149, 148, 143, 142, 147, 145, 146, 144, 130, 129, 128, 127, 126, 124, 123, 122, 121, 119, 120, 256, 255, 254, 253, 252, 248, 249, 246, 247, 259, 260, 261, 269, 258, 257, 125, 103, 102, 104, 105, 117, 115, 116, 118, 114, 113, 112, 110, 109, 111, 303, 302, 301, 300, 282, 281, 280, 279, 277, 278, 276, 283, 298, 299, 297, 296, 990, 304, 305, 306, 307, 308, 309, 310, 311, 44, 43, 42, 41, 40, 49, 39, 38, 37, 36, 35, 34, 33, 32, 31, 23, 22, 21, 20, 17, 18, 19, 25, 29, 30, 24, 16, 15, 12, 13, 9, 10, 11, 62, 63, 61, 60, 64, 58, 57, 56, 54, 55, 66, 65, 59, 50, 52, 51, 53, 71, 72, 70, 68, 67, 69, 6, 8, 7, 14, 28, 26, 27, 331, 332, 333, 327, 326, 328, 329, 330, 313, 314, 315, 324, 323, 325, 318, 317, 316, 319, 321, 320, 322, 293, 292, 294, 295, 288, 289, 290, 291, 401, 402, 403, 286, 287, 285, 284, 275, 274, 273, 226, 225, 224, 223, 222, 221, 496, 495, 494, 493, 492, 482, 483, 491, 490, 489, 485, 486, 487, 488, 499, 498, 497, 500, 501, 506, 507, 508, 509, 510, 511, 512, 484, 481, 480, 997, 579, 578, 570, 571, 572, 573, 590, 591, 558, 559, 557, 555, 556, 554, 553, 552, 551, 550, 549, 547, 546, 545, 544, 539, 543, 542, 541, 540, 538, 536, 535, 534, 533, 532, 531, 530, 528, 525, 526, 527, 524, 521, 520, 519, 516, 515, 566, 565, 567, 568, 569, 513, 514, 522, 523, 529, 998, 504, 505, 502, 503, 209, 185, 250, 251, 994, 141, 140, 139, 138, 137, 136, 131, 99, 100, 101, 993, 106, 107, 108, 84, 85, 86, 88, 87, 77, 78, 81, 82, 83, 80, 79, 73, 74, 75, 76, 92, 93, 91, 89, 90, 97, 96, 95, 94, 133, 132, 134, 135, 98, 46, 47, 45, 48, 312, 4, 2, 3, 5, 1, 0, 585, 586, 560, 561, 562, 548, 563, 564, 517, 518, 537, 825, 826, 827, 816, 815, 814, 813, 817, 818, 819, 811, 810, 820, 821, 822, 823, 824, 812, 840, 839, 838, 837, 836, 835, 834, 829, 828, 830, 833, 832, 831, 1001, 857, 851, 850, 849, 848, 847, 844, 843, 894, 893, 895, 896, 897, 841, 842, 845, 846, 892, 891, 890, 889, 888, 876, 875, 874, 873, 872, 867, 871, 870, 869, 868, 866, 864, 863, 862, 861, 860, 859, 858, 856, 853, 854, 855, 852, 865, 877, 878, 879, 880, 881, 882, 883, 884, 886, 919, 918, 901, 900, 899, 898, 906, 907, 808, 809, 806, 807, 797, 796, 795, 794, 781, 913, 914, 885, 887, 999, 762, 763, 764, 702, 703, 701, 704, 968]</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2082,17 +2082,17 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>268730</v>
+        <v>267976</v>
       </c>
       <c r="E50" t="n">
-        <v>3.738732652627922</v>
+        <v>3.447663533362929</v>
       </c>
       <c r="F50" t="n">
-        <v>7.718400001525879</v>
+        <v>8.929805040359497</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>[540, 539, 544, 538, 537, 536, 535, 534, 532, 530, 531, 533, 527, 526, 525, 528, 524, 521, 520, 519, 517, 516, 515, 566, 565, 567, 569, 568, 513, 514, 522, 523, 529, 998, 505, 504, 503, 502, 500, 501, 506, 507, 508, 509, 510, 511, 512, 486, 487, 488, 499, 498, 497, 212, 215, 216, 211, 210, 209, 208, 207, 206, 204, 205, 203, 202, 200, 197, 199, 198, 196, 201, 195, 194, 193, 192, 188, 187, 186, 185, 240, 241, 239, 237, 238, 189, 191, 190, 236, 235, 217, 218, 214, 213, 219, 220, 233, 234, 232, 221, 222, 223, 224, 225, 226, 496, 495, 494, 493, 492, 482, 483, 491, 490, 489, 485, 484, 481, 480, 997, 579, 578, 570, 571, 572, 573, 589, 590, 591, 558, 559, 557, 555, 556, 592, 593, 594, 595, 596, 598, 597, 587, 588, 575, 574, 577, 576, 580, 581, 582, 583, 586, 585, 584, 448, 447, 444, 446, 433, 432, 431, 430, 429, 428, 427, 460, 461, 462, 463, 465, 464, 459, 458, 457, 456, 455, 454, 452, 451, 450, 449, 453, 474, 472, 473, 475, 476, 477, 478, 479, 471, 470, 469, 468, 467, 466, 275, 274, 273, 272, 271, 270, 268, 267, 260, 261, 265, 266, 264, 228, 227, 229, 231, 230, 263, 262, 245, 244, 243, 242, 250, 251, 994, 152, 153, 154, 163, 155, 156, 157, 158, 184, 183, 182, 181, 995, 180, 179, 178, 177, 176, 175, 174, 173, 172, 169, 170, 171, 160, 159, 161, 162, 166, 167, 168, 165, 164, 151, 150, 149, 148, 143, 142, 141, 140, 139, 138, 137, 136, 131, 130, 144, 145, 147, 146, 125, 255, 254, 253, 252, 248, 249, 246, 247, 259, 269, 258, 257, 256, 120, 119, 121, 122, 123, 124, 126, 127, 129, 128, 101, 100, 99, 132, 133, 134, 135, 75, 74, 73, 0, 1, 4, 2, 3, 5, 6, 7, 8, 9, 13, 12, 14, 15, 16, 10, 11, 69, 68, 67, 71, 70, 72, 53, 54, 55, 66, 65, 64, 60, 59, 58, 57, 56, 52, 50, 51, 80, 79, 78, 77, 76, 92, 93, 94, 95, 96, 97, 98, 90, 91, 89, 88, 86, 84, 85, 87, 81, 82, 83, 47, 46, 45, 108, 107, 106, 993, 102, 103, 104, 105, 117, 118, 116, 115, 114, 113, 111, 109, 110, 112, 303, 302, 301, 300, 282, 281, 280, 279, 278, 277, 276, 283, 298, 299, 297, 296, 990, 304, 305, 306, 307, 308, 309, 310, 311, 316, 317, 318, 315, 312, 44, 43, 42, 41, 48, 40, 49, 39, 38, 37, 36, 35, 34, 33, 32, 61, 63, 62, 31, 23, 22, 21, 20, 17, 18, 19, 25, 24, 30, 29, 28, 26, 27, 331, 332, 333, 327, 328, 329, 330, 313, 314, 325, 324, 323, 326, 322, 319, 321, 320, 293, 292, 294, 295, 291, 290, 289, 288, 287, 286, 285, 284, 403, 402, 401, 407, 408, 379, 381, 400, 398, 399, 395, 396, 397, 334, 335, 336, 337, 338, 339, 390, 391, 389, 388, 387, 385, 386, 392, 393, 394, 383, 382, 384, 380, 378, 367, 377, 368, 376, 369, 370, 371, 372, 373, 374, 375, 411, 410, 412, 413, 414, 416, 415, 409, 406, 405, 404, 417, 418, 419, 420, 421, 422, 423, 424, 425, 426, 996, 434, 435, 436, 437, 438, 440, 439, 441, 445, 443, 442, 630, 631, 629, 628, 610, 609, 608, 607, 606, 605, 604, 603, 602, 601, 599, 600, 794, 795, 796, 797, 807, 806, 805, 804, 798, 799, 803, 802, 801, 800, 786, 785, 784, 787, 792, 793, 791, 790, 789, 788, 755, 756, 757, 758, 759, 760, 761, 773, 774, 772, 771, 770, 769, 958, 957, 959, 766, 768, 767, 765, 764, 763, 762, 999, 754, 753, 752, 751, 750, 749, 748, 745, 747, 746, 742, 740, 741, 743, 744, 732, 733, 734, 737, 738, 739, 703, 702, 701, 962, 961, 963, 964, 965, 966, 972, 973, 975, 974, 968, 967, 700, 699, 698, 697, 704, 696, 705, 706, 708, 707, 736, 735, 729, 730, 731, 615, 614, 613, 612, 611, 626, 627, 625, 624, 991, 632, 633, 634, 635, 636, 637, 638, 639, 640, 643, 642, 641, 363, 362, 364, 365, 366, 361, 360, 359, 351, 350, 344, 343, 340, 341, 342, 345, 346, 347, 348, 349, 352, 358, 357, 353, 356, 354, 355, 659, 660, 661, 655, 654, 656, 657, 658, 653, 652, 651, 650, 647, 646, 645, 644, 649, 648, 621, 620, 622, 623, 616, 617, 618, 619, 726, 728, 727, 723, 724, 725, 667, 666, 662, 663, 664, 665, 669, 668, 670, 671, 672, 718, 719, 717, 716, 720, 721, 722, 711, 710, 709, 712, 713, 714, 715, 695, 694, 693, 692, 691, 690, 689, 688, 687, 685, 686, 680, 679, 678, 677, 676, 673, 674, 675, 681, 684, 682, 683, 987, 988, 989, 983, 982, 984, 985, 986, 969, 970, 971, 980, 981, 979, 978, 977, 976, 949, 948, 950, 951, 947, 946, 945, 944, 943, 942, 941, 940, 939, 954, 955, 953, 952, 992, 960, 956, 938, 937, 936, 935, 934, 933, 932, 931, 930, 929, 928, 927, 925, 914, 913, 912, 776, 775, 777, 778, 779, 780, 782, 783, 781, 911, 910, 909, 908, 904, 905, 902, 903, 915, 916, 917, 924, 926, 923, 922, 921, 920, 919, 918, 901, 900, 899, 898, 906, 907, 1000, 808, 809, 810, 811, 812, 841, 896, 897, 895, 894, 893, 892, 891, 876, 889, 890, 888, 887, 885, 886, 884, 883, 882, 881, 880, 879, 878, 877, 875, 869, 870, 871, 868, 866, 867, 872, 874, 873, 846, 845, 847, 848, 844, 843, 842, 850, 849, 852, 853, 854, 855, 863, 864, 865, 862, 860, 861, 859, 858, 856, 851, 857, 1001, 837, 838, 836, 835, 834, 833, 832, 831, 830, 829, 828, 825, 826, 827, 816, 815, 814, 839, 840, 813, 817, 818, 819, 820, 821, 822, 823, 824, 554, 553, 552, 551, 550, 549, 548, 561, 560, 562, 563, 564, 518, 545, 546, 547, 541, 542, 543]</t>
+          <t>[365, 366, 387, 386, 385, 384, 381, 382, 383, 394, 393, 392, 388, 389, 391, 390, 344, 343, 342, 341, 340, 339, 338, 337, 336, 335, 334, 397, 396, 395, 399, 400, 398, 291, 290, 289, 288, 295, 294, 292, 293, 320, 321, 322, 319, 318, 317, 316, 311, 310, 309, 308, 307, 306, 45, 46, 47, 42, 43, 44, 312, 315, 324, 323, 325, 314, 313, 330, 329, 328, 326, 327, 333, 332, 331, 27, 26, 28, 25, 29, 30, 24, 23, 22, 21, 20, 19, 18, 17, 16, 15, 14, 12, 13, 9, 10, 11, 62, 63, 61, 31, 32, 33, 34, 35, 36, 37, 38, 39, 49, 40, 41, 48, 50, 52, 51, 53, 54, 56, 57, 58, 59, 60, 64, 65, 66, 55, 71, 72, 70, 67, 68, 69, 6, 8, 7, 5, 3, 2, 4, 1, 0, 73, 74, 75, 135, 134, 133, 132, 98, 97, 96, 95, 94, 93, 92, 76, 89, 91, 90, 86, 85, 88, 87, 77, 78, 79, 80, 81, 82, 83, 84, 108, 107, 106, 993, 102, 101, 100, 99, 131, 136, 137, 138, 139, 140, 141, 142, 143, 148, 149, 150, 151, 152, 153, 155, 163, 154, 164, 165, 168, 167, 166, 162, 161, 157, 158, 159, 160, 171, 170, 169, 172, 173, 174, 175, 176, 177, 178, 179, 180, 181, 182, 183, 184, 156, 185, 186, 194, 195, 201, 995, 202, 203, 205, 204, 206, 209, 208, 207, 199, 198, 197, 200, 196, 193, 192, 191, 188, 187, 238, 237, 239, 240, 241, 242, 243, 244, 245, 261, 260, 259, 247, 246, 248, 249, 250, 251, 994, 252, 253, 254, 255, 125, 146, 147, 145, 144, 130, 129, 128, 127, 126, 124, 123, 122, 121, 119, 120, 256, 257, 258, 269, 273, 272, 271, 270, 268, 267, 266, 265, 264, 263, 262, 230, 228, 227, 229, 231, 232, 234, 233, 220, 235, 236, 189, 190, 217, 218, 216, 211, 210, 212, 215, 214, 213, 219, 221, 222, 223, 224, 225, 226, 496, 495, 494, 493, 492, 482, 483, 491, 490, 489, 485, 484, 481, 480, 479, 478, 476, 477, 997, 579, 578, 570, 571, 572, 573, 590, 591, 558, 556, 555, 557, 559, 560, 562, 561, 548, 546, 545, 544, 539, 538, 536, 535, 527, 526, 525, 528, 524, 521, 515, 516, 520, 519, 517, 518, 563, 564, 565, 566, 567, 569, 568, 513, 514, 522, 523, 529, 509, 510, 511, 512, 486, 487, 488, 499, 498, 497, 500, 501, 502, 503, 504, 505, 506, 507, 508, 998, 530, 531, 533, 532, 534, 537, 540, 543, 542, 541, 547, 549, 550, 551, 552, 553, 554, 824, 823, 822, 821, 820, 810, 811, 819, 818, 817, 812, 813, 814, 815, 816, 827, 826, 825, 828, 829, 830, 831, 832, 833, 834, 835, 836, 840, 839, 838, 837, 1001, 858, 859, 860, 862, 865, 864, 863, 861, 855, 854, 853, 856, 857, 851, 852, 849, 850, 842, 841, 896, 897, 895, 893, 894, 843, 844, 848, 847, 845, 846, 892, 891, 890, 889, 876, 874, 873, 872, 867, 866, 868, 871, 870, 869, 875, 877, 878, 879, 880, 881, 882, 883, 884, 885, 887, 888, 886, 898, 899, 900, 901, 918, 919, 920, 921, 922, 923, 924, 926, 927, 928, 929, 930, 931, 932, 933, 934, 935, 936, 937, 938, 956, 957, 958, 959, 768, 766, 765, 767, 769, 770, 771, 772, 774, 773, 761, 760, 759, 779, 778, 777, 775, 776, 912, 911, 910, 909, 908, 914, 913, 925, 915, 916, 917, 902, 903, 904, 905, 906, 907, 1000, 809, 808, 807, 806, 805, 804, 803, 799, 798, 797, 800, 801, 802, 781, 780, 782, 783, 784, 785, 786, 787, 792, 793, 791, 790, 789, 750, 749, 748, 747, 745, 732, 733, 734, 737, 738, 739, 740, 741, 743, 744, 742, 746, 754, 753, 752, 751, 788, 755, 756, 757, 758, 999, 762, 763, 764, 701, 702, 703, 704, 696, 697, 698, 699, 700, 967, 966, 965, 964, 963, 962, 961, 960, 992, 952, 953, 955, 954, 939, 940, 941, 942, 943, 944, 945, 946, 947, 948, 951, 950, 949, 976, 977, 978, 975, 972, 973, 974, 971, 980, 979, 981, 970, 968, 969, 986, 985, 984, 982, 983, 989, 988, 987, 683, 682, 684, 681, 685, 686, 680, 675, 674, 673, 676, 677, 678, 679, 687, 688, 689, 690, 691, 692, 693, 694, 695, 705, 706, 713, 714, 715, 716, 720, 719, 717, 718, 672, 671, 670, 668, 669, 665, 664, 663, 662, 666, 667, 721, 722, 711, 727, 723, 724, 725, 726, 728, 709, 710, 712, 708, 707, 736, 735, 729, 730, 731, 615, 614, 613, 612, 611, 626, 627, 625, 624, 991, 632, 633, 635, 634, 373, 374, 375, 436, 435, 434, 996, 430, 431, 432, 433, 445, 446, 444, 443, 442, 441, 440, 439, 437, 438, 631, 630, 629, 628, 610, 609, 608, 607, 606, 605, 604, 603, 602, 601, 794, 795, 796, 600, 599, 598, 596, 595, 594, 592, 593, 589, 588, 597, 587, 575, 574, 577, 576, 580, 581, 582, 583, 586, 585, 584, 448, 447, 449, 450, 451, 452, 453, 454, 455, 456, 429, 428, 427, 460, 461, 462, 463, 465, 464, 459, 457, 458, 472, 473, 474, 475, 471, 470, 469, 468, 467, 466, 274, 275, 276, 277, 278, 279, 280, 281, 282, 300, 301, 302, 303, 112, 113, 114, 115, 116, 118, 103, 104, 105, 117, 111, 109, 110, 305, 304, 990, 296, 297, 299, 298, 283, 284, 285, 286, 287, 403, 402, 401, 407, 406, 405, 404, 420, 421, 422, 423, 424, 425, 426, 418, 419, 417, 416, 414, 412, 413, 415, 409, 410, 411, 408, 379, 380, 378, 367, 377, 368, 376, 369, 370, 371, 372, 639, 638, 637, 636, 622, 623, 616, 617, 618, 619, 620, 621, 648, 649, 650, 647, 646, 645, 644, 640, 643, 652, 651, 653, 642, 641, 658, 657, 656, 654, 655, 661, 660, 659, 355, 354, 347, 346, 345, 348, 349, 350, 351, 352, 353, 356, 357, 358, 359, 360, 361, 362, 363, 364]</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2122,7 +2122,7 @@
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>12.30584001541138</v>
+        <v>11.79944086074829</v>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
@@ -2184,16 +2184,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26.73</v>
+        <v>26.19</v>
       </c>
       <c r="C2" t="n">
-        <v>21.6</v>
+        <v>20.63</v>
       </c>
       <c r="D2" t="n">
-        <v>34.74</v>
+        <v>30.09</v>
       </c>
       <c r="E2" t="n">
-        <v>3.49</v>
+        <v>2.85</v>
       </c>
       <c r="F2" t="n">
         <v>0.03</v>
@@ -2206,19 +2206,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.800000000000001</v>
+        <v>8.69</v>
       </c>
       <c r="C3" t="n">
-        <v>5.63</v>
+        <v>1.17</v>
       </c>
       <c r="D3" t="n">
-        <v>16.38</v>
+        <v>23.92</v>
       </c>
       <c r="E3" t="n">
-        <v>3.15</v>
+        <v>5.97</v>
       </c>
       <c r="F3" t="n">
-        <v>1.84</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="4">
@@ -2228,16 +2228,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20.97</v>
+        <v>20.7</v>
       </c>
       <c r="C4" t="n">
-        <v>6.34</v>
+        <v>6.81</v>
       </c>
       <c r="D4" t="n">
-        <v>28.1</v>
+        <v>26.78</v>
       </c>
       <c r="E4" t="n">
-        <v>7.49</v>
+        <v>6.25</v>
       </c>
       <c r="F4" t="n">
         <v>60</v>
@@ -2250,19 +2250,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>3.74</v>
+        <v>3.45</v>
       </c>
       <c r="E5" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="F5" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="6">
@@ -2284,7 +2284,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>3.51</v>
+        <v>3.36</v>
       </c>
     </row>
   </sheetData>
